--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0096F69B-4092-4F6A-8C5A-42D95CF2F431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC5D553-17FE-4946-B674-2E2A9B8E2F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="72">
   <si>
     <t>10A1</t>
   </si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>Tự Nhiên</t>
-  </si>
-  <si>
-    <t>Ban Giáo Hiệu</t>
   </si>
   <si>
     <t>Tên môn học</t>
@@ -282,7 +279,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -388,6 +385,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -407,13 +413,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -428,19 +436,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -748,8 +756,8 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>72</v>
+      <c r="A5" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -772,15 +780,15 @@
         <v>33</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C7" s="1" t="str">
         <f>A47</f>
@@ -800,7 +808,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>12</v>
@@ -921,8 +929,8 @@
       <c r="G19" s="1"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" s="18" t="s">
-        <v>68</v>
+      <c r="A21" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
@@ -934,26 +942,26 @@
       <c r="A23" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-      <c r="U23" s="13"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
@@ -986,104 +994,104 @@
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="19" t="s">
-        <v>69</v>
+      <c r="A44" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
       </c>
       <c r="C46" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" ref="C46:C62" si="0">A$81</f>
         <v>Sáng</v>
       </c>
       <c r="D46" s="2">
@@ -1100,13 +1108,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2">
         <v>1</v>
       </c>
       <c r="C47" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D47" s="2">
@@ -1123,13 +1131,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2">
         <v>1</v>
       </c>
       <c r="C48" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D48" s="2">
@@ -1146,188 +1154,182 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" s="2">
         <v>1</v>
       </c>
       <c r="C49" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D49" s="2">
         <v>1</v>
       </c>
       <c r="E49" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" ref="E49:E62" si="1">B$82</f>
         <v>0</v>
       </c>
       <c r="F49" s="2" t="str">
         <f>A$66</f>
         <v>Xã Hội</v>
       </c>
-      <c r="G49" s="13"/>
+      <c r="G49" s="6"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
       </c>
       <c r="C50" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D50" s="2">
         <v>1</v>
       </c>
       <c r="E50" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F50" s="2" t="str">
         <f>A$66</f>
         <v>Xã Hội</v>
       </c>
-      <c r="G50" s="14"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2">
         <v>1</v>
       </c>
       <c r="C51" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D51" s="2">
         <v>1</v>
       </c>
       <c r="E51" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F51" s="2" t="str">
         <f>A$67</f>
         <v>Tự Nhiên</v>
       </c>
-      <c r="G51" s="14"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" s="2">
         <v>1</v>
       </c>
       <c r="C52" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D52" s="2">
         <v>1</v>
       </c>
       <c r="E52" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F52" s="2" t="str">
         <f>A$67</f>
         <v>Tự Nhiên</v>
       </c>
-      <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2">
         <v>1</v>
       </c>
       <c r="C53" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D53" s="2">
         <v>1</v>
       </c>
       <c r="E53" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F53" s="2" t="str">
         <f>A$67</f>
         <v>Tự Nhiên</v>
       </c>
-      <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54" s="2">
         <v>2</v>
       </c>
       <c r="C54" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D54" s="2">
         <v>2</v>
       </c>
       <c r="E54" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F54" s="2" t="str">
         <f>A$67</f>
         <v>Tự Nhiên</v>
       </c>
-      <c r="G54" s="14"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B55" s="2">
         <v>2</v>
       </c>
       <c r="C55" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D55" s="2">
         <v>2</v>
       </c>
       <c r="E55" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F55" s="2" t="str">
         <f>A$66</f>
         <v>Xã Hội</v>
       </c>
-      <c r="G55" s="14"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2">
         <v>1</v>
       </c>
       <c r="C56" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D56" s="2">
         <v>1</v>
       </c>
       <c r="E56" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F56" s="2" t="str">
@@ -1337,20 +1339,20 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2">
         <v>2</v>
       </c>
       <c r="C57" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D57" s="2">
         <v>2</v>
       </c>
       <c r="E57" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F57" s="2" t="str">
@@ -1360,20 +1362,20 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2">
         <v>2</v>
       </c>
       <c r="C58" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
       </c>
       <c r="E58" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F58" s="2" t="str">
@@ -1383,20 +1385,20 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2">
         <v>2</v>
       </c>
       <c r="C59" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D59" s="2">
         <v>2</v>
       </c>
       <c r="E59" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F59" s="2" t="str">
@@ -1406,20 +1408,20 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2">
         <v>2</v>
       </c>
       <c r="C60" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D60" s="2">
         <v>2</v>
       </c>
       <c r="E60" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F60" s="2" t="str">
@@ -1429,20 +1431,20 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2">
         <v>1</v>
       </c>
       <c r="C61" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D61" s="2">
         <v>1</v>
       </c>
       <c r="E61" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F61" s="2" t="str">
@@ -1452,20 +1454,20 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="2">
         <v>1</v>
       </c>
       <c r="C62" s="2" t="str">
-        <f>A$81</f>
+        <f t="shared" si="0"/>
         <v>Sáng</v>
       </c>
       <c r="D62" s="2">
         <v>1</v>
       </c>
       <c r="E62" s="2" t="b">
-        <f>B$82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F62" s="2" t="str">
@@ -1474,17 +1476,17 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="18" t="s">
-        <v>70</v>
+      <c r="A64" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
@@ -1492,108 +1494,79 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
+      <c r="A68" s="19"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
+      <c r="A70" s="10" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
+        <v>64</v>
+      </c>
+      <c r="B71" s="7"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B72" s="16"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
+      <c r="B72" s="8"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B73" s="16"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
+      <c r="B73" s="8"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B74" s="16"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
+      <c r="B74" s="8"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B75" s="16"/>
+      <c r="B75" s="8"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B76" s="16"/>
+      <c r="B76" s="8"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B77" s="16"/>
-      <c r="C77" s="13"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="6"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C78" s="13"/>
+      <c r="C78" s="6"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C79" s="14"/>
+      <c r="A79" s="9" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -1606,7 +1579,7 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="17" t="s">
+      <c r="A82" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B82" s="1" t="b">
@@ -1626,28 +1599,28 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="8"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -1713,7 +1686,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
@@ -1741,7 +1714,7 @@
       <c r="V6" s="1"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
+      <c r="A7" s="11"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
@@ -1767,7 +1740,7 @@
       <c r="V7" s="1"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
@@ -1793,7 +1766,7 @@
       <c r="V8" s="1"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
+      <c r="A9" s="11"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
@@ -1819,7 +1792,7 @@
       <c r="V9" s="1"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="9"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -1845,7 +1818,7 @@
       <c r="V10" s="1"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -1873,7 +1846,7 @@
       <c r="V11" s="1"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -1899,7 +1872,7 @@
       <c r="V12" s="1"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -1925,28 +1898,28 @@
       <c r="V13" s="1"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="8"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="17"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2012,7 +1985,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
@@ -2040,7 +2013,7 @@
       <c r="V18" s="1"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="9"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
@@ -2066,7 +2039,7 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
@@ -2092,7 +2065,7 @@
       <c r="V20" s="1"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="9"/>
+      <c r="A21" s="11"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -2118,7 +2091,7 @@
       <c r="V21" s="1"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="9"/>
+      <c r="A22" s="11"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -2144,7 +2117,7 @@
       <c r="V22" s="1"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -2172,7 +2145,7 @@
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="11"/>
+      <c r="A24" s="13"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -2198,7 +2171,7 @@
       <c r="V24" s="1"/>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="12"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -2224,28 +2197,28 @@
       <c r="V25" s="1"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="8"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="17"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -2311,7 +2284,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
@@ -2339,7 +2312,7 @@
       <c r="V30" s="1"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="9"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
@@ -2365,7 +2338,7 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="9"/>
+      <c r="A32" s="11"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -2391,7 +2364,7 @@
       <c r="V32" s="1"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="9"/>
+      <c r="A33" s="11"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -2417,7 +2390,7 @@
       <c r="V33" s="1"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="9"/>
+      <c r="A34" s="11"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -2443,7 +2416,7 @@
       <c r="V34" s="1"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -2471,7 +2444,7 @@
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="11"/>
+      <c r="A36" s="13"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -2497,7 +2470,7 @@
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="12"/>
+      <c r="A37" s="14"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -2523,28 +2496,28 @@
       <c r="V37" s="1"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="8"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16"/>
+      <c r="S40" s="16"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="16"/>
+      <c r="V40" s="17"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -2610,7 +2583,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -2638,7 +2611,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="9"/>
+      <c r="A43" s="11"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -2664,7 +2637,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="9"/>
+      <c r="A44" s="11"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -2690,7 +2663,7 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="9"/>
+      <c r="A45" s="11"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -2716,7 +2689,7 @@
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="9"/>
+      <c r="A46" s="11"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -2742,7 +2715,7 @@
       <c r="V46" s="1"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -2770,7 +2743,7 @@
       <c r="V47" s="1"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="11"/>
+      <c r="A48" s="13"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -2796,7 +2769,7 @@
       <c r="V48" s="1"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="12"/>
+      <c r="A49" s="14"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -2822,28 +2795,28 @@
       <c r="V49" s="1"/>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
-      <c r="U52" s="7"/>
-      <c r="V52" s="8"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="16"/>
+      <c r="V52" s="17"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -2909,7 +2882,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
@@ -2937,7 +2910,7 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="9"/>
+      <c r="A55" s="11"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -2963,7 +2936,7 @@
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="9"/>
+      <c r="A56" s="11"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -2989,7 +2962,7 @@
       <c r="V56" s="1"/>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="9"/>
+      <c r="A57" s="11"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -3015,7 +2988,7 @@
       <c r="V57" s="1"/>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="9"/>
+      <c r="A58" s="11"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -3041,7 +3014,7 @@
       <c r="V58" s="1"/>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -3069,7 +3042,7 @@
       <c r="V59" s="1"/>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="11"/>
+      <c r="A60" s="13"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -3095,7 +3068,7 @@
       <c r="V60" s="1"/>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="12"/>
+      <c r="A61" s="14"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -3121,28 +3094,28 @@
       <c r="V61" s="1"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="7"/>
-      <c r="T64" s="7"/>
-      <c r="U64" s="7"/>
-      <c r="V64" s="8"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="16"/>
+      <c r="L64" s="16"/>
+      <c r="M64" s="16"/>
+      <c r="N64" s="16"/>
+      <c r="O64" s="16"/>
+      <c r="P64" s="16"/>
+      <c r="Q64" s="16"/>
+      <c r="R64" s="16"/>
+      <c r="S64" s="16"/>
+      <c r="T64" s="16"/>
+      <c r="U64" s="16"/>
+      <c r="V64" s="17"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -3208,7 +3181,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -3236,7 +3209,7 @@
       <c r="V66" s="1"/>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="9"/>
+      <c r="A67" s="11"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -3262,7 +3235,7 @@
       <c r="V67" s="1"/>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="9"/>
+      <c r="A68" s="11"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -3288,7 +3261,7 @@
       <c r="V68" s="1"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="9"/>
+      <c r="A69" s="11"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -3314,7 +3287,7 @@
       <c r="V69" s="1"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="9"/>
+      <c r="A70" s="11"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -3340,7 +3313,7 @@
       <c r="V70" s="1"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -3368,7 +3341,7 @@
       <c r="V71" s="1"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="11"/>
+      <c r="A72" s="13"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -3394,7 +3367,7 @@
       <c r="V72" s="1"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="12"/>
+      <c r="A73" s="14"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -3421,6 +3394,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -3429,16 +3412,6 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC5D553-17FE-4946-B674-2E2A9B8E2F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E76DB2-2EA3-4178-9C49-E9834DB93D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="73">
   <si>
     <t>10A1</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Giáo Viên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổ </t>
   </si>
 </sst>
 </file>
@@ -424,6 +427,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -435,21 +453,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -755,12 +758,12 @@
     <col min="21" max="21" width="9.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -779,11 +782,14 @@
       <c r="F6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>65</v>
       </c>
@@ -805,8 +811,12 @@
         <f>A75</f>
         <v>Thứ Năm</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H7" s="1" t="str">
+        <f>F$47</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>65</v>
       </c>
@@ -828,8 +838,12 @@
         <f>A75</f>
         <v>Thứ Năm</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H8" s="1" t="str">
+        <f>F$47</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -837,8 +851,9 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -846,8 +861,9 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -855,8 +871,9 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -864,8 +881,9 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -873,8 +891,9 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -882,8 +901,9 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -891,8 +911,9 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -900,6 +921,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
@@ -909,6 +931,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
@@ -918,6 +941,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -927,6 +951,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
@@ -1494,12 +1519,12 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="19"/>
+      <c r="A68" s="12"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -1599,28 +1624,28 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="17"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="15"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -1686,7 +1711,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
@@ -1714,7 +1739,7 @@
       <c r="V6" s="1"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
@@ -1740,7 +1765,7 @@
       <c r="V7" s="1"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="11"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
@@ -1766,7 +1791,7 @@
       <c r="V8" s="1"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
@@ -1792,7 +1817,7 @@
       <c r="V9" s="1"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -1818,7 +1843,7 @@
       <c r="V10" s="1"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -1846,7 +1871,7 @@
       <c r="V11" s="1"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -1872,7 +1897,7 @@
       <c r="V12" s="1"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="14"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -1898,28 +1923,28 @@
       <c r="V13" s="1"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="17"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="15"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -1985,7 +2010,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
@@ -2013,7 +2038,7 @@
       <c r="V18" s="1"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="11"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
@@ -2039,7 +2064,7 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
@@ -2065,7 +2090,7 @@
       <c r="V20" s="1"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="11"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -2091,7 +2116,7 @@
       <c r="V21" s="1"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="11"/>
+      <c r="A22" s="16"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -2117,7 +2142,7 @@
       <c r="V22" s="1"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -2145,7 +2170,7 @@
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -2171,7 +2196,7 @@
       <c r="V24" s="1"/>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="14"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -2197,28 +2222,28 @@
       <c r="V25" s="1"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="17"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="15"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -2284,7 +2309,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
@@ -2312,7 +2337,7 @@
       <c r="V30" s="1"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="11"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
@@ -2338,7 +2363,7 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="11"/>
+      <c r="A32" s="16"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -2364,7 +2389,7 @@
       <c r="V32" s="1"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="11"/>
+      <c r="A33" s="16"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -2390,7 +2415,7 @@
       <c r="V33" s="1"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="11"/>
+      <c r="A34" s="16"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -2416,7 +2441,7 @@
       <c r="V34" s="1"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -2444,7 +2469,7 @@
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -2470,7 +2495,7 @@
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="14"/>
+      <c r="A37" s="19"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -2496,28 +2521,28 @@
       <c r="V37" s="1"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="17"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="14"/>
+      <c r="Q40" s="14"/>
+      <c r="R40" s="14"/>
+      <c r="S40" s="14"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="14"/>
+      <c r="V40" s="15"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -2583,7 +2608,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -2611,7 +2636,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="11"/>
+      <c r="A43" s="16"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -2637,7 +2662,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="11"/>
+      <c r="A44" s="16"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -2663,7 +2688,7 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="11"/>
+      <c r="A45" s="16"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -2689,7 +2714,7 @@
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="11"/>
+      <c r="A46" s="16"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -2715,7 +2740,7 @@
       <c r="V46" s="1"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -2743,7 +2768,7 @@
       <c r="V47" s="1"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
+      <c r="A48" s="18"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -2769,7 +2794,7 @@
       <c r="V48" s="1"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="14"/>
+      <c r="A49" s="19"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -2795,28 +2820,28 @@
       <c r="V49" s="1"/>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="16"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
-      <c r="S52" s="16"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="16"/>
-      <c r="V52" s="17"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="14"/>
+      <c r="O52" s="14"/>
+      <c r="P52" s="14"/>
+      <c r="Q52" s="14"/>
+      <c r="R52" s="14"/>
+      <c r="S52" s="14"/>
+      <c r="T52" s="14"/>
+      <c r="U52" s="14"/>
+      <c r="V52" s="15"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -2882,7 +2907,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
@@ -2910,7 +2935,7 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="11"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -2936,7 +2961,7 @@
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="11"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -2962,7 +2987,7 @@
       <c r="V56" s="1"/>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="11"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -2988,7 +3013,7 @@
       <c r="V57" s="1"/>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="11"/>
+      <c r="A58" s="16"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -3014,7 +3039,7 @@
       <c r="V58" s="1"/>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -3042,7 +3067,7 @@
       <c r="V59" s="1"/>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
+      <c r="A60" s="18"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -3068,7 +3093,7 @@
       <c r="V60" s="1"/>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="14"/>
+      <c r="A61" s="19"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -3094,28 +3119,28 @@
       <c r="V61" s="1"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="16"/>
-      <c r="O64" s="16"/>
-      <c r="P64" s="16"/>
-      <c r="Q64" s="16"/>
-      <c r="R64" s="16"/>
-      <c r="S64" s="16"/>
-      <c r="T64" s="16"/>
-      <c r="U64" s="16"/>
-      <c r="V64" s="17"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="14"/>
+      <c r="M64" s="14"/>
+      <c r="N64" s="14"/>
+      <c r="O64" s="14"/>
+      <c r="P64" s="14"/>
+      <c r="Q64" s="14"/>
+      <c r="R64" s="14"/>
+      <c r="S64" s="14"/>
+      <c r="T64" s="14"/>
+      <c r="U64" s="14"/>
+      <c r="V64" s="15"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -3181,7 +3206,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -3209,7 +3234,7 @@
       <c r="V66" s="1"/>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="11"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -3235,7 +3260,7 @@
       <c r="V67" s="1"/>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="11"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -3261,7 +3286,7 @@
       <c r="V68" s="1"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="11"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -3287,7 +3312,7 @@
       <c r="V69" s="1"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="11"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -3313,7 +3338,7 @@
       <c r="V70" s="1"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -3341,7 +3366,7 @@
       <c r="V71" s="1"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="13"/>
+      <c r="A72" s="18"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -3367,7 +3392,7 @@
       <c r="V72" s="1"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="14"/>
+      <c r="A73" s="19"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -3394,16 +3419,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -3412,6 +3427,16 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E76DB2-2EA3-4178-9C49-E9834DB93D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53BAE69-BAEB-44C9-9D48-BE1CC61330E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="76">
   <si>
     <t>10A1</t>
   </si>
@@ -245,6 +245,15 @@
   </si>
   <si>
     <t xml:space="preserve">Tổ </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Mã Đức Bảo-Văn</t>
+  </si>
+  <si>
+    <t>Mã Đức Bảo-CD Văn</t>
   </si>
 </sst>
 </file>
@@ -433,15 +442,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -453,6 +453,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1622,30 +1631,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E8B021-A1FC-47A8-882A-E3DB26CDCC96}">
   <dimension ref="A4:V73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="10" max="10" width="24.90625" customWidth="1"/>
+    <col min="11" max="11" width="17.90625" customWidth="1"/>
+    <col min="15" max="15" width="17.453125" customWidth="1"/>
+    <col min="17" max="17" width="19.6328125" customWidth="1"/>
+    <col min="18" max="18" width="24.36328125" customWidth="1"/>
+    <col min="19" max="19" width="23" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="15"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
+      <c r="V4" s="19"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -1711,240 +1728,560 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="16"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
         <v>6</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="18"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="19"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="15"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="19"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2010,240 +2347,560 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="16"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="16"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
+      <c r="A21" s="13"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
         <v>6</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
+      <c r="C23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="18"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="19"/>
+      <c r="A25" s="16"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
+      <c r="C25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="15"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="19"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -2309,240 +2966,560 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
+      <c r="C30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="16"/>
+      <c r="A31" s="13"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
+      <c r="C31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="16"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
+      <c r="C32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="16"/>
+      <c r="A33" s="13"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
+      <c r="C33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="16"/>
+      <c r="A34" s="13"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
+      <c r="C34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
         <v>6</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
+      <c r="C35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="18"/>
+      <c r="A36" s="15"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
+      <c r="C36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="19"/>
+      <c r="A37" s="16"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
+      <c r="C37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="14"/>
-      <c r="R40" s="14"/>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14"/>
-      <c r="V40" s="15"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="19"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -2608,240 +3585,560 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
         <v>1</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
+      <c r="C42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="16"/>
+      <c r="A43" s="13"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
+      <c r="C43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="16"/>
+      <c r="A44" s="13"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
+      <c r="C44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="16"/>
+      <c r="A45" s="13"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="16"/>
+      <c r="A46" s="13"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
+      <c r="C46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
         <v>6</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="18"/>
+      <c r="A48" s="15"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
+      <c r="C48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V48" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="19"/>
+      <c r="A49" s="16"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1"/>
+      <c r="C49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="14"/>
-      <c r="Q52" s="14"/>
-      <c r="R52" s="14"/>
-      <c r="S52" s="14"/>
-      <c r="T52" s="14"/>
-      <c r="U52" s="14"/>
-      <c r="V52" s="15"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="19"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -2907,240 +4204,560 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
+      <c r="C54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="16"/>
+      <c r="A55" s="13"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
+      <c r="C55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V55" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="16"/>
+      <c r="A56" s="13"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
+      <c r="C56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="16"/>
+      <c r="A57" s="13"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
+      <c r="C57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V57" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="16"/>
+      <c r="A58" s="13"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
+      <c r="C58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V58" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
         <v>6</v>
       </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
+      <c r="C59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="18"/>
+      <c r="A60" s="15"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1"/>
+      <c r="C60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="19"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-      <c r="S61" s="1"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1"/>
+      <c r="C61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-      <c r="N64" s="14"/>
-      <c r="O64" s="14"/>
-      <c r="P64" s="14"/>
-      <c r="Q64" s="14"/>
-      <c r="R64" s="14"/>
-      <c r="S64" s="14"/>
-      <c r="T64" s="14"/>
-      <c r="U64" s="14"/>
-      <c r="V64" s="15"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+      <c r="P64" s="18"/>
+      <c r="Q64" s="18"/>
+      <c r="R64" s="18"/>
+      <c r="S64" s="18"/>
+      <c r="T64" s="18"/>
+      <c r="U64" s="18"/>
+      <c r="V64" s="19"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -3206,219 +4823,549 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
       </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="R66" s="1"/>
-      <c r="S66" s="1"/>
-      <c r="T66" s="1"/>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1"/>
+      <c r="C66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="16"/>
+      <c r="A67" s="13"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
+      <c r="C67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="16"/>
+      <c r="A68" s="13"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1"/>
+      <c r="C68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="16"/>
+      <c r="A69" s="13"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="1"/>
-      <c r="U69" s="1"/>
-      <c r="V69" s="1"/>
+      <c r="C69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="16"/>
+      <c r="A70" s="13"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1"/>
+      <c r="C70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V70" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
         <v>6</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
-      <c r="U71" s="1"/>
-      <c r="V71" s="1"/>
+      <c r="C71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V71" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="18"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
-      <c r="T72" s="1"/>
-      <c r="U72" s="1"/>
-      <c r="V72" s="1"/>
+      <c r="C72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V72" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="19"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
-      <c r="R73" s="1"/>
-      <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
-      <c r="U73" s="1"/>
-      <c r="V73" s="1"/>
+      <c r="C73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V73" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -3427,16 +5374,6 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53BAE69-BAEB-44C9-9D48-BE1CC61330E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91747D2B-3DBC-4F0C-A233-649DBC7E0427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4081" uniqueCount="102">
   <si>
     <t>10A1</t>
   </si>
@@ -254,12 +254,91 @@
   </si>
   <si>
     <t>Mã Đức Bảo-CD Văn</t>
+  </si>
+  <si>
+    <t>Hoàng Hiếu Trình</t>
+  </si>
+  <si>
+    <t>Vi Văn Tình</t>
+  </si>
+  <si>
+    <t>11B3,11B4,11B5</t>
+  </si>
+  <si>
+    <t>Cao Thị Tố Uyên</t>
+  </si>
+  <si>
+    <t>10A3,10A4,10A5,10A6</t>
+  </si>
+  <si>
+    <t>10A1,10A2,11B3,11B4,11B5</t>
+  </si>
+  <si>
+    <t>10A7,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>10A4,10A5,10A6</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Chinh</t>
+  </si>
+  <si>
+    <t>11B3,11B4,11B5,11B6</t>
+  </si>
+  <si>
+    <t>11B1,11B2,11B3,11B4,11B5,11B6,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hằng</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7,12C1,12C2,12C3</t>
+  </si>
+  <si>
+    <t>10A4,10A5,10A6,10A7</t>
+  </si>
+  <si>
+    <t>Vi Văn Tình-Văn</t>
+  </si>
+  <si>
+    <t>Cao Thị Tố Uyên-Văn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hằng-Sử</t>
+  </si>
+  <si>
+    <t>Hoàng Hiếu Trình-Văn</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Chinh-Sử</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Chinh-CD Sử</t>
+  </si>
+  <si>
+    <t>Cao Thị Tố Uyên-CD Văn</t>
+  </si>
+  <si>
+    <t>Hoàng Hiếu Trình-CD Văn</t>
+  </si>
+  <si>
+    <t>Vi Văn Tình-CD Văn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hằng-CD Sử</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>4,5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -410,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -440,6 +519,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -743,28 +835,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:U82"/>
+  <dimension ref="A5:U124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.36328125" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.6328125" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="26.453125" customWidth="1"/>
-    <col min="10" max="10" width="6.54296875" customWidth="1"/>
-    <col min="11" max="11" width="15.90625" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
-    <col min="13" max="13" width="19.1796875" customWidth="1"/>
-    <col min="14" max="14" width="16.08984375" customWidth="1"/>
-    <col min="15" max="15" width="16.1796875" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" customWidth="1"/>
-    <col min="20" max="20" width="17.08984375" customWidth="1"/>
-    <col min="21" max="21" width="9.90625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="28.08984375"/>
+    <col min="2" max="2" customWidth="true" width="63.08984375"/>
+    <col min="3" max="3" customWidth="true" width="20.1796875"/>
+    <col min="4" max="4" customWidth="true" width="16.36328125"/>
+    <col min="5" max="5" customWidth="true" width="15.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.6328125"/>
+    <col min="7" max="7" customWidth="true" width="10.54296875"/>
+    <col min="8" max="8" customWidth="true" width="11.81640625"/>
+    <col min="9" max="9" customWidth="true" width="26.453125"/>
+    <col min="10" max="10" customWidth="true" width="6.54296875"/>
+    <col min="11" max="11" customWidth="true" width="15.90625"/>
+    <col min="12" max="12" customWidth="true" width="12.7265625"/>
+    <col min="13" max="13" customWidth="true" width="19.1796875"/>
+    <col min="14" max="14" customWidth="true" width="16.08984375"/>
+    <col min="15" max="15" customWidth="true" width="16.1796875"/>
+    <col min="16" max="16" customWidth="true" width="10.90625"/>
+    <col min="17" max="17" customWidth="true" width="13.54296875"/>
+    <col min="20" max="20" customWidth="true" width="17.08984375"/>
+    <col min="21" max="21" customWidth="true" width="9.90625"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -773,184 +865,359 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="14" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="1" t="str">
-        <f>A47</f>
+      <c r="C7" s="13" t="str">
+        <f>A$89</f>
         <v>Văn</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="13">
         <v>3</v>
       </c>
-      <c r="E7" s="1">
-        <v>315</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="str">
-        <f>A75</f>
+      <c r="E7" s="13">
+        <v>105</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="13" t="str">
+        <f>A117</f>
         <v>Thứ Năm</v>
       </c>
-      <c r="H7" s="1" t="str">
-        <f>F$47</f>
+      <c r="H7" s="13" t="str">
+        <f t="shared" ref="H7:H18" si="0">F$89</f>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1" t="str">
-        <f>A55</f>
+      <c r="C8" s="13" t="str">
+        <f>A97</f>
         <v>CD Văn</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="13">
         <v>1</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="13">
         <v>35</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1" t="str">
-        <f>A75</f>
+      <c r="F8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="13" t="str">
+        <f t="shared" ref="G8:G18" si="1">A$117</f>
         <v>Thứ Năm</v>
       </c>
-      <c r="H8" s="1" t="str">
-        <f>F$47</f>
+      <c r="H8" s="13" t="str">
+        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="A9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="13" t="str">
+        <f>A$89</f>
+        <v>Văn</v>
+      </c>
+      <c r="D9" s="13">
+        <v>3</v>
+      </c>
+      <c r="E9" s="13">
+        <v>105</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H9" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="A10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="13">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13">
+        <v>35</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H10" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="A11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="13" t="str">
+        <f>A$89</f>
+        <v>Văn</v>
+      </c>
+      <c r="D11" s="13">
+        <v>3</v>
+      </c>
+      <c r="E11" s="13">
+        <v>105</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H11" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="A12" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13">
+        <v>35</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H12" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="A13" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="13" t="str">
+        <f>A$89</f>
+        <v>Văn</v>
+      </c>
+      <c r="D13" s="13">
+        <v>3</v>
+      </c>
+      <c r="E13" s="13">
+        <v>105</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H13" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="A14" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13">
+        <v>35</v>
+      </c>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H14" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="A15" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="13" t="str">
+        <f>A$91</f>
+        <v>Sử</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2</v>
+      </c>
+      <c r="E15" s="13">
+        <v>52</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H15" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="A16" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="13" t="str">
+        <f>A$100</f>
+        <v>CD Sử</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13">
+        <v>35</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H16" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="13" t="str">
+        <f>A$91</f>
+        <v>Sử</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2</v>
+      </c>
+      <c r="E17" s="13">
+        <v>52</v>
+      </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+      <c r="G17" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H17" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="13" t="str">
+        <f>A$100</f>
+        <v>CD Sử</v>
+      </c>
+      <c r="D18" s="13">
+        <v>1</v>
+      </c>
+      <c r="E18" s="13">
+        <v>35</v>
+      </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+      <c r="G18" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="H18" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -962,28 +1229,45 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
-        <v>67</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
@@ -998,625 +1282,718 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="2">
-        <v>1</v>
-      </c>
-      <c r="C46" s="2" t="str">
-        <f t="shared" ref="C46:C62" si="0">A$81</f>
-        <v>Sáng</v>
-      </c>
-      <c r="D46" s="2">
-        <v>2</v>
-      </c>
-      <c r="E46" s="2" t="b">
-        <f>B$81</f>
-        <v>1</v>
-      </c>
-      <c r="F46" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="2">
-        <v>1</v>
-      </c>
-      <c r="C47" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D47" s="2">
-        <v>2</v>
-      </c>
-      <c r="E47" s="2" t="b">
-        <f>B$81</f>
-        <v>1</v>
-      </c>
-      <c r="F47" s="2" t="str">
-        <f>A$66</f>
-        <v>Xã Hội</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="2">
-        <v>1</v>
-      </c>
-      <c r="C48" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D48" s="2">
-        <v>2</v>
-      </c>
-      <c r="E48" s="2" t="b">
-        <f>B$81</f>
-        <v>1</v>
-      </c>
-      <c r="F48" s="2" t="str">
-        <f>A$66</f>
-        <v>Xã Hội</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="2">
-        <v>1</v>
-      </c>
-      <c r="C49" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D49" s="2">
-        <v>1</v>
-      </c>
-      <c r="E49" s="2" t="b">
-        <f t="shared" ref="E49:E62" si="1">B$82</f>
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F49" s="2" t="str">
-        <f>A$66</f>
-        <v>Xã Hội</v>
-      </c>
-      <c r="G49" s="6"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50" s="2">
-        <v>1</v>
-      </c>
-      <c r="C50" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D50" s="2">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="2" t="str">
-        <f>A$66</f>
-        <v>Xã Hội</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" s="2">
-        <v>1</v>
-      </c>
-      <c r="C51" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D51" s="2">
-        <v>1</v>
-      </c>
-      <c r="E51" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52" s="2">
-        <v>1</v>
-      </c>
-      <c r="C52" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D52" s="2">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" s="2">
-        <v>1</v>
-      </c>
-      <c r="C53" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D53" s="2">
-        <v>1</v>
-      </c>
-      <c r="E53" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" s="2">
-        <v>2</v>
-      </c>
-      <c r="C54" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D54" s="2">
-        <v>2</v>
-      </c>
-      <c r="E54" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55" s="2">
-        <v>2</v>
-      </c>
-      <c r="C55" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D55" s="2">
-        <v>2</v>
-      </c>
-      <c r="E55" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="2" t="str">
-        <f>A$66</f>
-        <v>Xã Hội</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="2">
-        <v>1</v>
-      </c>
-      <c r="C56" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D56" s="2">
-        <v>1</v>
-      </c>
-      <c r="E56" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F56" s="2" t="str">
-        <f>A$66</f>
-        <v>Xã Hội</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2">
-        <v>2</v>
-      </c>
-      <c r="C57" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D57" s="2">
-        <v>2</v>
-      </c>
-      <c r="E57" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="2" t="str">
-        <f>A$66</f>
-        <v>Xã Hội</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2">
-        <v>2</v>
-      </c>
-      <c r="C58" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D58" s="2">
-        <v>2</v>
-      </c>
-      <c r="E58" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="2" t="str">
-        <f>A$66</f>
-        <v>Xã Hội</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2">
-        <v>2</v>
-      </c>
-      <c r="C59" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D59" s="2">
-        <v>2</v>
-      </c>
-      <c r="E59" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F59" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2">
-        <v>2</v>
-      </c>
-      <c r="C60" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D60" s="2">
-        <v>2</v>
-      </c>
-      <c r="E60" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F60" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2">
-        <v>1</v>
-      </c>
-      <c r="C61" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D61" s="2">
-        <v>1</v>
-      </c>
-      <c r="E61" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F61" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2">
-        <v>1</v>
-      </c>
-      <c r="C62" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sáng</v>
-      </c>
-      <c r="D62" s="2">
-        <v>1</v>
-      </c>
-      <c r="E62" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="2" t="str">
-        <f>A$67</f>
-        <v>Tự Nhiên</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B65" s="7"/>
+      <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B88" s="2">
+        <v>1</v>
+      </c>
+      <c r="C88" s="2" t="str">
+        <f t="shared" ref="C88:C104" si="2">A$123</f>
+        <v>Sáng</v>
+      </c>
+      <c r="D88" s="2">
+        <v>2</v>
+      </c>
+      <c r="E88" s="2" t="b">
+        <f>B$123</f>
+        <v>1</v>
+      </c>
+      <c r="F88" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B89" s="2">
+        <v>1</v>
+      </c>
+      <c r="C89" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2</v>
+      </c>
+      <c r="E89" s="2" t="b">
+        <f>B$123</f>
+        <v>1</v>
+      </c>
+      <c r="F89" s="2" t="str">
+        <f>A$108</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B90" s="2">
+        <v>1</v>
+      </c>
+      <c r="C90" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D90" s="2">
+        <v>2</v>
+      </c>
+      <c r="E90" s="2" t="b">
+        <f>B$123</f>
+        <v>1</v>
+      </c>
+      <c r="F90" s="2" t="str">
+        <f>A$108</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B91" s="2">
+        <v>1</v>
+      </c>
+      <c r="C91" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D91" s="2">
+        <v>1</v>
+      </c>
+      <c r="E91" s="2" t="b">
+        <f t="shared" ref="E91:E104" si="3">B$124</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="str">
+        <f>A$108</f>
+        <v>Xã Hội</v>
+      </c>
+      <c r="G91" s="6"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B92" s="2">
+        <v>1</v>
+      </c>
+      <c r="C92" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D92" s="2">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="str">
+        <f>A$108</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B93" s="2">
+        <v>1</v>
+      </c>
+      <c r="C93" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1</v>
+      </c>
+      <c r="E93" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B94" s="2">
+        <v>1</v>
+      </c>
+      <c r="C94" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D94" s="2">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B95" s="2">
+        <v>1</v>
+      </c>
+      <c r="C95" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D95" s="2">
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B96" s="2">
+        <v>2</v>
+      </c>
+      <c r="C96" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D96" s="2">
+        <v>2</v>
+      </c>
+      <c r="E96" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B97" s="2">
+        <v>2</v>
+      </c>
+      <c r="C97" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D97" s="2">
+        <v>2</v>
+      </c>
+      <c r="E97" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="str">
+        <f>A$108</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B98" s="2">
+        <v>1</v>
+      </c>
+      <c r="C98" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D98" s="2">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="str">
+        <f>A$108</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B99" s="2">
+        <v>2</v>
+      </c>
+      <c r="C99" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D99" s="2">
+        <v>2</v>
+      </c>
+      <c r="E99" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="str">
+        <f>A$108</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B100" s="2">
+        <v>2</v>
+      </c>
+      <c r="C100" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D100" s="2">
+        <v>2</v>
+      </c>
+      <c r="E100" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="str">
+        <f>A$108</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B101" s="2">
+        <v>2</v>
+      </c>
+      <c r="C101" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D101" s="2">
+        <v>2</v>
+      </c>
+      <c r="E101" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B102" s="2">
+        <v>2</v>
+      </c>
+      <c r="C102" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D102" s="2">
+        <v>2</v>
+      </c>
+      <c r="E102" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B103" s="2">
+        <v>1</v>
+      </c>
+      <c r="C103" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D103" s="2">
+        <v>1</v>
+      </c>
+      <c r="E103" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B104" s="2">
+        <v>1</v>
+      </c>
+      <c r="C104" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Sáng</v>
+      </c>
+      <c r="D104" s="2">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="2" t="str">
+        <f>A$109</f>
+        <v>Tự Nhiên</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B107" s="7"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="11" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="12"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="10" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="5" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B71" s="7"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="B113" s="7"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B72" s="8"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="5" t="s">
+      <c r="B114" s="8"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B73" s="8"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="B115" s="8"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B74" s="8"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="5" t="s">
+      <c r="B116" s="8"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B75" s="8"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="5" t="s">
+      <c r="B117" s="8"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B76" s="8"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="5" t="s">
+      <c r="B118" s="8"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="6"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C78" s="6"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="9" t="s">
+      <c r="B119" s="8"/>
+      <c r="C119" s="6"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C120" s="6"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="2" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B122" s="15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="2" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B81" s="2" t="b">
+      <c r="B123" s="2" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="2" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="1" t="b">
+      <c r="B124" s="1" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
@@ -1632,37 +2009,37 @@
   <dimension ref="A4:V73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" width="24.90625" customWidth="1"/>
-    <col min="11" max="11" width="17.90625" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" customWidth="1"/>
-    <col min="17" max="17" width="19.6328125" customWidth="1"/>
-    <col min="18" max="18" width="24.36328125" customWidth="1"/>
-    <col min="19" max="19" width="23" customWidth="1"/>
+    <col min="10" max="10" customWidth="true" width="24.90625"/>
+    <col min="11" max="11" customWidth="true" width="17.90625"/>
+    <col min="15" max="15" customWidth="true" width="17.453125"/>
+    <col min="17" max="17" customWidth="true" width="19.6328125"/>
+    <col min="18" max="18" customWidth="true" width="24.36328125"/>
+    <col min="19" max="19" customWidth="true" width="23.0"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="V4" s="19"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="24"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -1728,32 +2105,32 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>74</v>
@@ -1762,7 +2139,7 @@
         <v>73</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>73</v>
@@ -1796,18 +2173,18 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>73</v>
@@ -1816,10 +2193,10 @@
         <v>73</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>74</v>
@@ -1831,7 +2208,7 @@
         <v>73</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>73</v>
@@ -1862,7 +2239,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
@@ -1870,13 +2247,13 @@
         <v>73</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>73</v>
@@ -1900,7 +2277,7 @@
         <v>73</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>73</v>
@@ -1909,7 +2286,7 @@
         <v>73</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>73</v>
@@ -1918,7 +2295,7 @@
         <v>73</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="U8" s="1" t="s">
         <v>73</v>
@@ -1928,7 +2305,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
@@ -1936,13 +2313,13 @@
         <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>73</v>
@@ -1969,7 +2346,7 @@
         <v>73</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>73</v>
@@ -1978,13 +2355,13 @@
         <v>73</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>73</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="U9" s="1" t="s">
         <v>73</v>
@@ -1994,7 +2371,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -2011,7 +2388,7 @@
         <v>73</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>73</v>
@@ -2026,7 +2403,7 @@
         <v>73</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>73</v>
@@ -2047,20 +2424,20 @@
         <v>73</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>73</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -2128,7 +2505,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="15"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -2194,7 +2571,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -2260,28 +2637,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="19"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="24"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2347,32 +2724,32 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>74</v>
@@ -2381,7 +2758,7 @@
         <v>73</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>73</v>
@@ -2415,18 +2792,18 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>73</v>
@@ -2435,10 +2812,10 @@
         <v>73</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>74</v>
@@ -2450,7 +2827,7 @@
         <v>73</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>73</v>
@@ -2481,7 +2858,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
@@ -2489,13 +2866,13 @@
         <v>73</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>73</v>
@@ -2519,7 +2896,7 @@
         <v>73</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>73</v>
@@ -2528,7 +2905,7 @@
         <v>73</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>73</v>
@@ -2537,7 +2914,7 @@
         <v>73</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="U20" s="1" t="s">
         <v>73</v>
@@ -2547,7 +2924,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -2555,13 +2932,13 @@
         <v>73</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>73</v>
@@ -2588,7 +2965,7 @@
         <v>73</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>73</v>
@@ -2597,13 +2974,13 @@
         <v>73</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>73</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="U21" s="1" t="s">
         <v>73</v>
@@ -2613,7 +2990,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -2630,7 +3007,7 @@
         <v>73</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>73</v>
@@ -2645,7 +3022,7 @@
         <v>73</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>73</v>
@@ -2666,20 +3043,20 @@
         <v>73</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>73</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -2747,7 +3124,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="15"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -2813,7 +3190,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -2879,28 +3256,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="19"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="24"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -2966,14 +3343,14 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>73</v>
@@ -2985,7 +3362,7 @@
         <v>73</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>73</v>
@@ -2994,13 +3371,13 @@
         <v>73</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>73</v>
@@ -3027,14 +3404,14 @@
         <v>73</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
@@ -3042,7 +3419,7 @@
         <v>73</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>73</v>
@@ -3051,7 +3428,7 @@
         <v>73</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>73</v>
@@ -3063,10 +3440,10 @@
         <v>73</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>73</v>
@@ -3093,14 +3470,14 @@
         <v>73</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -3111,7 +3488,7 @@
         <v>73</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>73</v>
@@ -3120,7 +3497,7 @@
         <v>73</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>73</v>
@@ -3135,7 +3512,7 @@
         <v>73</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>73</v>
@@ -3156,17 +3533,17 @@
         <v>73</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="U32" s="1" t="s">
         <v>73</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -3180,13 +3557,13 @@
         <v>73</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>73</v>
@@ -3201,10 +3578,10 @@
         <v>73</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>73</v>
@@ -3228,11 +3605,11 @@
         <v>73</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -3246,7 +3623,7 @@
         <v>73</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>73</v>
@@ -3255,7 +3632,7 @@
         <v>73</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>73</v>
@@ -3270,7 +3647,7 @@
         <v>73</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>73</v>
@@ -3298,7 +3675,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -3366,7 +3743,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="15"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -3432,7 +3809,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="16"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -3498,28 +3875,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="19"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="24"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -3585,7 +3962,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -3653,7 +4030,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -3719,7 +4096,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -3785,7 +4162,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -3851,7 +4228,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -3917,7 +4294,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -3985,7 +4362,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="15"/>
+      <c r="A48" s="20"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -4051,7 +4428,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="16"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -4117,28 +4494,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-      <c r="M52" s="18"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="18"/>
-      <c r="P52" s="18"/>
-      <c r="Q52" s="18"/>
-      <c r="R52" s="18"/>
-      <c r="S52" s="18"/>
-      <c r="T52" s="18"/>
-      <c r="U52" s="18"/>
-      <c r="V52" s="19"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="23"/>
+      <c r="K52" s="23"/>
+      <c r="L52" s="23"/>
+      <c r="M52" s="23"/>
+      <c r="N52" s="23"/>
+      <c r="O52" s="23"/>
+      <c r="P52" s="23"/>
+      <c r="Q52" s="23"/>
+      <c r="R52" s="23"/>
+      <c r="S52" s="23"/>
+      <c r="T52" s="23"/>
+      <c r="U52" s="23"/>
+      <c r="V52" s="24"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -4204,14 +4581,14 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>73</v>
@@ -4226,13 +4603,13 @@
         <v>73</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>73</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>73</v>
@@ -4241,7 +4618,7 @@
         <v>73</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>73</v>
@@ -4268,11 +4645,11 @@
         <v>73</v>
       </c>
       <c r="V54" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
+      <c r="A55" s="18"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -4280,7 +4657,7 @@
         <v>73</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>73</v>
@@ -4292,7 +4669,7 @@
         <v>73</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>73</v>
@@ -4301,13 +4678,13 @@
         <v>73</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>73</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>73</v>
@@ -4334,11 +4711,11 @@
         <v>73</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
+      <c r="A56" s="18"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -4349,13 +4726,13 @@
         <v>73</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>73</v>
@@ -4376,7 +4753,7 @@
         <v>73</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>73</v>
@@ -4394,7 +4771,7 @@
         <v>73</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="U56" s="1" t="s">
         <v>73</v>
@@ -4404,7 +4781,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
+      <c r="A57" s="18"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -4418,10 +4795,10 @@
         <v>73</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>73</v>
@@ -4442,7 +4819,7 @@
         <v>73</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>73</v>
@@ -4463,14 +4840,14 @@
         <v>73</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="V57" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
+      <c r="A58" s="18"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -4493,7 +4870,7 @@
         <v>73</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>73</v>
@@ -4502,7 +4879,7 @@
         <v>73</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>73</v>
@@ -4511,7 +4888,7 @@
         <v>73</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>73</v>
@@ -4536,7 +4913,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -4604,7 +4981,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="15"/>
+      <c r="A60" s="20"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -4670,7 +5047,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="16"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -4736,28 +5113,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
-      <c r="P64" s="18"/>
-      <c r="Q64" s="18"/>
-      <c r="R64" s="18"/>
-      <c r="S64" s="18"/>
-      <c r="T64" s="18"/>
-      <c r="U64" s="18"/>
-      <c r="V64" s="19"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
+      <c r="I64" s="23"/>
+      <c r="J64" s="23"/>
+      <c r="K64" s="23"/>
+      <c r="L64" s="23"/>
+      <c r="M64" s="23"/>
+      <c r="N64" s="23"/>
+      <c r="O64" s="23"/>
+      <c r="P64" s="23"/>
+      <c r="Q64" s="23"/>
+      <c r="R64" s="23"/>
+      <c r="S64" s="23"/>
+      <c r="T64" s="23"/>
+      <c r="U64" s="23"/>
+      <c r="V64" s="24"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -4823,7 +5200,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -4845,10 +5222,10 @@
         <v>73</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>73</v>
@@ -4860,7 +5237,7 @@
         <v>73</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>73</v>
@@ -4884,14 +5261,14 @@
         <v>73</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="V66" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
+      <c r="A67" s="18"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -4905,13 +5282,13 @@
         <v>73</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>73</v>
@@ -4923,10 +5300,10 @@
         <v>73</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>73</v>
@@ -4957,7 +5334,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -4971,7 +5348,7 @@
         <v>73</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>73</v>
@@ -4989,13 +5366,13 @@
         <v>73</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>73</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>75</v>
@@ -5023,7 +5400,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
+      <c r="A69" s="18"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -5040,7 +5417,7 @@
         <v>73</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>73</v>
@@ -5061,7 +5438,7 @@
         <v>73</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>75</v>
@@ -5089,7 +5466,7 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
+      <c r="A70" s="18"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -5106,7 +5483,7 @@
         <v>73</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>73</v>
@@ -5155,7 +5532,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -5223,7 +5600,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="15"/>
+      <c r="A72" s="20"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -5289,7 +5666,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="16"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91747D2B-3DBC-4F0C-A233-649DBC7E0427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92742E33-99B4-423C-8B85-0F1B3B7551B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4800" yWindow="0" windowWidth="14400" windowHeight="7810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4081" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="101">
   <si>
     <t>10A1</t>
   </si>
@@ -251,9 +251,6 @@
   </si>
   <si>
     <t>Mã Đức Bảo-Văn</t>
-  </si>
-  <si>
-    <t>Mã Đức Bảo-CD Văn</t>
   </si>
   <si>
     <t>Hoàng Hiếu Trình</t>
@@ -534,6 +531,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -545,15 +551,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -908,7 +905,7 @@
         <v>105</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G7" s="13" t="str">
         <f>A117</f>
@@ -937,7 +934,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G8" s="13" t="str">
         <f t="shared" ref="G8:G18" si="1">A$117</f>
@@ -950,10 +947,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" s="13" t="str">
         <f>A$89</f>
@@ -966,7 +963,7 @@
         <v>105</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G9" s="13" t="str">
         <f t="shared" si="1"/>
@@ -979,7 +976,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>6</v>
@@ -994,7 +991,7 @@
         <v>35</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G10" s="13" t="str">
         <f t="shared" si="1"/>
@@ -1007,10 +1004,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" s="13" t="str">
         <f>A$89</f>
@@ -1022,7 +1019,9 @@
       <c r="E11" s="13">
         <v>105</v>
       </c>
-      <c r="F11" s="13"/>
+      <c r="F11" s="13" t="s">
+        <v>99</v>
+      </c>
       <c r="G11" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
@@ -1034,10 +1033,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>55</v>
@@ -1048,7 +1047,9 @@
       <c r="E12" s="13">
         <v>35</v>
       </c>
-      <c r="F12" s="13"/>
+      <c r="F12" s="13" t="s">
+        <v>99</v>
+      </c>
       <c r="G12" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
@@ -1060,10 +1061,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>79</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>80</v>
       </c>
       <c r="C13" s="13" t="str">
         <f>A$89</f>
@@ -1087,10 +1088,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>55</v>
@@ -1113,10 +1114,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="13" t="str">
         <f>A$91</f>
@@ -1140,10 +1141,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>84</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>85</v>
       </c>
       <c r="C16" s="13" t="str">
         <f>A$100</f>
@@ -1167,10 +1168,10 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C17" s="13" t="str">
         <f>A$91</f>
@@ -1194,10 +1195,10 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="13" t="str">
         <f>A$100</f>
@@ -2018,28 +2019,28 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="24"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="20"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -2105,41 +2106,41 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="F6" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>73</v>
@@ -2173,42 +2174,42 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="18"/>
+      <c r="A7" s="21"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="H7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>73</v>
@@ -2239,45 +2240,45 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="18"/>
+      <c r="A8" s="21"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="I8" s="1" t="s">
         <v>73</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>73</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>73</v>
@@ -2286,17 +2287,17 @@
         <v>73</v>
       </c>
       <c r="Q8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="U8" s="1" t="s">
         <v>73</v>
       </c>
@@ -2305,63 +2306,63 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="R9" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>73</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="U9" s="1" t="s">
         <v>73</v>
@@ -2371,7 +2372,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="18"/>
+      <c r="A10" s="21"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -2379,7 +2380,7 @@
         <v>73</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>73</v>
@@ -2388,56 +2389,56 @@
         <v>73</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="S10" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>73</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -2505,7 +2506,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="20"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -2571,7 +2572,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="21"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -2637,28 +2638,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="24"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2724,41 +2725,41 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="F18" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>73</v>
@@ -2792,42 +2793,42 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="H19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="M19" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>73</v>
@@ -2858,45 +2859,45 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="18"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="I20" s="1" t="s">
         <v>73</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>73</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>73</v>
@@ -2905,17 +2906,17 @@
         <v>73</v>
       </c>
       <c r="Q20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T20" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="R20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="U20" s="1" t="s">
         <v>73</v>
       </c>
@@ -2924,63 +2925,63 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="R21" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>73</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="U21" s="1" t="s">
         <v>73</v>
@@ -2990,7 +2991,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -2998,7 +2999,7 @@
         <v>73</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>73</v>
@@ -3007,56 +3008,56 @@
         <v>73</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="S22" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>73</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -3124,7 +3125,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="20"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -3190,7 +3191,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="21"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -3256,28 +3257,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="24"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="20"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -3343,75 +3344,75 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="U30" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="18"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
@@ -3419,55 +3420,55 @@
         <v>73</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T31" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="U31" s="1" t="s">
         <v>93</v>
@@ -3477,7 +3478,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -3485,65 +3486,65 @@
         <v>73</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U32" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="18"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -3551,37 +3552,37 @@
         <v>73</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="J33" s="1" t="s">
         <v>73</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>73</v>
@@ -3590,7 +3591,7 @@
         <v>73</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>73</v>
@@ -3605,11 +3606,11 @@
         <v>73</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -3623,7 +3624,7 @@
         <v>73</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>73</v>
@@ -3632,7 +3633,7 @@
         <v>73</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>73</v>
@@ -3641,16 +3642,16 @@
         <v>73</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>73</v>
@@ -3659,10 +3660,10 @@
         <v>73</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="T34" s="1" t="s">
         <v>73</v>
@@ -3675,7 +3676,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -3743,7 +3744,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="20"/>
+      <c r="A36" s="23"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -3809,7 +3810,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="21"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -3875,28 +3876,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="23"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="23"/>
-      <c r="U40" s="23"/>
-      <c r="V40" s="24"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="20"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -3962,7 +3963,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -4030,7 +4031,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="18"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -4096,7 +4097,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="18"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -4162,7 +4163,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="18"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -4228,7 +4229,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="18"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -4294,7 +4295,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -4362,7 +4363,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="20"/>
+      <c r="A48" s="23"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -4428,7 +4429,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="21"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -4494,28 +4495,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="23"/>
-      <c r="R52" s="23"/>
-      <c r="S52" s="23"/>
-      <c r="T52" s="23"/>
-      <c r="U52" s="23"/>
-      <c r="V52" s="24"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="19"/>
+      <c r="T52" s="19"/>
+      <c r="U52" s="19"/>
+      <c r="V52" s="20"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -4581,75 +4582,75 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U54" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="V54" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="18"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -4657,65 +4658,65 @@
         <v>73</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="U55" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="V55" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="18"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -4726,62 +4727,62 @@
         <v>73</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V56" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="V56" s="1" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="18"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -4795,16 +4796,16 @@
         <v>73</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>73</v>
@@ -4813,16 +4814,16 @@
         <v>73</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>73</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>73</v>
@@ -4831,7 +4832,7 @@
         <v>73</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>73</v>
@@ -4840,14 +4841,14 @@
         <v>73</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="18"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -4870,7 +4871,7 @@
         <v>73</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>73</v>
@@ -4879,28 +4880,28 @@
         <v>73</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>73</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>73</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="T58" s="1" t="s">
         <v>73</v>
@@ -4913,7 +4914,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="19" t="s">
+      <c r="A59" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -4981,7 +4982,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="20"/>
+      <c r="A60" s="23"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -5047,7 +5048,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="21"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -5113,28 +5114,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="23"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="23"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="23"/>
-      <c r="Q64" s="23"/>
-      <c r="R64" s="23"/>
-      <c r="S64" s="23"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="23"/>
-      <c r="V64" s="24"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="19"/>
+      <c r="U64" s="19"/>
+      <c r="V64" s="20"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -5200,7 +5201,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -5216,59 +5217,59 @@
         <v>73</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V66" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M66" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="18"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -5282,13 +5283,13 @@
         <v>73</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>73</v>
@@ -5300,10 +5301,10 @@
         <v>73</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>73</v>
@@ -5321,20 +5322,20 @@
         <v>73</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="T67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="18"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -5348,16 +5349,16 @@
         <v>73</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>73</v>
@@ -5366,22 +5367,22 @@
         <v>73</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>73</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R68" s="1" t="s">
         <v>73</v>
@@ -5400,7 +5401,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="18"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -5417,7 +5418,7 @@
         <v>73</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>73</v>
@@ -5435,19 +5436,19 @@
         <v>73</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>73</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>73</v>
@@ -5466,7 +5467,7 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="18"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -5483,13 +5484,13 @@
         <v>73</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>73</v>
@@ -5504,7 +5505,7 @@
         <v>73</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="O70" s="1" t="s">
         <v>73</v>
@@ -5516,7 +5517,7 @@
         <v>73</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>73</v>
@@ -5532,7 +5533,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="19" t="s">
+      <c r="A71" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -5600,7 +5601,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="20"/>
+      <c r="A72" s="23"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -5666,7 +5667,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="21"/>
+      <c r="A73" s="24"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -5733,16 +5734,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -5751,6 +5742,16 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92742E33-99B4-423C-8B85-0F1B3B7551B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6627D37E-F0CC-4B05-8E15-C0F49847478D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="0" windowWidth="14400" windowHeight="7810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="108">
   <si>
     <t>10A1</t>
   </si>
@@ -127,9 +127,6 @@
     <t>Số tiết trên năm</t>
   </si>
   <si>
-    <t>Tiết học tránh dạy</t>
-  </si>
-  <si>
     <t>Các lớp hiện có</t>
   </si>
   <si>
@@ -319,23 +316,46 @@
     <t>Hoàng Hiếu Trình-CD Văn</t>
   </si>
   <si>
+    <t>Nguyễn Thị Hằng-CD Sử</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T2)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T3)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T4)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T5)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T6)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T7)</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
     <t>Vi Văn Tình-CD Văn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Hằng-CD Sử</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>4,5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -531,15 +551,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -551,6 +562,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -835,33 +855,33 @@
   <dimension ref="A5:U124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="28.08984375"/>
-    <col min="2" max="2" customWidth="true" width="63.08984375"/>
-    <col min="3" max="3" customWidth="true" width="20.1796875"/>
-    <col min="4" max="4" customWidth="true" width="16.36328125"/>
-    <col min="5" max="5" customWidth="true" width="15.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.6328125"/>
-    <col min="7" max="7" customWidth="true" width="10.54296875"/>
-    <col min="8" max="8" customWidth="true" width="11.81640625"/>
-    <col min="9" max="9" customWidth="true" width="26.453125"/>
-    <col min="10" max="10" customWidth="true" width="6.54296875"/>
-    <col min="11" max="11" customWidth="true" width="15.90625"/>
-    <col min="12" max="12" customWidth="true" width="12.7265625"/>
-    <col min="13" max="13" customWidth="true" width="19.1796875"/>
-    <col min="14" max="14" customWidth="true" width="16.08984375"/>
-    <col min="15" max="15" customWidth="true" width="16.1796875"/>
-    <col min="16" max="16" customWidth="true" width="10.90625"/>
-    <col min="17" max="17" customWidth="true" width="13.54296875"/>
-    <col min="20" max="20" customWidth="true" width="17.08984375"/>
-    <col min="21" max="21" customWidth="true" width="9.90625"/>
+    <col min="1" max="1" width="28.08984375" customWidth="1"/>
+    <col min="2" max="2" width="63.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" customWidth="1"/>
+    <col min="8" max="8" width="20.36328125" customWidth="1"/>
+    <col min="9" max="9" width="26.453125" customWidth="1"/>
+    <col min="10" max="10" width="22.81640625" customWidth="1"/>
+    <col min="11" max="11" width="23.36328125" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="13" max="13" width="19.1796875" customWidth="1"/>
+    <col min="14" max="14" width="16.08984375" customWidth="1"/>
+    <col min="15" max="15" width="16.1796875" customWidth="1"/>
+    <col min="16" max="16" width="10.90625" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" customWidth="1"/>
+    <col min="20" max="20" width="17.08984375" customWidth="1"/>
+    <col min="21" max="21" width="9.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>28</v>
       </c>
@@ -878,21 +898,36 @@
         <v>32</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="C7" s="13" t="str">
         <f>A$89</f>
@@ -905,20 +940,33 @@
         <v>105</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="G7" s="13" t="str">
+        <v>97</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L7" s="13" t="str">
         <f>A117</f>
         <v>Thứ Năm</v>
       </c>
-      <c r="H7" s="13" t="str">
-        <f t="shared" ref="H7:H18" si="0">F$89</f>
+      <c r="M7" s="13" t="str">
+        <f t="shared" ref="M7:M18" si="0">F$89</f>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>12</v>
@@ -934,23 +982,36 @@
         <v>35</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="G8" s="13" t="str">
-        <f t="shared" ref="G8:G18" si="1">A$117</f>
+        <v>97</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8" s="13" t="str">
+        <f t="shared" ref="L8:L18" si="1">A$117</f>
         <v>Thứ Năm</v>
       </c>
-      <c r="H8" s="13" t="str">
+      <c r="M8" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="13" t="str">
         <f>A$89</f>
@@ -963,26 +1024,39 @@
         <v>105</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="13" t="str">
+        <v>98</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H9" s="13" t="str">
+      <c r="M9" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="13">
         <v>1</v>
@@ -990,24 +1064,27 @@
       <c r="E10" s="13">
         <v>35</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="13" t="str">
+      <c r="F10" s="13"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H10" s="13" t="str">
+      <c r="M10" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" s="13" t="str">
         <f>A$89</f>
@@ -1019,27 +1096,30 @@
       <c r="E11" s="13">
         <v>105</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="13" t="str">
+      <c r="F11" s="13"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H11" s="13" t="str">
+      <c r="M11" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="C12" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="13">
         <v>1</v>
@@ -1047,24 +1127,27 @@
       <c r="E12" s="13">
         <v>35</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="G12" s="13" t="str">
+      <c r="F12" s="13"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H12" s="13" t="str">
+      <c r="M12" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>78</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>79</v>
       </c>
       <c r="C13" s="13" t="str">
         <f>A$89</f>
@@ -1077,24 +1160,29 @@
         <v>105</v>
       </c>
       <c r="F13" s="13"/>
-      <c r="G13" s="13" t="str">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H13" s="13" t="str">
+      <c r="M13" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="13">
         <v>1</v>
@@ -1103,21 +1191,26 @@
         <v>35</v>
       </c>
       <c r="F14" s="13"/>
-      <c r="G14" s="13" t="str">
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H14" s="13" t="str">
+      <c r="M14" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="13" t="str">
         <f>A$91</f>
@@ -1130,21 +1223,26 @@
         <v>52</v>
       </c>
       <c r="F15" s="13"/>
-      <c r="G15" s="13" t="str">
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H15" s="13" t="str">
+      <c r="M15" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>83</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>84</v>
       </c>
       <c r="C16" s="13" t="str">
         <f>A$100</f>
@@ -1157,21 +1255,26 @@
         <v>35</v>
       </c>
       <c r="F16" s="13"/>
-      <c r="G16" s="13" t="str">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H16" s="13" t="str">
+      <c r="M16" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="C17" s="13" t="str">
         <f>A$91</f>
@@ -1184,21 +1287,26 @@
         <v>52</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="13" t="str">
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H17" s="13" t="str">
+      <c r="M17" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="13" t="str">
         <f>A$100</f>
@@ -1211,11 +1319,16 @@
         <v>35</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="13" t="str">
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thứ Năm</v>
       </c>
-      <c r="H18" s="13" t="str">
+      <c r="M18" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
@@ -1229,6 +1342,11 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
@@ -1239,6 +1357,11 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
@@ -1249,6 +1372,11 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
@@ -1259,6 +1387,11 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
@@ -1269,10 +1402,11 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -1291,6 +1425,11 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
@@ -1301,6 +1440,11 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
@@ -1311,6 +1455,11 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
@@ -1321,6 +1470,11 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
@@ -1331,6 +1485,11 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
@@ -1341,6 +1500,11 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
@@ -1351,15 +1515,20 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -1472,32 +1641,32 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B87" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B87" s="16" t="s">
+      <c r="C87" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="D87" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="16" t="s">
+      <c r="E87" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E87" s="15" t="s">
+      <c r="F87" s="16" t="s">
         <v>42</v>
-      </c>
-      <c r="F87" s="16" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B88" s="2">
         <v>1</v>
@@ -1520,7 +1689,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B89" s="2">
         <v>1</v>
@@ -1543,7 +1712,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B90" s="2">
         <v>1</v>
@@ -1566,7 +1735,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B91" s="2">
         <v>1</v>
@@ -1590,7 +1759,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B92" s="2">
         <v>1</v>
@@ -1613,7 +1782,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B93" s="2">
         <v>1</v>
@@ -1636,7 +1805,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B94" s="2">
         <v>1</v>
@@ -1659,7 +1828,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B95" s="2">
         <v>1</v>
@@ -1682,7 +1851,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B96" s="2">
         <v>2</v>
@@ -1705,7 +1874,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B97" s="2">
         <v>2</v>
@@ -1728,7 +1897,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B98" s="2">
         <v>1</v>
@@ -1751,7 +1920,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B99" s="2">
         <v>2</v>
@@ -1774,7 +1943,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B100" s="2">
         <v>2</v>
@@ -1797,7 +1966,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B101" s="2">
         <v>2</v>
@@ -1820,7 +1989,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B102" s="2">
         <v>2</v>
@@ -1843,7 +2012,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B103" s="2">
         <v>1</v>
@@ -1866,7 +2035,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B104" s="2">
         <v>1</v>
@@ -1889,12 +2058,12 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="6"/>
@@ -1902,12 +2071,12 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -1919,12 +2088,12 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B113" s="7"/>
     </row>
@@ -1970,15 +2139,15 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B122" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="B122" s="15" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
@@ -2010,37 +2179,37 @@
   <dimension ref="A4:V73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" customWidth="true" width="24.90625"/>
-    <col min="11" max="11" customWidth="true" width="17.90625"/>
-    <col min="15" max="15" customWidth="true" width="17.453125"/>
-    <col min="17" max="17" customWidth="true" width="19.6328125"/>
-    <col min="18" max="18" customWidth="true" width="24.36328125"/>
-    <col min="19" max="19" customWidth="true" width="23.0"/>
+    <col min="10" max="10" width="24.90625" customWidth="1"/>
+    <col min="11" max="11" width="17.90625" customWidth="1"/>
+    <col min="15" max="15" width="17.453125" customWidth="1"/>
+    <col min="17" max="17" width="19.6328125" customWidth="1"/>
+    <col min="18" max="18" width="24.36328125" customWidth="1"/>
+    <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="20"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="24"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -2106,560 +2275,560 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="21"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="K8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="R8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="U8" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="21"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="K9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="S9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="21"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="L10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="T10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="23"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="24"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="20"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="24"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2725,560 +2894,560 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="21"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="M19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="21"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="G20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="K20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="R20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T20" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="U20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="21"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="K21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="S21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="21"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="L22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S22" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="T22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="23"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="24"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="20"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="24"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -3344,560 +3513,560 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="21"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="U31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="V31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="21"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F32" s="1" t="s">
+      <c r="I32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U32" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U32" s="1" t="s">
+      <c r="V32" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="V32" s="1" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="21"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="I33" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="21"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="P34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
         <v>6</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="23"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="24"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="20"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="24"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -3963,560 +4132,560 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="21"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="21"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="21"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="21"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
         <v>6</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="23"/>
+      <c r="A48" s="20"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="24"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19"/>
-      <c r="O52" s="19"/>
-      <c r="P52" s="19"/>
-      <c r="Q52" s="19"/>
-      <c r="R52" s="19"/>
-      <c r="S52" s="19"/>
-      <c r="T52" s="19"/>
-      <c r="U52" s="19"/>
-      <c r="V52" s="20"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="23"/>
+      <c r="K52" s="23"/>
+      <c r="L52" s="23"/>
+      <c r="M52" s="23"/>
+      <c r="N52" s="23"/>
+      <c r="O52" s="23"/>
+      <c r="P52" s="23"/>
+      <c r="Q52" s="23"/>
+      <c r="R52" s="23"/>
+      <c r="S52" s="23"/>
+      <c r="T52" s="23"/>
+      <c r="U52" s="23"/>
+      <c r="V52" s="24"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -4582,560 +4751,560 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U54" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="V54" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="21"/>
+      <c r="A55" s="18"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U55" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="21"/>
+      <c r="A56" s="18"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O56" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="P56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="21"/>
+      <c r="A57" s="18"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O57" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I57" s="1" t="s">
+      <c r="P57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="V57" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="21"/>
+      <c r="A58" s="18"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q58" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R58" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V58" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="V58" s="1" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
         <v>6</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V59" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="23"/>
+      <c r="A60" s="20"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="24"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V61" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="19"/>
-      <c r="M64" s="19"/>
-      <c r="N64" s="19"/>
-      <c r="O64" s="19"/>
-      <c r="P64" s="19"/>
-      <c r="Q64" s="19"/>
-      <c r="R64" s="19"/>
-      <c r="S64" s="19"/>
-      <c r="T64" s="19"/>
-      <c r="U64" s="19"/>
-      <c r="V64" s="20"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
+      <c r="I64" s="23"/>
+      <c r="J64" s="23"/>
+      <c r="K64" s="23"/>
+      <c r="L64" s="23"/>
+      <c r="M64" s="23"/>
+      <c r="N64" s="23"/>
+      <c r="O64" s="23"/>
+      <c r="P64" s="23"/>
+      <c r="Q64" s="23"/>
+      <c r="R64" s="23"/>
+      <c r="S64" s="23"/>
+      <c r="T64" s="23"/>
+      <c r="U64" s="23"/>
+      <c r="V64" s="24"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -5201,539 +5370,549 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q66" s="1" t="s">
         <v>73</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="21"/>
+      <c r="A67" s="18"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="21"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R68" s="1" t="s">
         <v>73</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="21"/>
+      <c r="A69" s="18"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="21"/>
+      <c r="A70" s="18"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="22" t="s">
+      <c r="A71" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
         <v>6</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="23"/>
+      <c r="A72" s="20"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="24"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -5742,16 +5921,6 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6627D37E-F0CC-4B05-8E15-C0F49847478D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6B1EB5-25AE-4BB2-9D19-D0E02F79F37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="107">
   <si>
     <t>10A1</t>
   </si>
@@ -310,15 +310,9 @@
     <t>Hoàng Văn Chinh-CD Sử</t>
   </si>
   <si>
-    <t>Cao Thị Tố Uyên-CD Văn</t>
-  </si>
-  <si>
     <t>Hoàng Hiếu Trình-CD Văn</t>
   </si>
   <si>
-    <t>Nguyễn Thị Hằng-CD Sử</t>
-  </si>
-  <si>
     <t>1,2</t>
   </si>
   <si>
@@ -350,12 +344,16 @@
   </si>
   <si>
     <t>Vi Văn Tình-CD Văn</t>
+  </si>
+  <si>
+    <t>Mã Đức Bảo-CD Văn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -551,6 +549,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -562,15 +569,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -855,25 +853,25 @@
   <dimension ref="A5:U124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" customWidth="1"/>
-    <col min="2" max="2" width="63.08984375" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.36328125" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="21.54296875" customWidth="1"/>
-    <col min="8" max="8" width="20.36328125" customWidth="1"/>
-    <col min="9" max="9" width="26.453125" customWidth="1"/>
-    <col min="10" max="10" width="22.81640625" customWidth="1"/>
-    <col min="11" max="11" width="23.36328125" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
-    <col min="13" max="13" width="19.1796875" customWidth="1"/>
-    <col min="14" max="14" width="16.08984375" customWidth="1"/>
-    <col min="15" max="15" width="16.1796875" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" customWidth="1"/>
-    <col min="20" max="20" width="17.08984375" customWidth="1"/>
-    <col min="21" max="21" width="9.90625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="28.08984375"/>
+    <col min="2" max="2" customWidth="true" width="63.08984375"/>
+    <col min="3" max="3" customWidth="true" width="20.1796875"/>
+    <col min="4" max="4" customWidth="true" width="16.36328125"/>
+    <col min="5" max="5" customWidth="true" width="15.26953125"/>
+    <col min="6" max="6" customWidth="true" width="22.7265625"/>
+    <col min="7" max="7" customWidth="true" width="21.54296875"/>
+    <col min="8" max="8" customWidth="true" width="20.36328125"/>
+    <col min="9" max="9" customWidth="true" width="26.453125"/>
+    <col min="10" max="10" customWidth="true" width="22.81640625"/>
+    <col min="11" max="11" customWidth="true" width="23.36328125"/>
+    <col min="12" max="12" customWidth="true" width="12.7265625"/>
+    <col min="13" max="13" customWidth="true" width="19.1796875"/>
+    <col min="14" max="14" customWidth="true" width="16.08984375"/>
+    <col min="15" max="15" customWidth="true" width="16.1796875"/>
+    <col min="16" max="16" customWidth="true" width="10.90625"/>
+    <col min="17" max="17" customWidth="true" width="13.54296875"/>
+    <col min="20" max="20" customWidth="true" width="17.08984375"/>
+    <col min="21" max="21" customWidth="true" width="9.90625"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -898,22 +896,22 @@
         <v>32</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="I6" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="J6" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="K6" s="16" t="s">
         <v>102</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>104</v>
       </c>
       <c r="L6" s="14" t="s">
         <v>62</v>
@@ -939,22 +937,12 @@
       <c r="E7" s="13">
         <v>105</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
       <c r="L7" s="13" t="str">
         <f>A117</f>
         <v>Thứ Năm</v>
@@ -982,20 +970,20 @@
         <v>35</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L8" s="13" t="str">
         <f t="shared" ref="L8:L18" si="1">A$117</f>
@@ -1024,20 +1012,20 @@
         <v>105</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L9" s="13" t="str">
         <f t="shared" si="1"/>
@@ -2179,37 +2167,37 @@
   <dimension ref="A4:V73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" width="24.90625" customWidth="1"/>
-    <col min="11" max="11" width="17.90625" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" customWidth="1"/>
-    <col min="17" max="17" width="19.6328125" customWidth="1"/>
-    <col min="18" max="18" width="24.36328125" customWidth="1"/>
-    <col min="19" max="19" width="23" customWidth="1"/>
+    <col min="10" max="10" customWidth="true" width="24.90625"/>
+    <col min="11" max="11" customWidth="true" width="17.90625"/>
+    <col min="15" max="15" customWidth="true" width="17.453125"/>
+    <col min="17" max="17" customWidth="true" width="19.6328125"/>
+    <col min="18" max="18" customWidth="true" width="24.36328125"/>
+    <col min="19" max="19" customWidth="true" width="23.0"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="24"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="20"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -2275,17 +2263,17 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>89</v>
@@ -2294,7 +2282,7 @@
         <v>72</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>72</v>
@@ -2303,10 +2291,10 @@
         <v>91</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>72</v>
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="18"/>
+      <c r="A7" s="21"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
@@ -2351,7 +2339,7 @@
         <v>88</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>89</v>
@@ -2363,7 +2351,7 @@
         <v>72</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>91</v>
@@ -2372,10 +2360,10 @@
         <v>72</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>72</v>
@@ -2409,7 +2397,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="18"/>
+      <c r="A8" s="21"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
@@ -2417,7 +2405,7 @@
         <v>72</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>72</v>
@@ -2426,7 +2414,7 @@
         <v>89</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>72</v>
@@ -2441,10 +2429,10 @@
         <v>72</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>72</v>
@@ -2456,7 +2444,7 @@
         <v>72</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>72</v>
@@ -2475,7 +2463,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
@@ -2483,7 +2471,7 @@
         <v>72</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>72</v>
@@ -2495,25 +2483,25 @@
         <v>72</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="L9" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>72</v>
@@ -2525,7 +2513,7 @@
         <v>72</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>72</v>
@@ -2541,7 +2529,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="18"/>
+      <c r="A10" s="21"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -2570,31 +2558,31 @@
         <v>72</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="P10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>72</v>
@@ -2607,7 +2595,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -2647,10 +2635,10 @@
         <v>72</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>72</v>
@@ -2675,7 +2663,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="20"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -2741,7 +2729,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="21"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -2807,28 +2795,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="24"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2894,17 +2882,17 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>89</v>
@@ -2913,7 +2901,7 @@
         <v>72</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>72</v>
@@ -2922,10 +2910,10 @@
         <v>91</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>72</v>
@@ -2962,7 +2950,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
@@ -2970,7 +2958,7 @@
         <v>88</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>89</v>
@@ -2982,7 +2970,7 @@
         <v>72</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>91</v>
@@ -2991,10 +2979,10 @@
         <v>72</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>72</v>
@@ -3028,7 +3016,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="18"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
@@ -3036,7 +3024,7 @@
         <v>72</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>72</v>
@@ -3045,7 +3033,7 @@
         <v>89</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>72</v>
@@ -3060,10 +3048,10 @@
         <v>72</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>72</v>
@@ -3075,7 +3063,7 @@
         <v>72</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>72</v>
@@ -3094,7 +3082,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -3102,7 +3090,7 @@
         <v>72</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>72</v>
@@ -3114,25 +3102,25 @@
         <v>72</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>72</v>
@@ -3144,7 +3132,7 @@
         <v>72</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>72</v>
@@ -3160,7 +3148,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -3189,31 +3177,31 @@
         <v>72</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="P22" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>72</v>
@@ -3226,7 +3214,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -3266,7 +3254,7 @@
         <v>72</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>72</v>
@@ -3294,7 +3282,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="20"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -3360,7 +3348,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="21"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -3426,28 +3414,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="24"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="20"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -3513,20 +3501,20 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>72</v>
@@ -3541,22 +3529,22 @@
         <v>72</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>72</v>
@@ -3581,21 +3569,21 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="18"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>89</v>
@@ -3607,13 +3595,13 @@
         <v>72</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>72</v>
@@ -3647,7 +3635,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -3655,10 +3643,10 @@
         <v>72</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>72</v>
@@ -3670,7 +3658,7 @@
         <v>89</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>72</v>
@@ -3682,7 +3670,7 @@
         <v>72</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>72</v>
@@ -3713,7 +3701,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="18"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -3721,13 +3709,13 @@
         <v>72</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>72</v>
@@ -3736,7 +3724,7 @@
         <v>89</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>72</v>
@@ -3745,13 +3733,13 @@
         <v>72</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>72</v>
@@ -3763,7 +3751,7 @@
         <v>72</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>72</v>
@@ -3779,7 +3767,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -3793,7 +3781,7 @@
         <v>72</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>72</v>
@@ -3802,25 +3790,25 @@
         <v>72</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>72</v>
@@ -3832,7 +3820,7 @@
         <v>72</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="T34" s="1" t="s">
         <v>72</v>
@@ -3845,7 +3833,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -3913,7 +3901,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="20"/>
+      <c r="A36" s="23"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -3979,7 +3967,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="21"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -4045,28 +4033,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="23"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="23"/>
-      <c r="U40" s="23"/>
-      <c r="V40" s="24"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="20"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -4132,7 +4120,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -4200,7 +4188,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="18"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -4266,7 +4254,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="18"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -4332,7 +4320,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="18"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -4398,7 +4386,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="18"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -4464,7 +4452,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -4532,7 +4520,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="20"/>
+      <c r="A48" s="23"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -4598,7 +4586,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="21"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -4664,28 +4652,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="23"/>
-      <c r="R52" s="23"/>
-      <c r="S52" s="23"/>
-      <c r="T52" s="23"/>
-      <c r="U52" s="23"/>
-      <c r="V52" s="24"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="19"/>
+      <c r="T52" s="19"/>
+      <c r="U52" s="19"/>
+      <c r="V52" s="20"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -4751,20 +4739,20 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>72</v>
@@ -4779,7 +4767,7 @@
         <v>72</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>72</v>
@@ -4794,7 +4782,7 @@
         <v>72</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>72</v>
@@ -4819,7 +4807,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="18"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -4827,13 +4815,13 @@
         <v>72</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>72</v>
@@ -4885,7 +4873,7 @@
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="18"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -4896,19 +4884,19 @@
         <v>72</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>72</v>
@@ -4951,7 +4939,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="18"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -4965,10 +4953,10 @@
         <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>72</v>
@@ -4983,7 +4971,7 @@
         <v>72</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>72</v>
@@ -4992,16 +4980,16 @@
         <v>88</v>
       </c>
       <c r="O57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q57" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="R57" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>72</v>
@@ -5017,7 +5005,7 @@
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="18"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -5040,7 +5028,7 @@
         <v>72</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>72</v>
@@ -5049,7 +5037,7 @@
         <v>72</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>72</v>
@@ -5070,7 +5058,7 @@
         <v>72</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="T58" s="1" t="s">
         <v>72</v>
@@ -5083,7 +5071,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="19" t="s">
+      <c r="A59" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -5151,7 +5139,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="20"/>
+      <c r="A60" s="23"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -5217,7 +5205,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="21"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -5283,28 +5271,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="23"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="23"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="23"/>
-      <c r="Q64" s="23"/>
-      <c r="R64" s="23"/>
-      <c r="S64" s="23"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="23"/>
-      <c r="V64" s="24"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="19"/>
+      <c r="U64" s="19"/>
+      <c r="V64" s="20"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -5370,7 +5358,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -5392,10 +5380,10 @@
         <v>72</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>72</v>
@@ -5407,10 +5395,10 @@
         <v>72</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>72</v>
@@ -5438,7 +5426,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="18"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -5452,13 +5440,13 @@
         <v>72</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>72</v>
@@ -5473,10 +5461,10 @@
         <v>72</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="O67" s="1" t="s">
         <v>72</v>
@@ -5504,7 +5492,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="18"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -5518,7 +5506,7 @@
         <v>72</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>72</v>
@@ -5539,10 +5527,10 @@
         <v>72</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>93</v>
@@ -5570,7 +5558,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="18"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -5587,7 +5575,7 @@
         <v>72</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>72</v>
@@ -5605,10 +5593,10 @@
         <v>72</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>93</v>
@@ -5636,7 +5624,7 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="18"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -5653,13 +5641,13 @@
         <v>72</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>72</v>
@@ -5702,7 +5690,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="19" t="s">
+      <c r="A71" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -5770,7 +5758,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="20"/>
+      <c r="A72" s="23"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -5836,7 +5824,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="21"/>
+      <c r="A73" s="24"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -5903,16 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -5921,6 +5899,16 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6B1EB5-25AE-4BB2-9D19-D0E02F79F37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95676F4-FDF9-4DED-9845-F83B0BC78DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4087" uniqueCount="108">
   <si>
     <t>10A1</t>
   </si>
@@ -337,9 +337,6 @@
     <t>Tiết học tránh dạy (T7)</t>
   </si>
   <si>
-    <t>3,4</t>
-  </si>
-  <si>
     <t>2,3</t>
   </si>
   <si>
@@ -347,6 +344,12 @@
   </si>
   <si>
     <t>Mã Đức Bảo-CD Văn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hằng-CD Sử</t>
+  </si>
+  <si>
+    <t>Cao Thị Tố Uyên-CD Văn</t>
   </si>
 </sst>
 </file>
@@ -549,15 +552,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -569,6 +563,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -969,22 +972,12 @@
       <c r="E8" s="13">
         <v>35</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>96</v>
-      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
       <c r="L8" s="13" t="str">
         <f t="shared" ref="L8:L18" si="1">A$117</f>
         <v>Thứ Năm</v>
@@ -1022,7 +1015,7 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>95</v>
@@ -2176,28 +2169,28 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="20"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="24"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -2263,7 +2256,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
@@ -2294,7 +2287,7 @@
         <v>92</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>72</v>
@@ -2331,7 +2324,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="21"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
@@ -2357,7 +2350,7 @@
         <v>91</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>92</v>
@@ -2397,7 +2390,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
@@ -2423,7 +2416,7 @@
         <v>72</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>72</v>
@@ -2438,7 +2431,7 @@
         <v>72</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>72</v>
@@ -2463,7 +2456,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="21"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
@@ -2492,7 +2485,7 @@
         <v>72</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>88</v>
@@ -2504,7 +2497,7 @@
         <v>72</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>72</v>
@@ -2529,7 +2522,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="21"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -2570,17 +2563,17 @@
         <v>92</v>
       </c>
       <c r="O10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="S10" s="1" t="s">
         <v>72</v>
       </c>
@@ -2595,7 +2588,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -2635,10 +2628,10 @@
         <v>72</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>72</v>
@@ -2663,7 +2656,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="23"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -2729,7 +2722,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="24"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -2795,28 +2788,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="20"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="24"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2882,7 +2875,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
@@ -2913,7 +2906,7 @@
         <v>92</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>72</v>
@@ -2950,7 +2943,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="21"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
@@ -2961,11 +2954,11 @@
         <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="G19" s="1" t="s">
         <v>72</v>
       </c>
@@ -2973,10 +2966,10 @@
         <v>72</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>92</v>
@@ -3006,7 +2999,7 @@
         <v>72</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>72</v>
@@ -3016,7 +3009,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="21"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
@@ -3027,14 +3020,14 @@
         <v>72</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="H20" s="1" t="s">
         <v>72</v>
       </c>
@@ -3042,7 +3035,7 @@
         <v>72</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>72</v>
@@ -3057,7 +3050,7 @@
         <v>72</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>72</v>
@@ -3082,7 +3075,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="21"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -3096,13 +3089,13 @@
         <v>72</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="H21" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>72</v>
@@ -3111,7 +3104,7 @@
         <v>72</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>88</v>
@@ -3129,7 +3122,7 @@
         <v>72</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>72</v>
@@ -3148,7 +3141,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="21"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -3165,13 +3158,13 @@
         <v>72</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="I22" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>72</v>
@@ -3189,14 +3182,14 @@
         <v>92</v>
       </c>
       <c r="O22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P22" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="R22" s="1" t="s">
         <v>72</v>
       </c>
@@ -3214,7 +3207,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -3254,7 +3247,7 @@
         <v>72</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>72</v>
@@ -3282,7 +3275,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="23"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -3348,7 +3341,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="24"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -3414,28 +3407,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="20"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="24"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -3501,7 +3494,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
@@ -3520,10 +3513,10 @@
         <v>72</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>72</v>
@@ -3559,25 +3552,25 @@
         <v>72</v>
       </c>
       <c r="T30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="U30" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="V30" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="21"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>72</v>
@@ -3586,20 +3579,20 @@
         <v>90</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="I31" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="L31" s="1" t="s">
         <v>72</v>
       </c>
@@ -3625,17 +3618,17 @@
         <v>72</v>
       </c>
       <c r="T31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="U31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="V31" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="21"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -3643,34 +3636,34 @@
         <v>72</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="M32" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>72</v>
@@ -3685,7 +3678,7 @@
         <v>72</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>72</v>
@@ -3694,14 +3687,14 @@
         <v>72</v>
       </c>
       <c r="U32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V32" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="V32" s="1" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="21"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -3709,35 +3702,35 @@
         <v>72</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="N33" s="1" t="s">
         <v>72</v>
       </c>
@@ -3751,7 +3744,7 @@
         <v>72</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>72</v>
@@ -3763,11 +3756,11 @@
         <v>72</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="21"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -3796,32 +3789,32 @@
         <v>72</v>
       </c>
       <c r="K34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S34" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="T34" s="1" t="s">
         <v>72</v>
       </c>
@@ -3833,7 +3826,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -3901,7 +3894,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="23"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -3967,7 +3960,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="24"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -4033,28 +4026,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="20"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="24"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -4120,7 +4113,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -4188,7 +4181,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="21"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -4254,7 +4247,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="21"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -4320,7 +4313,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="21"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -4386,7 +4379,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="21"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -4452,7 +4445,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -4520,7 +4513,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="23"/>
+      <c r="A48" s="20"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -4586,7 +4579,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="24"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -4652,28 +4645,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19"/>
-      <c r="O52" s="19"/>
-      <c r="P52" s="19"/>
-      <c r="Q52" s="19"/>
-      <c r="R52" s="19"/>
-      <c r="S52" s="19"/>
-      <c r="T52" s="19"/>
-      <c r="U52" s="19"/>
-      <c r="V52" s="20"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="23"/>
+      <c r="K52" s="23"/>
+      <c r="L52" s="23"/>
+      <c r="M52" s="23"/>
+      <c r="N52" s="23"/>
+      <c r="O52" s="23"/>
+      <c r="P52" s="23"/>
+      <c r="Q52" s="23"/>
+      <c r="R52" s="23"/>
+      <c r="S52" s="23"/>
+      <c r="T52" s="23"/>
+      <c r="U52" s="23"/>
+      <c r="V52" s="24"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -4739,7 +4732,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
@@ -4752,17 +4745,17 @@
         <v>72</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="I54" s="1" t="s">
         <v>72</v>
       </c>
@@ -4776,10 +4769,10 @@
         <v>72</v>
       </c>
       <c r="M54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N54" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>92</v>
@@ -4791,7 +4784,7 @@
         <v>72</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>72</v>
@@ -4807,7 +4800,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="21"/>
+      <c r="A55" s="18"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -4821,46 +4814,46 @@
         <v>72</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q55" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="R55" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T55" s="1" t="s">
         <v>92</v>
@@ -4873,7 +4866,7 @@
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="21"/>
+      <c r="A56" s="18"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -4896,50 +4889,50 @@
         <v>72</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R56" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O56" s="1" t="s">
+      <c r="S56" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="T56" s="1" t="s">
         <v>72</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="V56" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="21"/>
+      <c r="A57" s="18"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -4953,7 +4946,7 @@
         <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>72</v>
@@ -4974,22 +4967,22 @@
         <v>72</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>72</v>
@@ -4998,14 +4991,14 @@
         <v>72</v>
       </c>
       <c r="U57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="V57" s="1" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="21"/>
+      <c r="A58" s="18"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -5022,7 +5015,7 @@
         <v>72</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>72</v>
@@ -5037,7 +5030,7 @@
         <v>72</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>72</v>
@@ -5052,13 +5045,13 @@
         <v>72</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="T58" s="1" t="s">
         <v>72</v>
@@ -5071,7 +5064,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -5139,7 +5132,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="23"/>
+      <c r="A60" s="20"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -5205,7 +5198,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="24"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -5271,28 +5264,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="19"/>
-      <c r="M64" s="19"/>
-      <c r="N64" s="19"/>
-      <c r="O64" s="19"/>
-      <c r="P64" s="19"/>
-      <c r="Q64" s="19"/>
-      <c r="R64" s="19"/>
-      <c r="S64" s="19"/>
-      <c r="T64" s="19"/>
-      <c r="U64" s="19"/>
-      <c r="V64" s="20"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
+      <c r="I64" s="23"/>
+      <c r="J64" s="23"/>
+      <c r="K64" s="23"/>
+      <c r="L64" s="23"/>
+      <c r="M64" s="23"/>
+      <c r="N64" s="23"/>
+      <c r="O64" s="23"/>
+      <c r="P64" s="23"/>
+      <c r="Q64" s="23"/>
+      <c r="R64" s="23"/>
+      <c r="S64" s="23"/>
+      <c r="T64" s="23"/>
+      <c r="U64" s="23"/>
+      <c r="V64" s="24"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -5358,7 +5351,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -5398,35 +5391,35 @@
         <v>72</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="T66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U66" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="U66" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="V66" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="21"/>
+      <c r="A67" s="18"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -5446,7 +5439,7 @@
         <v>72</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>72</v>
@@ -5464,7 +5457,7 @@
         <v>72</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="O67" s="1" t="s">
         <v>72</v>
@@ -5473,7 +5466,7 @@
         <v>72</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R67" s="1" t="s">
         <v>72</v>
@@ -5485,14 +5478,14 @@
         <v>72</v>
       </c>
       <c r="U67" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V67" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="V67" s="1" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="21"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -5515,7 +5508,7 @@
         <v>72</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>72</v>
@@ -5527,13 +5520,13 @@
         <v>72</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>72</v>
@@ -5542,7 +5535,7 @@
         <v>72</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>72</v>
@@ -5554,11 +5547,11 @@
         <v>72</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="21"/>
+      <c r="A69" s="18"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -5581,7 +5574,7 @@
         <v>72</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>72</v>
@@ -5593,13 +5586,13 @@
         <v>72</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>72</v>
@@ -5620,11 +5613,11 @@
         <v>72</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="21"/>
+      <c r="A70" s="18"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -5647,7 +5640,7 @@
         <v>72</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>72</v>
@@ -5690,7 +5683,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="22" t="s">
+      <c r="A71" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -5758,7 +5751,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="23"/>
+      <c r="A72" s="20"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -5824,7 +5817,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="24"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -5891,6 +5884,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -5899,16 +5902,6 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95676F4-FDF9-4DED-9845-F83B0BC78DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9343F26A-BD00-4C7C-B6DC-63003231AC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4087" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7927" uniqueCount="108">
   <si>
     <t>10A1</t>
   </si>
@@ -552,6 +552,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -563,15 +572,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -967,7 +967,7 @@
         <v>CD Văn</v>
       </c>
       <c r="D8" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="13">
         <v>35</v>
@@ -2169,28 +2169,28 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="24"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="20"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -2256,7 +2256,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
@@ -2324,7 +2324,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="18"/>
+      <c r="A7" s="21"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
@@ -2390,7 +2390,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="18"/>
+      <c r="A8" s="21"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
@@ -2456,7 +2456,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
@@ -2522,7 +2522,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="18"/>
+      <c r="A10" s="21"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -2588,7 +2588,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -2656,7 +2656,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="20"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -2722,7 +2722,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="21"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -2788,28 +2788,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="24"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2875,7 +2875,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
@@ -2943,7 +2943,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
@@ -3009,7 +3009,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="18"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
@@ -3075,7 +3075,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -3141,7 +3141,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -3207,7 +3207,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -3275,7 +3275,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="20"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>72</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>72</v>
@@ -3341,7 +3341,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="21"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -3407,28 +3407,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="24"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="20"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -3494,7 +3494,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
@@ -3562,7 +3562,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="18"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
@@ -3628,7 +3628,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -3694,7 +3694,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="18"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -3760,7 +3760,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -3826,7 +3826,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -3894,7 +3894,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="20"/>
+      <c r="A36" s="23"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -3960,7 +3960,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="21"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -4026,28 +4026,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="23"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="23"/>
-      <c r="U40" s="23"/>
-      <c r="V40" s="24"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="20"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -4113,7 +4113,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -4181,7 +4181,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="18"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -4247,7 +4247,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="18"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -4313,7 +4313,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="18"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -4379,7 +4379,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="18"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -4445,7 +4445,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -4513,7 +4513,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="20"/>
+      <c r="A48" s="23"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -4579,7 +4579,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="21"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -4645,28 +4645,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="23"/>
-      <c r="R52" s="23"/>
-      <c r="S52" s="23"/>
-      <c r="T52" s="23"/>
-      <c r="U52" s="23"/>
-      <c r="V52" s="24"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="19"/>
+      <c r="T52" s="19"/>
+      <c r="U52" s="19"/>
+      <c r="V52" s="20"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -4732,7 +4732,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="18"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -4866,7 +4866,7 @@
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="18"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -4932,7 +4932,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="18"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -4998,7 +4998,7 @@
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="18"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -5064,7 +5064,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="19" t="s">
+      <c r="A59" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -5132,7 +5132,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="20"/>
+      <c r="A60" s="23"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -5198,7 +5198,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="21"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -5264,28 +5264,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="23"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="23"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="23"/>
-      <c r="Q64" s="23"/>
-      <c r="R64" s="23"/>
-      <c r="S64" s="23"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="23"/>
-      <c r="V64" s="24"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="19"/>
+      <c r="U64" s="19"/>
+      <c r="V64" s="20"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -5351,7 +5351,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -5419,7 +5419,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="18"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>72</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>72</v>
@@ -5485,7 +5485,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="18"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -5551,7 +5551,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="18"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -5617,7 +5617,7 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="18"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -5683,7 +5683,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="19" t="s">
+      <c r="A71" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -5751,7 +5751,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="20"/>
+      <c r="A72" s="23"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -5817,7 +5817,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="21"/>
+      <c r="A73" s="24"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -5884,16 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -5902,6 +5892,16 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9343F26A-BD00-4C7C-B6DC-63003231AC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2A5254-3CC1-4217-A8A4-02BF812D0D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7927" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="105">
   <si>
     <t>10A1</t>
   </si>
@@ -310,9 +310,6 @@
     <t>Hoàng Văn Chinh-CD Sử</t>
   </si>
   <si>
-    <t>Hoàng Hiếu Trình-CD Văn</t>
-  </si>
-  <si>
     <t>1,2</t>
   </si>
   <si>
@@ -338,12 +335,6 @@
   </si>
   <si>
     <t>2,3</t>
-  </si>
-  <si>
-    <t>Vi Văn Tình-CD Văn</t>
-  </si>
-  <si>
-    <t>Mã Đức Bảo-CD Văn</t>
   </si>
   <si>
     <t>Nguyễn Thị Hằng-CD Sử</t>
@@ -356,7 +347,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -856,25 +846,25 @@
   <dimension ref="A5:U124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="28.08984375"/>
-    <col min="2" max="2" customWidth="true" width="63.08984375"/>
-    <col min="3" max="3" customWidth="true" width="20.1796875"/>
-    <col min="4" max="4" customWidth="true" width="16.36328125"/>
-    <col min="5" max="5" customWidth="true" width="15.26953125"/>
-    <col min="6" max="6" customWidth="true" width="22.7265625"/>
-    <col min="7" max="7" customWidth="true" width="21.54296875"/>
-    <col min="8" max="8" customWidth="true" width="20.36328125"/>
-    <col min="9" max="9" customWidth="true" width="26.453125"/>
-    <col min="10" max="10" customWidth="true" width="22.81640625"/>
-    <col min="11" max="11" customWidth="true" width="23.36328125"/>
-    <col min="12" max="12" customWidth="true" width="12.7265625"/>
-    <col min="13" max="13" customWidth="true" width="19.1796875"/>
-    <col min="14" max="14" customWidth="true" width="16.08984375"/>
-    <col min="15" max="15" customWidth="true" width="16.1796875"/>
-    <col min="16" max="16" customWidth="true" width="10.90625"/>
-    <col min="17" max="17" customWidth="true" width="13.54296875"/>
-    <col min="20" max="20" customWidth="true" width="17.08984375"/>
-    <col min="21" max="21" customWidth="true" width="9.90625"/>
+    <col min="1" max="1" width="28.08984375" customWidth="1"/>
+    <col min="2" max="2" width="63.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" customWidth="1"/>
+    <col min="8" max="8" width="20.36328125" customWidth="1"/>
+    <col min="9" max="9" width="26.453125" customWidth="1"/>
+    <col min="10" max="10" width="22.81640625" customWidth="1"/>
+    <col min="11" max="11" width="23.36328125" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="13" max="13" width="19.1796875" customWidth="1"/>
+    <col min="14" max="14" width="16.08984375" customWidth="1"/>
+    <col min="15" max="15" width="16.1796875" customWidth="1"/>
+    <col min="16" max="16" width="10.90625" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" customWidth="1"/>
+    <col min="20" max="20" width="17.08984375" customWidth="1"/>
+    <col min="21" max="21" width="9.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -899,22 +889,22 @@
         <v>32</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="I6" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="J6" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="K6" s="16" t="s">
         <v>101</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>102</v>
       </c>
       <c r="L6" s="14" t="s">
         <v>62</v>
@@ -967,7 +957,7 @@
         <v>CD Văn</v>
       </c>
       <c r="D8" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="13">
         <v>35</v>
@@ -1005,20 +995,20 @@
         <v>105</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L9" s="13" t="str">
         <f t="shared" si="1"/>
@@ -2160,12 +2150,12 @@
   <dimension ref="A4:V73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" customWidth="true" width="24.90625"/>
-    <col min="11" max="11" customWidth="true" width="17.90625"/>
-    <col min="15" max="15" customWidth="true" width="17.453125"/>
-    <col min="17" max="17" customWidth="true" width="19.6328125"/>
-    <col min="18" max="18" customWidth="true" width="24.36328125"/>
-    <col min="19" max="19" customWidth="true" width="23.0"/>
+    <col min="10" max="10" width="24.90625" customWidth="1"/>
+    <col min="11" max="11" width="17.90625" customWidth="1"/>
+    <col min="15" max="15" width="17.453125" customWidth="1"/>
+    <col min="17" max="17" width="19.6328125" customWidth="1"/>
+    <col min="18" max="18" width="24.36328125" customWidth="1"/>
+    <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
@@ -2425,7 +2415,7 @@
         <v>92</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>72</v>
@@ -2446,7 +2436,7 @@
         <v>72</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="U8" s="1" t="s">
         <v>72</v>
@@ -2470,13 +2460,13 @@
         <v>72</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>72</v>
@@ -2497,7 +2487,7 @@
         <v>72</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>72</v>
@@ -2539,7 +2529,7 @@
         <v>72</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>72</v>
@@ -2560,7 +2550,7 @@
         <v>72</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>72</v>
@@ -2569,10 +2559,10 @@
         <v>72</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>72</v>
@@ -3023,10 +3013,10 @@
         <v>90</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>72</v>
@@ -3044,7 +3034,7 @@
         <v>92</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>72</v>
@@ -3065,7 +3055,7 @@
         <v>72</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="U20" s="1" t="s">
         <v>72</v>
@@ -3089,10 +3079,10 @@
         <v>72</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>72</v>
@@ -3122,7 +3112,7 @@
         <v>72</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>72</v>
@@ -3161,10 +3151,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>72</v>
@@ -3179,7 +3169,7 @@
         <v>72</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>72</v>
@@ -3188,7 +3178,7 @@
         <v>72</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>72</v>
@@ -3316,7 +3306,7 @@
         <v>72</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>72</v>
@@ -3513,10 +3503,10 @@
         <v>72</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>72</v>
@@ -3534,10 +3524,10 @@
         <v>72</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>72</v>
@@ -3552,10 +3542,10 @@
         <v>72</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>72</v>
@@ -3579,10 +3569,10 @@
         <v>90</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>72</v>
@@ -3603,7 +3593,7 @@
         <v>72</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>72</v>
@@ -3618,10 +3608,10 @@
         <v>72</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>72</v>
@@ -3642,16 +3632,16 @@
         <v>72</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>72</v>
@@ -3663,13 +3653,13 @@
         <v>88</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>72</v>
@@ -3678,7 +3668,7 @@
         <v>72</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>72</v>
@@ -3687,10 +3677,10 @@
         <v>72</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
@@ -3711,13 +3701,13 @@
         <v>72</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>72</v>
@@ -3729,7 +3719,7 @@
         <v>72</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>72</v>
@@ -3744,7 +3734,7 @@
         <v>72</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>72</v>
@@ -3792,13 +3782,13 @@
         <v>72</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>72</v>
@@ -3807,13 +3797,13 @@
         <v>72</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T34" s="1" t="s">
         <v>72</v>
@@ -4751,14 +4741,14 @@
         <v>72</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="J54" s="1" t="s">
         <v>72</v>
       </c>
@@ -4769,22 +4759,22 @@
         <v>72</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>72</v>
@@ -4820,7 +4810,7 @@
         <v>72</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>72</v>
@@ -4835,28 +4825,28 @@
         <v>72</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R55" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="R55" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="S55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="U55" s="1" t="s">
         <v>72</v>
@@ -4886,7 +4876,7 @@
         <v>72</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>72</v>
@@ -4898,13 +4888,13 @@
         <v>72</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>72</v>
@@ -4916,16 +4906,16 @@
         <v>72</v>
       </c>
       <c r="R56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S56" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="S56" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="T56" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>72</v>
@@ -4946,7 +4936,7 @@
         <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>72</v>
@@ -4967,13 +4957,13 @@
         <v>72</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>72</v>
@@ -4991,10 +4981,10 @@
         <v>72</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
@@ -5015,7 +5005,7 @@
         <v>72</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>72</v>
@@ -5060,7 +5050,7 @@
         <v>72</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
@@ -5367,13 +5357,13 @@
         <v>72</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>72</v>
@@ -5388,31 +5378,31 @@
         <v>72</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="V66" s="1" t="s">
         <v>72</v>
@@ -5436,10 +5426,10 @@
         <v>72</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>72</v>
@@ -5457,19 +5447,19 @@
         <v>72</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>72</v>
@@ -5478,10 +5468,10 @@
         <v>72</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
@@ -5505,10 +5495,10 @@
         <v>72</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>72</v>
@@ -5517,13 +5507,13 @@
         <v>72</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>72</v>
@@ -5535,16 +5525,16 @@
         <v>72</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="T68" s="1" t="s">
         <v>72</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="V68" s="1" t="s">
         <v>72</v>
@@ -5568,13 +5558,13 @@
         <v>72</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>72</v>
@@ -5586,7 +5576,7 @@
         <v>72</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>72</v>
@@ -5613,7 +5603,7 @@
         <v>72</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2A5254-3CC1-4217-A8A4-02BF812D0D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC59CBD-F45D-4193-AA5A-7290932A14D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4087" uniqueCount="108">
   <si>
     <t>10A1</t>
   </si>
@@ -341,12 +341,22 @@
   </si>
   <si>
     <t>Cao Thị Tố Uyên-CD Văn</t>
+  </si>
+  <si>
+    <t>Vi Văn Tình-CD Văn</t>
+  </si>
+  <si>
+    <t>Hoàng Hiếu Trình-CD Văn</t>
+  </si>
+  <si>
+    <t>Mã Đức Bảo-CD Văn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -846,25 +856,25 @@
   <dimension ref="A5:U124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" customWidth="1"/>
-    <col min="2" max="2" width="63.08984375" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.36328125" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="21.54296875" customWidth="1"/>
-    <col min="8" max="8" width="20.36328125" customWidth="1"/>
-    <col min="9" max="9" width="26.453125" customWidth="1"/>
-    <col min="10" max="10" width="22.81640625" customWidth="1"/>
-    <col min="11" max="11" width="23.36328125" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
-    <col min="13" max="13" width="19.1796875" customWidth="1"/>
-    <col min="14" max="14" width="16.08984375" customWidth="1"/>
-    <col min="15" max="15" width="16.1796875" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" customWidth="1"/>
-    <col min="20" max="20" width="17.08984375" customWidth="1"/>
-    <col min="21" max="21" width="9.90625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="28.08984375"/>
+    <col min="2" max="2" customWidth="true" width="63.08984375"/>
+    <col min="3" max="3" customWidth="true" width="20.1796875"/>
+    <col min="4" max="4" customWidth="true" width="16.36328125"/>
+    <col min="5" max="5" customWidth="true" width="15.26953125"/>
+    <col min="6" max="6" customWidth="true" width="22.7265625"/>
+    <col min="7" max="7" customWidth="true" width="21.54296875"/>
+    <col min="8" max="8" customWidth="true" width="20.36328125"/>
+    <col min="9" max="9" customWidth="true" width="26.453125"/>
+    <col min="10" max="10" customWidth="true" width="22.81640625"/>
+    <col min="11" max="11" customWidth="true" width="23.36328125"/>
+    <col min="12" max="12" customWidth="true" width="12.7265625"/>
+    <col min="13" max="13" customWidth="true" width="19.1796875"/>
+    <col min="14" max="14" customWidth="true" width="16.08984375"/>
+    <col min="15" max="15" customWidth="true" width="16.1796875"/>
+    <col min="16" max="16" customWidth="true" width="10.90625"/>
+    <col min="17" max="17" customWidth="true" width="13.54296875"/>
+    <col min="20" max="20" customWidth="true" width="17.08984375"/>
+    <col min="21" max="21" customWidth="true" width="9.90625"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -937,11 +947,11 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="13" t="str">
-        <f>A117</f>
+        <f t="shared" ref="L7:L18" si="0">A$117</f>
         <v>Thứ Năm</v>
       </c>
       <c r="M7" s="13" t="str">
-        <f t="shared" ref="M7:M18" si="0">F$89</f>
+        <f t="shared" ref="M7:M18" si="1">F$89</f>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -969,11 +979,11 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="13" t="str">
-        <f t="shared" ref="L8:L18" si="1">A$117</f>
+        <f t="shared" si="0"/>
         <v>Thứ Năm</v>
       </c>
       <c r="M8" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1011,11 +1021,11 @@
         <v>94</v>
       </c>
       <c r="L9" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M9" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M9" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1042,11 +1052,11 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M10" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M10" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1074,11 +1084,11 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M11" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M11" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1105,11 +1115,11 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M12" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M12" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1137,11 +1147,11 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M13" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M13" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1168,11 +1178,11 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M14" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M14" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1200,11 +1210,11 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M15" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M15" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1232,11 +1242,11 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M16" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M16" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1264,11 +1274,11 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M17" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M17" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1296,11 +1306,11 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M18" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M18" s="13" t="str">
-        <f t="shared" si="0"/>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -2150,12 +2160,12 @@
   <dimension ref="A4:V73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" width="24.90625" customWidth="1"/>
-    <col min="11" max="11" width="17.90625" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" customWidth="1"/>
-    <col min="17" max="17" width="19.6328125" customWidth="1"/>
-    <col min="18" max="18" width="24.36328125" customWidth="1"/>
-    <col min="19" max="19" width="23" customWidth="1"/>
+    <col min="10" max="10" customWidth="true" width="24.90625"/>
+    <col min="11" max="11" customWidth="true" width="17.90625"/>
+    <col min="15" max="15" customWidth="true" width="17.453125"/>
+    <col min="17" max="17" customWidth="true" width="19.6328125"/>
+    <col min="18" max="18" customWidth="true" width="24.36328125"/>
+    <col min="19" max="19" customWidth="true" width="23.0"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
@@ -2394,10 +2404,10 @@
         <v>72</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>72</v>
@@ -2442,7 +2452,7 @@
         <v>72</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
@@ -2460,10 +2470,10 @@
         <v>72</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -2481,7 +2491,7 @@
         <v>88</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>72</v>
@@ -2499,7 +2509,7 @@
         <v>72</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>72</v>
@@ -2559,7 +2569,7 @@
         <v>72</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>72</v>
@@ -2600,7 +2610,7 @@
         <v>72</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>72</v>
@@ -2615,10 +2625,10 @@
         <v>72</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>72</v>
@@ -2663,7 +2673,7 @@
         <v>72</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>72</v>
@@ -2684,10 +2694,10 @@
         <v>72</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>72</v>
@@ -3013,7 +3023,7 @@
         <v>90</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>72</v>
@@ -3079,10 +3089,10 @@
         <v>72</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>72</v>
@@ -3181,7 +3191,7 @@
         <v>72</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>72</v>
@@ -3222,7 +3232,7 @@
         <v>72</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>72</v>
@@ -3240,7 +3250,7 @@
         <v>72</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>72</v>
@@ -3500,10 +3510,10 @@
         <v>90</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>72</v>
@@ -3521,10 +3531,10 @@
         <v>72</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>72</v>
@@ -3566,10 +3576,10 @@
         <v>72</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>72</v>
@@ -3590,10 +3600,10 @@
         <v>72</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>72</v>
@@ -3635,13 +3645,13 @@
         <v>72</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>72</v>
@@ -3659,7 +3669,7 @@
         <v>72</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>72</v>
@@ -3677,7 +3687,7 @@
         <v>72</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>72</v>
@@ -3704,11 +3714,11 @@
         <v>72</v>
       </c>
       <c r="H33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="J33" s="1" t="s">
         <v>72</v>
       </c>
@@ -3725,7 +3735,7 @@
         <v>72</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>72</v>
@@ -3743,10 +3753,10 @@
         <v>72</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
@@ -3838,7 +3848,7 @@
         <v>72</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>72</v>
@@ -3850,7 +3860,7 @@
         <v>72</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>72</v>
@@ -4807,10 +4817,10 @@
         <v>72</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>72</v>
@@ -4840,10 +4850,10 @@
         <v>73</v>
       </c>
       <c r="R55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S55" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="T55" s="1" t="s">
         <v>72</v>
@@ -4870,7 +4880,7 @@
         <v>72</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>72</v>
@@ -4909,7 +4919,7 @@
         <v>73</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="T56" s="1" t="s">
         <v>92</v>
@@ -4936,17 +4946,17 @@
         <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="J57" s="1" t="s">
         <v>72</v>
       </c>
@@ -4972,7 +4982,7 @@
         <v>72</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>72</v>
@@ -5041,7 +5051,7 @@
         <v>72</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T58" s="1" t="s">
         <v>72</v>
@@ -5050,7 +5060,7 @@
         <v>72</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
@@ -5088,7 +5098,7 @@
         <v>72</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>72</v>
@@ -5357,13 +5367,13 @@
         <v>72</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>72</v>
@@ -5393,7 +5403,7 @@
         <v>73</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>72</v>
@@ -5429,7 +5439,7 @@
         <v>104</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>72</v>
@@ -5456,7 +5466,7 @@
         <v>72</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="R67" s="1" t="s">
         <v>73</v>
@@ -5495,7 +5505,7 @@
         <v>72</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>72</v>
@@ -5507,7 +5517,7 @@
         <v>72</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>72</v>
@@ -5522,13 +5532,13 @@
         <v>72</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="R68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S68" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="T68" s="1" t="s">
         <v>72</v>
@@ -5537,7 +5547,7 @@
         <v>91</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
@@ -5558,7 +5568,7 @@
         <v>72</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>72</v>
@@ -5576,7 +5586,7 @@
         <v>72</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>72</v>
@@ -5594,7 +5604,7 @@
         <v>72</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="T69" s="1" t="s">
         <v>72</v>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4087" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9847" uniqueCount="108">
   <si>
     <t>10A1</t>
   </si>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9847" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10807" uniqueCount="108">
   <si>
     <t>10A1</t>
   </si>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC59CBD-F45D-4193-AA5A-7290932A14D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A09B352-3BA8-4B37-B27C-08D183ABD690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10807" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="108">
   <si>
     <t>10A1</t>
   </si>
@@ -356,7 +356,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -552,15 +551,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -572,6 +562,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -856,25 +855,25 @@
   <dimension ref="A5:U124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="28.08984375"/>
-    <col min="2" max="2" customWidth="true" width="63.08984375"/>
-    <col min="3" max="3" customWidth="true" width="20.1796875"/>
-    <col min="4" max="4" customWidth="true" width="16.36328125"/>
-    <col min="5" max="5" customWidth="true" width="15.26953125"/>
-    <col min="6" max="6" customWidth="true" width="22.7265625"/>
-    <col min="7" max="7" customWidth="true" width="21.54296875"/>
-    <col min="8" max="8" customWidth="true" width="20.36328125"/>
-    <col min="9" max="9" customWidth="true" width="26.453125"/>
-    <col min="10" max="10" customWidth="true" width="22.81640625"/>
-    <col min="11" max="11" customWidth="true" width="23.36328125"/>
-    <col min="12" max="12" customWidth="true" width="12.7265625"/>
-    <col min="13" max="13" customWidth="true" width="19.1796875"/>
-    <col min="14" max="14" customWidth="true" width="16.08984375"/>
-    <col min="15" max="15" customWidth="true" width="16.1796875"/>
-    <col min="16" max="16" customWidth="true" width="10.90625"/>
-    <col min="17" max="17" customWidth="true" width="13.54296875"/>
-    <col min="20" max="20" customWidth="true" width="17.08984375"/>
-    <col min="21" max="21" customWidth="true" width="9.90625"/>
+    <col min="1" max="1" width="28.08984375" customWidth="1"/>
+    <col min="2" max="2" width="63.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" customWidth="1"/>
+    <col min="8" max="8" width="20.36328125" customWidth="1"/>
+    <col min="9" max="9" width="26.453125" customWidth="1"/>
+    <col min="10" max="10" width="22.81640625" customWidth="1"/>
+    <col min="11" max="11" width="23.36328125" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="13" max="13" width="19.1796875" customWidth="1"/>
+    <col min="14" max="14" width="16.08984375" customWidth="1"/>
+    <col min="15" max="15" width="16.1796875" customWidth="1"/>
+    <col min="16" max="16" width="10.90625" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" customWidth="1"/>
+    <col min="20" max="20" width="17.08984375" customWidth="1"/>
+    <col min="21" max="21" width="9.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2160,37 +2159,37 @@
   <dimension ref="A4:V73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" customWidth="true" width="24.90625"/>
-    <col min="11" max="11" customWidth="true" width="17.90625"/>
-    <col min="15" max="15" customWidth="true" width="17.453125"/>
-    <col min="17" max="17" customWidth="true" width="19.6328125"/>
-    <col min="18" max="18" customWidth="true" width="24.36328125"/>
-    <col min="19" max="19" customWidth="true" width="23.0"/>
+    <col min="10" max="10" width="24.90625" customWidth="1"/>
+    <col min="11" max="11" width="17.90625" customWidth="1"/>
+    <col min="15" max="15" width="17.453125" customWidth="1"/>
+    <col min="17" max="17" width="19.6328125" customWidth="1"/>
+    <col min="18" max="18" width="24.36328125" customWidth="1"/>
+    <col min="19" max="19" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="20"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="24"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -2256,7 +2255,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
@@ -2324,7 +2323,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="21"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
@@ -2390,7 +2389,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
@@ -2456,7 +2455,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="21"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
@@ -2522,7 +2521,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="21"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -2588,7 +2587,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -2610,7 +2609,7 @@
         <v>72</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>72</v>
@@ -2656,7 +2655,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="23"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>105</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>72</v>
@@ -2722,7 +2721,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="24"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -2788,28 +2787,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="20"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="24"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2875,7 +2874,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
@@ -2943,7 +2942,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="21"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
@@ -3009,7 +3008,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="21"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
@@ -3075,7 +3074,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="21"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -3141,7 +3140,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="21"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -3207,7 +3206,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -3229,7 +3228,7 @@
         <v>72</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>106</v>
@@ -3275,7 +3274,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="23"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -3341,7 +3340,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="24"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -3407,28 +3406,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="20"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="24"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -3494,7 +3493,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
@@ -3562,7 +3561,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="21"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
@@ -3628,7 +3627,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="21"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -3694,7 +3693,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="21"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -3760,7 +3759,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="21"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -3826,7 +3825,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -3860,7 +3859,7 @@
         <v>72</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>72</v>
@@ -3894,7 +3893,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="23"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -3960,7 +3959,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="24"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -4026,28 +4025,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="20"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="24"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -4113,7 +4112,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -4181,7 +4180,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="21"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -4247,7 +4246,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="21"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -4313,7 +4312,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="21"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -4379,7 +4378,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="21"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -4445,7 +4444,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -4513,7 +4512,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="23"/>
+      <c r="A48" s="20"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -4579,7 +4578,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="24"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -4645,28 +4644,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19"/>
-      <c r="O52" s="19"/>
-      <c r="P52" s="19"/>
-      <c r="Q52" s="19"/>
-      <c r="R52" s="19"/>
-      <c r="S52" s="19"/>
-      <c r="T52" s="19"/>
-      <c r="U52" s="19"/>
-      <c r="V52" s="20"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="23"/>
+      <c r="K52" s="23"/>
+      <c r="L52" s="23"/>
+      <c r="M52" s="23"/>
+      <c r="N52" s="23"/>
+      <c r="O52" s="23"/>
+      <c r="P52" s="23"/>
+      <c r="Q52" s="23"/>
+      <c r="R52" s="23"/>
+      <c r="S52" s="23"/>
+      <c r="T52" s="23"/>
+      <c r="U52" s="23"/>
+      <c r="V52" s="24"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -4732,7 +4731,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
@@ -4800,7 +4799,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="21"/>
+      <c r="A55" s="18"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -4866,7 +4865,7 @@
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="21"/>
+      <c r="A56" s="18"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -4932,7 +4931,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="21"/>
+      <c r="A57" s="18"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -4998,7 +4997,7 @@
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="21"/>
+      <c r="A58" s="18"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -5064,7 +5063,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -5098,7 +5097,7 @@
         <v>72</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>72</v>
@@ -5132,7 +5131,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="23"/>
+      <c r="A60" s="20"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -5198,7 +5197,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="24"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -5264,28 +5263,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="19"/>
-      <c r="M64" s="19"/>
-      <c r="N64" s="19"/>
-      <c r="O64" s="19"/>
-      <c r="P64" s="19"/>
-      <c r="Q64" s="19"/>
-      <c r="R64" s="19"/>
-      <c r="S64" s="19"/>
-      <c r="T64" s="19"/>
-      <c r="U64" s="19"/>
-      <c r="V64" s="20"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
+      <c r="I64" s="23"/>
+      <c r="J64" s="23"/>
+      <c r="K64" s="23"/>
+      <c r="L64" s="23"/>
+      <c r="M64" s="23"/>
+      <c r="N64" s="23"/>
+      <c r="O64" s="23"/>
+      <c r="P64" s="23"/>
+      <c r="Q64" s="23"/>
+      <c r="R64" s="23"/>
+      <c r="S64" s="23"/>
+      <c r="T64" s="23"/>
+      <c r="U64" s="23"/>
+      <c r="V64" s="24"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -5351,7 +5350,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -5419,7 +5418,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="21"/>
+      <c r="A67" s="18"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -5485,7 +5484,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="21"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -5551,7 +5550,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="21"/>
+      <c r="A69" s="18"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -5617,7 +5616,7 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="21"/>
+      <c r="A70" s="18"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -5683,7 +5682,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="22" t="s">
+      <c r="A71" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -5717,7 +5716,7 @@
         <v>72</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>72</v>
@@ -5751,7 +5750,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="23"/>
+      <c r="A72" s="20"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -5792,7 +5791,7 @@
         <v>72</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>72</v>
@@ -5817,7 +5816,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="24"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -5884,6 +5883,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -5892,16 +5901,6 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A09B352-3BA8-4B37-B27C-08D183ABD690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C071C662-1851-4E27-9E20-3F8A2C4F9F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="201">
   <si>
     <t>10A1</t>
   </si>
@@ -280,15 +280,9 @@
     <t>11B3,11B4,11B5,11B6</t>
   </si>
   <si>
-    <t>11B1,11B2,11B3,11B4,11B5,11B6,12C4,12C5,12C6</t>
-  </si>
-  <si>
     <t>Nguyễn Thị Hằng</t>
   </si>
   <si>
-    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7,12C1,12C2,12C3</t>
-  </si>
-  <si>
     <t>10A4,10A5,10A6,10A7</t>
   </si>
   <si>
@@ -350,6 +344,291 @@
   </si>
   <si>
     <t>Mã Đức Bảo-CD Văn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hường</t>
+  </si>
+  <si>
+    <t>11B1,11B2,11B3,11B4,11B5,11B6</t>
+  </si>
+  <si>
+    <t>12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7</t>
+  </si>
+  <si>
+    <t>12C1,12C2,12C3</t>
+  </si>
+  <si>
+    <t>11B1,11B2,11B3,11B4,11B5,11B6,12C6</t>
+  </si>
+  <si>
+    <t>Nông Thị Đảm</t>
+  </si>
+  <si>
+    <t>10A4,10A5,10A6,10A7,12C1,12C2,12C3,12C4,12C5</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Châm</t>
+  </si>
+  <si>
+    <t>10A7,12C3,12C4,12C5</t>
+  </si>
+  <si>
+    <t>Dương Thị Nhật Lệ</t>
+  </si>
+  <si>
+    <t>Tạ Thanh Hải</t>
+  </si>
+  <si>
+    <t>10A1,12C1,12C2,12C6</t>
+  </si>
+  <si>
+    <t>Củng Thị Trường</t>
+  </si>
+  <si>
+    <t>10A2,10A3,10A4,10A5,10A6</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngà</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3</t>
+  </si>
+  <si>
+    <t>GDCD</t>
+  </si>
+  <si>
+    <t>11B4,11B5</t>
+  </si>
+  <si>
+    <t>12C1,12C2,12C3,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>Đinh Ngọc Trà</t>
+  </si>
+  <si>
+    <t>10A5,10A6,10A7</t>
+  </si>
+  <si>
+    <t>Bùi Văn Hiệu</t>
+  </si>
+  <si>
+    <t>Đặng Công Đức</t>
+  </si>
+  <si>
+    <t>Dương Thành Tuyên</t>
+  </si>
+  <si>
+    <t>10A4,11B2,11B3,11B4,11B5,11B6</t>
+  </si>
+  <si>
+    <t>Phạm Văn Thanh</t>
+  </si>
+  <si>
+    <t>10A3,10A4,10A5</t>
+  </si>
+  <si>
+    <t>Nguyễn Thế Duy</t>
+  </si>
+  <si>
+    <t>11B1,11B3,11B4,12C1,12C2,12C3</t>
+  </si>
+  <si>
+    <t>Vương T.Ngọc Trang</t>
+  </si>
+  <si>
+    <t>10A1,10A2</t>
+  </si>
+  <si>
+    <t>Phùng Công Thành</t>
+  </si>
+  <si>
+    <t>11B1,11B2,12C3,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>11B1,11B2</t>
+  </si>
+  <si>
+    <t>Thò Mí Say</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,12C1,12C2</t>
+  </si>
+  <si>
+    <t>Lương Bích Hồng</t>
+  </si>
+  <si>
+    <t>11B3,11B6</t>
+  </si>
+  <si>
+    <t>Hồ Duy Kiên</t>
+  </si>
+  <si>
+    <t>10A3,10A6,10A7</t>
+  </si>
+  <si>
+    <t>CD Sinh</t>
+  </si>
+  <si>
+    <t>Vương Thị Thanh</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Biển</t>
+  </si>
+  <si>
+    <t>Lù Văn Chương</t>
+  </si>
+  <si>
+    <t>11B5,11B6</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Công</t>
+  </si>
+  <si>
+    <t>Phạm Văn Đoàn</t>
+  </si>
+  <si>
+    <t>10A4,10A5,10A6,10A7,11B1,11B2,11B4,11B5</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Đô</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7,11B1,11B2,11B3,11B4,11B5,11B6, 12C1,12C2,12C3,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Phúc</t>
+  </si>
+  <si>
+    <t>11B1,11B2,12C1,12C2,12C3,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Quang</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,10A4,10A5,11B3,11B4,11B5,11B6</t>
+  </si>
+  <si>
+    <t>Ngô Thị Hà Chang</t>
+  </si>
+  <si>
+    <t>10A6,10A7</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Quang-TD</t>
+  </si>
+  <si>
+    <t>Củng Thị Trường-Anh</t>
+  </si>
+  <si>
+    <t>Dương Thành Tuyên-Toán</t>
+  </si>
+  <si>
+    <t>Nông Thị Đảm-Địa</t>
+  </si>
+  <si>
+    <t>Hồ Duy Kiên-Sinh</t>
+  </si>
+  <si>
+    <t>Bùi Văn Hiệu-Toán</t>
+  </si>
+  <si>
+    <t>Dương Thị Nhật Lệ-Anh</t>
+  </si>
+  <si>
+    <t>Nguyễn Thế Duy-Lý</t>
+  </si>
+  <si>
+    <t>Lù Văn Chương-CN</t>
+  </si>
+  <si>
+    <t>Lương Bích Hồng-Sinh</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Công-Tin</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Châm-Anh</t>
+  </si>
+  <si>
+    <t>Vương T.Ngọc Trang-Lý</t>
+  </si>
+  <si>
+    <t>Đinh Ngọc Trà-Toán</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hường-Địa</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Biển-Sinh</t>
+  </si>
+  <si>
+    <t>Phạm Văn Đoàn-Tin</t>
+  </si>
+  <si>
+    <t>Ngô Thị Hà Chang-TD</t>
+  </si>
+  <si>
+    <t>Thò Mí Say-Hóa</t>
+  </si>
+  <si>
+    <t>Vương Thị Thanh-Sinh</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Phúc-TD</t>
+  </si>
+  <si>
+    <t>Tạ Thanh Hải-Anh</t>
+  </si>
+  <si>
+    <t>Phùng Công Thành-Hóa</t>
+  </si>
+  <si>
+    <t>Phạm Văn Thanh-Lý</t>
+  </si>
+  <si>
+    <t>Vương T.Ngọc Trang-CD Lý</t>
+  </si>
+  <si>
+    <t>Thò Mí Say-CD Hóa</t>
+  </si>
+  <si>
+    <t>Nguyễn Thế Duy-CD Lý</t>
+  </si>
+  <si>
+    <t>Dương Thành Tuyên-CD Toán</t>
+  </si>
+  <si>
+    <t>Hồ Duy Kiên-CD Sinh</t>
+  </si>
+  <si>
+    <t>Nông Thị Đảm-CD Địa</t>
+  </si>
+  <si>
+    <t>Phùng Công Thành-CD Hóa</t>
+  </si>
+  <si>
+    <t>Đặng Công Đức-CD Toán</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hường-CD Địa</t>
+  </si>
+  <si>
+    <t>Đặng Công Đức-Toán</t>
+  </si>
+  <si>
+    <t>Hồ Duy Kiên-CN</t>
+  </si>
+  <si>
+    <t>Phạm Văn Thanh-CD Lý</t>
+  </si>
+  <si>
+    <t>Bùi Văn Hiệu-CD Toán</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngà-GDCD</t>
   </si>
 </sst>
 </file>
@@ -506,7 +785,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -551,6 +830,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -852,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:U124"/>
+  <dimension ref="A5:U153"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.08984375" customWidth="1"/>
@@ -898,22 +1178,22 @@
         <v>32</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="I6" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="J6" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="K6" s="16" t="s">
         <v>99</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>101</v>
       </c>
       <c r="L6" s="14" t="s">
         <v>62</v>
@@ -930,7 +1210,7 @@
         <v>65</v>
       </c>
       <c r="C7" s="13" t="str">
-        <f>A$89</f>
+        <f>A$116</f>
         <v>Văn</v>
       </c>
       <c r="D7" s="13">
@@ -946,11 +1226,11 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="13" t="str">
-        <f t="shared" ref="L7:L18" si="0">A$117</f>
+        <f t="shared" ref="L7:L31" si="0">A$146</f>
         <v>Thứ Năm</v>
       </c>
       <c r="M7" s="13" t="str">
-        <f t="shared" ref="M7:M18" si="1">F$89</f>
+        <f t="shared" ref="M7:M31" si="1">F$116</f>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -962,7 +1242,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="13" t="str">
-        <f>A97</f>
+        <f>A124</f>
         <v>CD Văn</v>
       </c>
       <c r="D8" s="13">
@@ -994,7 +1274,7 @@
         <v>80</v>
       </c>
       <c r="C9" s="13" t="str">
-        <f>A$89</f>
+        <f>A$116</f>
         <v>Văn</v>
       </c>
       <c r="D9" s="13">
@@ -1004,20 +1284,20 @@
         <v>105</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L9" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1067,7 +1347,7 @@
         <v>79</v>
       </c>
       <c r="C11" s="13" t="str">
-        <f>A$89</f>
+        <f>A$116</f>
         <v>Văn</v>
       </c>
       <c r="D11" s="13">
@@ -1130,7 +1410,7 @@
         <v>78</v>
       </c>
       <c r="C13" s="13" t="str">
-        <f>A$89</f>
+        <f>A$116</f>
         <v>Văn</v>
       </c>
       <c r="D13" s="13">
@@ -1190,10 +1470,10 @@
         <v>82</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C15" s="13" t="str">
-        <f>A$91</f>
+        <f>A$118</f>
         <v>Sử</v>
       </c>
       <c r="D15" s="13">
@@ -1222,17 +1502,17 @@
         <v>82</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C16" s="13" t="str">
-        <f>A$100</f>
-        <v>CD Sử</v>
+        <f>A$118</f>
+        <v>Sử</v>
       </c>
       <c r="D16" s="13">
         <v>1</v>
       </c>
       <c r="E16" s="13">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="1"/>
@@ -1250,23 +1530,23 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>86</v>
+      <c r="A17" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="C17" s="13" t="str">
-        <f>A$91</f>
-        <v>Sử</v>
+        <f>A$127</f>
+        <v>CD Sử</v>
       </c>
       <c r="D17" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="13">
-        <v>52</v>
-      </c>
-      <c r="F17" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="F17" s="13"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1283,20 +1563,20 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C18" s="13" t="str">
-        <f>A$100</f>
-        <v>CD Sử</v>
+        <f>A$118</f>
+        <v>Sử</v>
       </c>
       <c r="D18" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="13">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1314,79 +1594,161 @@
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="13" t="str">
+        <f>A$118</f>
+        <v>Sử</v>
+      </c>
+      <c r="D19" s="13">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13">
+        <v>52</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
+      <c r="L19" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M19" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="13" t="str">
+        <f>A$127</f>
+        <v>CD Sử</v>
+      </c>
+      <c r="D20" s="13">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13">
+        <v>35</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
+      <c r="L20" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M20" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>44</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
+      <c r="L21" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M21" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>35</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
+      <c r="L22" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M22" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>44</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
+      <c r="L23" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M23" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -1397,753 +1759,2252 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>29</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+      <c r="L24" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M24" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="A25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1">
+        <v>105</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
+      <c r="L25" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M25" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>105</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+      <c r="L26" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M26" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>105</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
+      <c r="L27" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M27" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>97</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
+      <c r="L28" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M28" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="A29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>77</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
+      <c r="L29" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M29" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>70</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" s="9" t="s">
+      <c r="L30" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M30" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>35</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Thứ Năm</v>
+      </c>
+      <c r="M31" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>105</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
+        <v>123</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>105</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>123</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>35</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>105</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>35</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>105</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>35</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>70</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
+        <v>35</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>35</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>70</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>76</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1">
+        <v>35</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>70</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" s="1">
+        <v>35</v>
+      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1">
+        <v>70</v>
+      </c>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1">
+        <v>35</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="1">
+        <v>50</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="1">
+        <v>50</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1">
+        <v>25</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1">
+        <v>50</v>
+      </c>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2</v>
+      </c>
+      <c r="E56" s="1">
+        <v>34</v>
+      </c>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1">
+        <v>70</v>
+      </c>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2</v>
+      </c>
+      <c r="E58" s="1">
+        <v>70</v>
+      </c>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1</v>
+      </c>
+      <c r="E59" s="1">
+        <v>35</v>
+      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60" s="1">
+        <v>2</v>
+      </c>
+      <c r="E60" s="1">
+        <v>52</v>
+      </c>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A61" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" s="18">
+        <v>2</v>
+      </c>
+      <c r="E61" s="1">
+        <v>70</v>
+      </c>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1">
+        <v>35</v>
+      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63" s="1">
+        <v>2</v>
+      </c>
+      <c r="E63" s="1">
+        <v>70</v>
+      </c>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D64" s="1">
+        <v>2</v>
+      </c>
+      <c r="E64" s="1">
+        <v>70</v>
+      </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1">
+        <v>50</v>
+      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A90" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" s="15" t="s">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A91" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A65" s="2" t="s">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A66" s="2" t="s">
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A67" s="2" t="s">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A69" s="2" t="s">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A70" s="2" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A71" s="2" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A72" s="2" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A73" s="2" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A74" s="2" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A75" s="2" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A76" s="2" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A77" s="2" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A78" s="2" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A79" s="2" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A80" s="2" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A81" s="2" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A82" s="2" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A83" s="2" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A84" s="2" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86" s="10" t="s">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A87" s="15" t="s">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B87" s="16" t="s">
+      <c r="B114" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C114" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D87" s="16" t="s">
+      <c r="D114" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E87" s="15" t="s">
+      <c r="E114" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F87" s="16" t="s">
+      <c r="F114" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A88" s="2" t="s">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B115" s="2">
         <v>1</v>
       </c>
-      <c r="C88" s="2" t="str">
-        <f t="shared" ref="C88:C104" si="2">A$123</f>
+      <c r="C115" s="2" t="str">
+        <f t="shared" ref="C115:C131" si="2">A$152</f>
         <v>Sáng</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D115" s="2">
         <v>2</v>
       </c>
-      <c r="E88" s="2" t="b">
-        <f>B$123</f>
+      <c r="E115" s="2" t="b">
+        <f>B$152</f>
         <v>1</v>
       </c>
-      <c r="F88" s="2" t="str">
-        <f>A$109</f>
+      <c r="F115" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89" s="2" t="s">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B116" s="2">
         <v>1</v>
       </c>
-      <c r="C89" s="2" t="str">
+      <c r="C116" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D116" s="2">
         <v>2</v>
       </c>
-      <c r="E89" s="2" t="b">
-        <f>B$123</f>
+      <c r="E116" s="2" t="b">
+        <f>B$152</f>
         <v>1</v>
       </c>
-      <c r="F89" s="2" t="str">
-        <f>A$108</f>
+      <c r="F116" s="2" t="str">
+        <f>A$137</f>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A90" s="2" t="s">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B117" s="2">
         <v>1</v>
       </c>
-      <c r="C90" s="2" t="str">
+      <c r="C117" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D117" s="2">
         <v>2</v>
       </c>
-      <c r="E90" s="2" t="b">
-        <f>B$123</f>
+      <c r="E117" s="2" t="b">
+        <f>B$152</f>
         <v>1</v>
       </c>
-      <c r="F90" s="2" t="str">
-        <f>A$108</f>
+      <c r="F117" s="2" t="str">
+        <f>A$137</f>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A91" s="2" t="s">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B118" s="2">
         <v>1</v>
       </c>
-      <c r="C91" s="2" t="str">
+      <c r="C118" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D118" s="2">
         <v>1</v>
       </c>
-      <c r="E91" s="2" t="b">
-        <f t="shared" ref="E91:E104" si="3">B$124</f>
+      <c r="E118" s="2" t="b">
+        <f t="shared" ref="E118:E131" si="3">B$153</f>
         <v>0</v>
       </c>
-      <c r="F91" s="2" t="str">
-        <f>A$108</f>
+      <c r="F118" s="2" t="str">
+        <f>A$137</f>
         <v>Xã Hội</v>
       </c>
-      <c r="G91" s="6"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A92" s="2" t="s">
+      <c r="G118" s="6"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B119" s="2">
         <v>1</v>
       </c>
-      <c r="C92" s="2" t="str">
+      <c r="C119" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D119" s="2">
         <v>1</v>
       </c>
-      <c r="E92" s="2" t="b">
+      <c r="E119" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F92" s="2" t="str">
-        <f>A$108</f>
+      <c r="F119" s="2" t="str">
+        <f>A$137</f>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A93" s="2" t="s">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B120" s="2">
         <v>1</v>
       </c>
-      <c r="C93" s="2" t="str">
+      <c r="C120" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D120" s="2">
         <v>1</v>
       </c>
-      <c r="E93" s="2" t="b">
+      <c r="E120" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F93" s="2" t="str">
-        <f>A$109</f>
+      <c r="F120" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A94" s="2" t="s">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B121" s="2">
         <v>1</v>
       </c>
-      <c r="C94" s="2" t="str">
+      <c r="C121" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D121" s="2">
         <v>1</v>
       </c>
-      <c r="E94" s="2" t="b">
+      <c r="E121" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F94" s="2" t="str">
-        <f>A$109</f>
+      <c r="F121" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A95" s="2" t="s">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B122" s="2">
         <v>1</v>
       </c>
-      <c r="C95" s="2" t="str">
+      <c r="C122" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D122" s="2">
         <v>1</v>
       </c>
-      <c r="E95" s="2" t="b">
+      <c r="E122" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F95" s="2" t="str">
-        <f>A$109</f>
+      <c r="F122" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A96" s="2" t="s">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B123" s="2">
         <v>2</v>
       </c>
-      <c r="C96" s="2" t="str">
+      <c r="C123" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D123" s="2">
         <v>2</v>
       </c>
-      <c r="E96" s="2" t="b">
+      <c r="E123" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F96" s="2" t="str">
-        <f>A$109</f>
+      <c r="F123" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="2" t="s">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B124" s="2">
         <v>2</v>
       </c>
-      <c r="C97" s="2" t="str">
+      <c r="C124" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D124" s="2">
         <v>2</v>
       </c>
-      <c r="E97" s="2" t="b">
+      <c r="E124" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F97" s="2" t="str">
-        <f>A$108</f>
+      <c r="F124" s="2" t="str">
+        <f>A$137</f>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="2" t="s">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B125" s="2">
         <v>1</v>
       </c>
-      <c r="C98" s="2" t="str">
+      <c r="C125" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D125" s="2">
         <v>1</v>
       </c>
-      <c r="E98" s="2" t="b">
+      <c r="E125" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F98" s="2" t="str">
-        <f>A$108</f>
-        <v>Xã Hội</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="2" t="s">
+      <c r="F125" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B126" s="2">
         <v>2</v>
       </c>
-      <c r="C99" s="2" t="str">
+      <c r="C126" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D126" s="2">
         <v>2</v>
       </c>
-      <c r="E99" s="2" t="b">
+      <c r="E126" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F99" s="2" t="str">
-        <f>A$108</f>
+      <c r="F126" s="2" t="str">
+        <f>A$137</f>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="2" t="s">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B127" s="2">
         <v>2</v>
       </c>
-      <c r="C100" s="2" t="str">
+      <c r="C127" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D127" s="2">
         <v>2</v>
       </c>
-      <c r="E100" s="2" t="b">
+      <c r="E127" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F100" s="2" t="str">
-        <f>A$108</f>
+      <c r="F127" s="2" t="str">
+        <f>A$137</f>
         <v>Xã Hội</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="2" t="s">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B128" s="2">
         <v>2</v>
       </c>
-      <c r="C101" s="2" t="str">
+      <c r="C128" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D128" s="2">
         <v>2</v>
       </c>
-      <c r="E101" s="2" t="b">
+      <c r="E128" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F101" s="2" t="str">
-        <f>A$109</f>
+      <c r="F128" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="2" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B129" s="2">
         <v>2</v>
       </c>
-      <c r="C102" s="2" t="str">
+      <c r="C129" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D129" s="2">
         <v>2</v>
       </c>
-      <c r="E102" s="2" t="b">
+      <c r="E129" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F102" s="2" t="str">
-        <f>A$109</f>
+      <c r="F129" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="2" t="s">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B130" s="2">
         <v>1</v>
       </c>
-      <c r="C103" s="2" t="str">
+      <c r="C130" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D130" s="2">
         <v>1</v>
       </c>
-      <c r="E103" s="2" t="b">
+      <c r="E130" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F103" s="2" t="str">
-        <f>A$109</f>
+      <c r="F130" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="2" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B131" s="2">
         <v>1</v>
       </c>
-      <c r="C104" s="2" t="str">
+      <c r="C131" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Sáng</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D131" s="2">
         <v>1</v>
       </c>
-      <c r="E104" s="2" t="b">
+      <c r="E131" s="2" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F104" s="2" t="str">
-        <f>A$109</f>
+      <c r="F131" s="2" t="str">
+        <f>A$138</f>
         <v>Tự Nhiên</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="9" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B132" s="2">
+        <v>2</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D132" s="2">
+        <v>2</v>
+      </c>
+      <c r="E132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B133" s="2">
+        <v>1</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D133" s="2">
+        <v>1</v>
+      </c>
+      <c r="E133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2" t="str">
+        <f>A$137</f>
+        <v>Xã Hội</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C134" s="6"/>
+      <c r="D134" s="6"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="17" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B107" s="7"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="2" t="s">
+      <c r="B136" s="7"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="11" t="s">
+      <c r="C137" s="6"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="10" t="s">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="12"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" s="17" t="s">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B113" s="7"/>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" s="5" t="s">
+      <c r="B142" s="7"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B114" s="8"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="5" t="s">
+      <c r="B143" s="8"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B115" s="8"/>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" s="5" t="s">
+      <c r="B144" s="8"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B116" s="8"/>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="5" t="s">
+      <c r="B145" s="8"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B117" s="8"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" s="5" t="s">
+      <c r="B146" s="8"/>
+      <c r="C146" s="6"/>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B118" s="8"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="5" t="s">
+      <c r="B147" s="8"/>
+      <c r="C147" s="6"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B119" s="8"/>
-      <c r="C119" s="6"/>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C120" s="6"/>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" s="9" t="s">
+      <c r="B148" s="8"/>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" s="15" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B122" s="15" t="s">
+      <c r="B151" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="2" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B123" s="2" t="b">
+      <c r="B152" s="2" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" s="2" t="s">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B124" s="1" t="b">
+      <c r="B153" s="1" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
@@ -2161,6 +4022,7 @@
   <cols>
     <col min="10" max="10" width="24.90625" customWidth="1"/>
     <col min="11" max="11" width="17.90625" customWidth="1"/>
+    <col min="14" max="14" width="16.26953125" customWidth="1"/>
     <col min="15" max="15" width="17.453125" customWidth="1"/>
     <col min="17" max="17" width="19.6328125" customWidth="1"/>
     <col min="18" max="18" width="24.36328125" customWidth="1"/>
@@ -2168,28 +4030,28 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="25"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -2255,179 +4117,179 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="R6" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="18"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="N7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="P7" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="18"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>73</v>
@@ -2436,64 +4298,64 @@
         <v>72</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>72</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>72</v>
@@ -2505,10 +4367,10 @@
         <v>72</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>72</v>
@@ -2517,28 +4379,28 @@
         <v>72</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="18"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>72</v>
@@ -2547,47 +4409,47 @@
         <v>72</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="U10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -2600,7 +4462,7 @@
         <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>72</v>
@@ -2609,25 +4471,25 @@
         <v>72</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>72</v>
@@ -2655,7 +4517,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="20"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -2666,16 +4528,16 @@
         <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>72</v>
@@ -2684,7 +4546,7 @@
         <v>72</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>72</v>
@@ -2693,7 +4555,7 @@
         <v>72</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>72</v>
@@ -2721,7 +4583,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="21"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -2738,7 +4600,7 @@
         <v>72</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>72</v>
@@ -2759,7 +4621,7 @@
         <v>72</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>72</v>
@@ -2787,28 +4649,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="25"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -2874,62 +4736,62 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="P18" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="T18" s="1" t="s">
         <v>72</v>
@@ -2942,7 +4804,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
@@ -2950,113 +4812,113 @@
         <v>88</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="M19" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="U19" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="18"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="N20" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="O20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="R20" s="1" t="s">
         <v>72</v>
       </c>
@@ -3067,14 +4929,14 @@
         <v>72</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -3085,10 +4947,10 @@
         <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>72</v>
@@ -3097,7 +4959,7 @@
         <v>72</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>72</v>
@@ -3106,10 +4968,10 @@
         <v>72</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>72</v>
@@ -3124,7 +4986,7 @@
         <v>72</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>72</v>
@@ -3136,11 +4998,11 @@
         <v>72</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -3190,10 +5052,10 @@
         <v>72</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>72</v>
@@ -3206,7 +5068,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -3228,10 +5090,10 @@
         <v>72</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>72</v>
@@ -3249,7 +5111,7 @@
         <v>72</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>72</v>
@@ -3274,7 +5136,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="20"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -3340,7 +5202,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="21"/>
+      <c r="A25" s="22"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -3406,28 +5268,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="24"/>
+      <c r="U28" s="24"/>
+      <c r="V28" s="25"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -3493,218 +5355,218 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="H30" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="M30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="T30" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="U30" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="18"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" s="1" t="s">
+      <c r="I31" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="T31" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="U31" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="18"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>72</v>
@@ -3713,70 +5575,70 @@
         <v>72</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="P33" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>72</v>
@@ -3785,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>72</v>
@@ -3794,28 +5656,28 @@
         <v>72</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="U34" s="1" t="s">
         <v>72</v>
@@ -3825,7 +5687,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -3847,7 +5709,7 @@
         <v>72</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>72</v>
@@ -3859,10 +5721,10 @@
         <v>72</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>72</v>
@@ -3893,7 +5755,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="20"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -3901,7 +5763,7 @@
         <v>72</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>72</v>
@@ -3913,7 +5775,7 @@
         <v>72</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>72</v>
@@ -3959,7 +5821,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="21"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -4025,28 +5887,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="23"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="23"/>
-      <c r="U40" s="23"/>
-      <c r="V40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="24"/>
+      <c r="S40" s="24"/>
+      <c r="T40" s="24"/>
+      <c r="U40" s="24"/>
+      <c r="V40" s="25"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -4112,38 +5974,38 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>72</v>
@@ -4155,19 +6017,19 @@
         <v>72</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="T42" s="1" t="s">
         <v>72</v>
@@ -4176,43 +6038,43 @@
         <v>72</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="18"/>
+      <c r="A43" s="19"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>72</v>
@@ -4227,26 +6089,26 @@
         <v>72</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="18"/>
+      <c r="A44" s="19"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -4257,7 +6119,7 @@
         <v>72</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>72</v>
@@ -4266,7 +6128,7 @@
         <v>72</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>72</v>
@@ -4278,10 +6140,10 @@
         <v>72</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>72</v>
@@ -4296,23 +6158,23 @@
         <v>72</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="18"/>
+      <c r="A45" s="19"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -4347,10 +6209,10 @@
         <v>72</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>72</v>
@@ -4374,11 +6236,11 @@
         <v>72</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="18"/>
+      <c r="A46" s="19"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -4416,7 +6278,7 @@
         <v>72</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>72</v>
@@ -4444,7 +6306,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -4512,7 +6374,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="20"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -4578,7 +6440,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="21"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -4644,28 +6506,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="23"/>
-      <c r="R52" s="23"/>
-      <c r="S52" s="23"/>
-      <c r="T52" s="23"/>
-      <c r="U52" s="23"/>
-      <c r="V52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
+      <c r="N52" s="24"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="24"/>
+      <c r="Q52" s="24"/>
+      <c r="R52" s="24"/>
+      <c r="S52" s="24"/>
+      <c r="T52" s="24"/>
+      <c r="U52" s="24"/>
+      <c r="V52" s="25"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -4731,141 +6593,141 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="G54" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="U54" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="V54" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="18"/>
+      <c r="A55" s="19"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="U55" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="18"/>
+      <c r="A56" s="19"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -4873,131 +6735,131 @@
         <v>72</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>72</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="V56" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="18"/>
+      <c r="A57" s="19"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="H57" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="U57" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="V57" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="18"/>
+      <c r="A58" s="19"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -5011,10 +6873,10 @@
         <v>72</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>72</v>
@@ -5026,44 +6888,44 @@
         <v>72</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="19" t="s">
+      <c r="A59" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -5100,13 +6962,13 @@
         <v>72</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="N59" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>72</v>
@@ -5131,7 +6993,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="20"/>
+      <c r="A60" s="21"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -5145,7 +7007,7 @@
         <v>72</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>72</v>
@@ -5197,7 +7059,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="21"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -5214,7 +7076,7 @@
         <v>72</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>72</v>
@@ -5263,28 +7125,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="23"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="23"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="23"/>
-      <c r="Q64" s="23"/>
-      <c r="R64" s="23"/>
-      <c r="S64" s="23"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="23"/>
-      <c r="V64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="24"/>
+      <c r="J64" s="24"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="24"/>
+      <c r="N64" s="24"/>
+      <c r="O64" s="24"/>
+      <c r="P64" s="24"/>
+      <c r="Q64" s="24"/>
+      <c r="R64" s="24"/>
+      <c r="S64" s="24"/>
+      <c r="T64" s="24"/>
+      <c r="U64" s="24"/>
+      <c r="V64" s="25"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -5350,141 +7212,141 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="R66" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="U66" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="S66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="V66" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="18"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="18"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -5492,28 +7354,28 @@
         <v>72</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>72</v>
@@ -5522,40 +7384,40 @@
         <v>72</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="18"/>
+      <c r="A69" s="19"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>72</v>
@@ -5564,7 +7426,7 @@
         <v>72</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>72</v>
@@ -5573,25 +7435,25 @@
         <v>72</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>72</v>
@@ -5600,23 +7462,23 @@
         <v>72</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>90</v>
+        <v>166</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="18"/>
+      <c r="A70" s="19"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -5630,7 +7492,7 @@
         <v>72</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>72</v>
@@ -5639,7 +7501,7 @@
         <v>72</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>72</v>
@@ -5648,13 +7510,13 @@
         <v>72</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="O70" s="1" t="s">
         <v>72</v>
@@ -5666,23 +7528,23 @@
         <v>72</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="V70" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="19" t="s">
+      <c r="A71" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -5707,16 +7569,16 @@
         <v>72</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>72</v>
@@ -5750,7 +7612,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="20"/>
+      <c r="A72" s="21"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -5773,7 +7635,7 @@
         <v>72</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>72</v>
@@ -5785,13 +7647,13 @@
         <v>72</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>72</v>
@@ -5816,7 +7678,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="21"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -5839,7 +7701,7 @@
         <v>72</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>72</v>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C071C662-1851-4E27-9E20-3F8A2C4F9F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18903091-5D99-4E82-B557-702971302EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3371" uniqueCount="201">
   <si>
     <t>10A1</t>
   </si>
@@ -247,394 +247,395 @@
     <t/>
   </si>
   <si>
+    <t>Hoàng Hiếu Trình</t>
+  </si>
+  <si>
+    <t>Vi Văn Tình</t>
+  </si>
+  <si>
+    <t>11B3,11B4,11B5</t>
+  </si>
+  <si>
+    <t>Cao Thị Tố Uyên</t>
+  </si>
+  <si>
+    <t>10A3,10A4,10A5,10A6</t>
+  </si>
+  <si>
+    <t>10A1,10A2,11B3,11B4,11B5</t>
+  </si>
+  <si>
+    <t>10A7,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>10A4,10A5,10A6</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Chinh</t>
+  </si>
+  <si>
+    <t>11B3,11B4,11B5,11B6</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hằng</t>
+  </si>
+  <si>
+    <t>10A4,10A5,10A6,10A7</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T2)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T3)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T4)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T5)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T6)</t>
+  </si>
+  <si>
+    <t>Tiết học tránh dạy (T7)</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hường</t>
+  </si>
+  <si>
+    <t>11B1,11B2,11B3,11B4,11B5,11B6</t>
+  </si>
+  <si>
+    <t>12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7</t>
+  </si>
+  <si>
+    <t>12C1,12C2,12C3</t>
+  </si>
+  <si>
+    <t>11B1,11B2,11B3,11B4,11B5,11B6,12C6</t>
+  </si>
+  <si>
+    <t>Nông Thị Đảm</t>
+  </si>
+  <si>
+    <t>10A4,10A5,10A6,10A7,12C1,12C2,12C3,12C4,12C5</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Châm</t>
+  </si>
+  <si>
+    <t>10A7,12C3,12C4,12C5</t>
+  </si>
+  <si>
+    <t>Dương Thị Nhật Lệ</t>
+  </si>
+  <si>
+    <t>Tạ Thanh Hải</t>
+  </si>
+  <si>
+    <t>10A1,12C1,12C2,12C6</t>
+  </si>
+  <si>
+    <t>Củng Thị Trường</t>
+  </si>
+  <si>
+    <t>10A2,10A3,10A4,10A5,10A6</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngà</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3</t>
+  </si>
+  <si>
+    <t>GDCD</t>
+  </si>
+  <si>
+    <t>11B4,11B5</t>
+  </si>
+  <si>
+    <t>12C1,12C2,12C3,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>Đinh Ngọc Trà</t>
+  </si>
+  <si>
+    <t>10A5,10A6,10A7</t>
+  </si>
+  <si>
+    <t>Bùi Văn Hiệu</t>
+  </si>
+  <si>
+    <t>Đặng Công Đức</t>
+  </si>
+  <si>
+    <t>Dương Thành Tuyên</t>
+  </si>
+  <si>
+    <t>10A4,11B2,11B3,11B4,11B5,11B6</t>
+  </si>
+  <si>
+    <t>Phạm Văn Thanh</t>
+  </si>
+  <si>
+    <t>10A3,10A4,10A5</t>
+  </si>
+  <si>
+    <t>Nguyễn Thế Duy</t>
+  </si>
+  <si>
+    <t>11B1,11B3,11B4,12C1,12C2,12C3</t>
+  </si>
+  <si>
+    <t>Vương T.Ngọc Trang</t>
+  </si>
+  <si>
+    <t>10A1,10A2</t>
+  </si>
+  <si>
+    <t>Phùng Công Thành</t>
+  </si>
+  <si>
+    <t>11B1,11B2,12C3,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>11B1,11B2</t>
+  </si>
+  <si>
+    <t>Thò Mí Say</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,12C1,12C2</t>
+  </si>
+  <si>
+    <t>Lương Bích Hồng</t>
+  </si>
+  <si>
+    <t>11B3,11B6</t>
+  </si>
+  <si>
+    <t>Hồ Duy Kiên</t>
+  </si>
+  <si>
+    <t>10A3,10A6,10A7</t>
+  </si>
+  <si>
+    <t>CD Sinh</t>
+  </si>
+  <si>
+    <t>Vương Thị Thanh</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Biển</t>
+  </si>
+  <si>
+    <t>Lù Văn Chương</t>
+  </si>
+  <si>
+    <t>11B5,11B6</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Công</t>
+  </si>
+  <si>
+    <t>Phạm Văn Đoàn</t>
+  </si>
+  <si>
+    <t>10A4,10A5,10A6,10A7,11B1,11B2,11B4,11B5</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Đô</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7,11B1,11B2,11B3,11B4,11B5,11B6, 12C1,12C2,12C3,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Phúc</t>
+  </si>
+  <si>
+    <t>11B1,11B2,12C1,12C2,12C3,12C4,12C5,12C6</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Quang</t>
+  </si>
+  <si>
+    <t>10A1,10A2,10A3,10A4,10A5,11B3,11B4,11B5,11B6</t>
+  </si>
+  <si>
+    <t>Ngô Thị Hà Chang</t>
+  </si>
+  <si>
+    <t>10A6,10A7</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Quang-TD</t>
+  </si>
+  <si>
+    <t>Củng Thị Trường-Anh</t>
+  </si>
+  <si>
+    <t>Cao Thị Tố Uyên-Văn</t>
+  </si>
+  <si>
+    <t>Dương Thành Tuyên-Toán</t>
+  </si>
+  <si>
+    <t>Nông Thị Đảm-Địa</t>
+  </si>
+  <si>
+    <t>Hồ Duy Kiên-Sinh</t>
+  </si>
+  <si>
+    <t>Hoàng Hiếu Trình-Văn</t>
+  </si>
+  <si>
+    <t>Bùi Văn Hiệu-Toán</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Chinh-Sử</t>
+  </si>
+  <si>
+    <t>Dương Thị Nhật Lệ-Anh</t>
+  </si>
+  <si>
+    <t>Nguyễn Thế Duy-Lý</t>
+  </si>
+  <si>
+    <t>Lù Văn Chương-CN</t>
+  </si>
+  <si>
+    <t>Lương Bích Hồng-Sinh</t>
+  </si>
+  <si>
     <t>Mã Đức Bảo-Văn</t>
   </si>
   <si>
-    <t>Hoàng Hiếu Trình</t>
-  </si>
-  <si>
-    <t>Vi Văn Tình</t>
-  </si>
-  <si>
-    <t>11B3,11B4,11B5</t>
-  </si>
-  <si>
-    <t>Cao Thị Tố Uyên</t>
-  </si>
-  <si>
-    <t>10A3,10A4,10A5,10A6</t>
-  </si>
-  <si>
-    <t>10A1,10A2,11B3,11B4,11B5</t>
-  </si>
-  <si>
-    <t>10A7,12C4,12C5,12C6</t>
-  </si>
-  <si>
-    <t>10A4,10A5,10A6</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Chinh</t>
-  </si>
-  <si>
-    <t>11B3,11B4,11B5,11B6</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Hằng</t>
-  </si>
-  <si>
-    <t>10A4,10A5,10A6,10A7</t>
+    <t>Nguyễn Thành Công-Tin</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Châm-Anh</t>
+  </si>
+  <si>
+    <t>Vương T.Ngọc Trang-Lý</t>
+  </si>
+  <si>
+    <t>Đinh Ngọc Trà-Toán</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hường-Địa</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Biển-Sinh</t>
+  </si>
+  <si>
+    <t>Phạm Văn Đoàn-Tin</t>
+  </si>
+  <si>
+    <t>Ngô Thị Hà Chang-TD</t>
   </si>
   <si>
     <t>Vi Văn Tình-Văn</t>
   </si>
   <si>
-    <t>Cao Thị Tố Uyên-Văn</t>
+    <t>Thò Mí Say-Hóa</t>
   </si>
   <si>
     <t>Nguyễn Thị Hằng-Sử</t>
   </si>
   <si>
-    <t>Hoàng Hiếu Trình-Văn</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Chinh-Sử</t>
+    <t>Nguyễn Đình Phúc-TD</t>
+  </si>
+  <si>
+    <t>Tạ Thanh Hải-Anh</t>
+  </si>
+  <si>
+    <t>Phùng Công Thành-Hóa</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngà-GDCD</t>
+  </si>
+  <si>
+    <t>Vương Thị Thanh-Sinh</t>
+  </si>
+  <si>
+    <t>Phạm Văn Thanh-Lý</t>
+  </si>
+  <si>
+    <t>Vương T.Ngọc Trang-CD Lý</t>
+  </si>
+  <si>
+    <t>Hồ Duy Kiên-CD Sinh</t>
+  </si>
+  <si>
+    <t>Cao Thị Tố Uyên-CD Văn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thế Duy-CD Lý</t>
   </si>
   <si>
     <t>Hoàng Văn Chinh-CD Sử</t>
   </si>
   <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>4,5</t>
-  </si>
-  <si>
-    <t>Tiết học tránh dạy (T2)</t>
-  </si>
-  <si>
-    <t>Tiết học tránh dạy (T3)</t>
-  </si>
-  <si>
-    <t>Tiết học tránh dạy (T4)</t>
-  </si>
-  <si>
-    <t>Tiết học tránh dạy (T5)</t>
-  </si>
-  <si>
-    <t>Tiết học tránh dạy (T6)</t>
-  </si>
-  <si>
-    <t>Tiết học tránh dạy (T7)</t>
-  </si>
-  <si>
-    <t>2,3</t>
+    <t>Dương Thành Tuyên-CD Toán</t>
+  </si>
+  <si>
+    <t>Thò Mí Say-CD Hóa</t>
   </si>
   <si>
     <t>Nguyễn Thị Hằng-CD Sử</t>
   </si>
   <si>
-    <t>Cao Thị Tố Uyên-CD Văn</t>
+    <t>Nông Thị Đảm-CD Địa</t>
+  </si>
+  <si>
+    <t>Phùng Công Thành-CD Hóa</t>
+  </si>
+  <si>
+    <t>Phạm Văn Thanh-CD Lý</t>
+  </si>
+  <si>
+    <t>Đặng Công Đức-CD Toán</t>
   </si>
   <si>
     <t>Vi Văn Tình-CD Văn</t>
   </si>
   <si>
+    <t>Đặng Công Đức-Toán</t>
+  </si>
+  <si>
+    <t>Hồ Duy Kiên-CN</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hường-CD Địa</t>
+  </si>
+  <si>
+    <t>Mã Đức Bảo-CD Văn</t>
+  </si>
+  <si>
+    <t>Bùi Văn Hiệu-CD Toán</t>
+  </si>
+  <si>
     <t>Hoàng Hiếu Trình-CD Văn</t>
-  </si>
-  <si>
-    <t>Mã Đức Bảo-CD Văn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Hường</t>
-  </si>
-  <si>
-    <t>11B1,11B2,11B3,11B4,11B5,11B6</t>
-  </si>
-  <si>
-    <t>12C4,12C5,12C6</t>
-  </si>
-  <si>
-    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7</t>
-  </si>
-  <si>
-    <t>12C1,12C2,12C3</t>
-  </si>
-  <si>
-    <t>11B1,11B2,11B3,11B4,11B5,11B6,12C6</t>
-  </si>
-  <si>
-    <t>Nông Thị Đảm</t>
-  </si>
-  <si>
-    <t>10A4,10A5,10A6,10A7,12C1,12C2,12C3,12C4,12C5</t>
-  </si>
-  <si>
-    <t>Nguyễn Hồng Châm</t>
-  </si>
-  <si>
-    <t>10A7,12C3,12C4,12C5</t>
-  </si>
-  <si>
-    <t>Dương Thị Nhật Lệ</t>
-  </si>
-  <si>
-    <t>Tạ Thanh Hải</t>
-  </si>
-  <si>
-    <t>10A1,12C1,12C2,12C6</t>
-  </si>
-  <si>
-    <t>Củng Thị Trường</t>
-  </si>
-  <si>
-    <t>10A2,10A3,10A4,10A5,10A6</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Ngà</t>
-  </si>
-  <si>
-    <t>10A1,10A2,10A3</t>
-  </si>
-  <si>
-    <t>GDCD</t>
-  </si>
-  <si>
-    <t>11B4,11B5</t>
-  </si>
-  <si>
-    <t>12C1,12C2,12C3,12C4,12C5,12C6</t>
-  </si>
-  <si>
-    <t>Đinh Ngọc Trà</t>
-  </si>
-  <si>
-    <t>10A5,10A6,10A7</t>
-  </si>
-  <si>
-    <t>Bùi Văn Hiệu</t>
-  </si>
-  <si>
-    <t>Đặng Công Đức</t>
-  </si>
-  <si>
-    <t>Dương Thành Tuyên</t>
-  </si>
-  <si>
-    <t>10A4,11B2,11B3,11B4,11B5,11B6</t>
-  </si>
-  <si>
-    <t>Phạm Văn Thanh</t>
-  </si>
-  <si>
-    <t>10A3,10A4,10A5</t>
-  </si>
-  <si>
-    <t>Nguyễn Thế Duy</t>
-  </si>
-  <si>
-    <t>11B1,11B3,11B4,12C1,12C2,12C3</t>
-  </si>
-  <si>
-    <t>Vương T.Ngọc Trang</t>
-  </si>
-  <si>
-    <t>10A1,10A2</t>
-  </si>
-  <si>
-    <t>Phùng Công Thành</t>
-  </si>
-  <si>
-    <t>11B1,11B2,12C3,12C4,12C5,12C6</t>
-  </si>
-  <si>
-    <t>11B1,11B2</t>
-  </si>
-  <si>
-    <t>Thò Mí Say</t>
-  </si>
-  <si>
-    <t>10A1,10A2,10A3,12C1,12C2</t>
-  </si>
-  <si>
-    <t>Lương Bích Hồng</t>
-  </si>
-  <si>
-    <t>11B3,11B6</t>
-  </si>
-  <si>
-    <t>Hồ Duy Kiên</t>
-  </si>
-  <si>
-    <t>10A3,10A6,10A7</t>
-  </si>
-  <si>
-    <t>CD Sinh</t>
-  </si>
-  <si>
-    <t>Vương Thị Thanh</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Biển</t>
-  </si>
-  <si>
-    <t>Lù Văn Chương</t>
-  </si>
-  <si>
-    <t>11B5,11B6</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Công</t>
-  </si>
-  <si>
-    <t>Phạm Văn Đoàn</t>
-  </si>
-  <si>
-    <t>10A4,10A5,10A6,10A7,11B1,11B2,11B4,11B5</t>
-  </si>
-  <si>
-    <t>Hoàng Thanh Đô</t>
-  </si>
-  <si>
-    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7,11B1,11B2,11B3,11B4,11B5,11B6, 12C1,12C2,12C3,12C4,12C5,12C6</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Phúc</t>
-  </si>
-  <si>
-    <t>11B1,11B2,12C1,12C2,12C3,12C4,12C5,12C6</t>
-  </si>
-  <si>
-    <t>Hoàng Thanh Quang</t>
-  </si>
-  <si>
-    <t>10A1,10A2,10A3,10A4,10A5,11B3,11B4,11B5,11B6</t>
-  </si>
-  <si>
-    <t>Ngô Thị Hà Chang</t>
-  </si>
-  <si>
-    <t>10A6,10A7</t>
-  </si>
-  <si>
-    <t>Hoàng Thanh Quang-TD</t>
-  </si>
-  <si>
-    <t>Củng Thị Trường-Anh</t>
-  </si>
-  <si>
-    <t>Dương Thành Tuyên-Toán</t>
-  </si>
-  <si>
-    <t>Nông Thị Đảm-Địa</t>
-  </si>
-  <si>
-    <t>Hồ Duy Kiên-Sinh</t>
-  </si>
-  <si>
-    <t>Bùi Văn Hiệu-Toán</t>
-  </si>
-  <si>
-    <t>Dương Thị Nhật Lệ-Anh</t>
-  </si>
-  <si>
-    <t>Nguyễn Thế Duy-Lý</t>
-  </si>
-  <si>
-    <t>Lù Văn Chương-CN</t>
-  </si>
-  <si>
-    <t>Lương Bích Hồng-Sinh</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Công-Tin</t>
-  </si>
-  <si>
-    <t>Nguyễn Hồng Châm-Anh</t>
-  </si>
-  <si>
-    <t>Vương T.Ngọc Trang-Lý</t>
-  </si>
-  <si>
-    <t>Đinh Ngọc Trà-Toán</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Hường-Địa</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Biển-Sinh</t>
-  </si>
-  <si>
-    <t>Phạm Văn Đoàn-Tin</t>
-  </si>
-  <si>
-    <t>Ngô Thị Hà Chang-TD</t>
-  </si>
-  <si>
-    <t>Thò Mí Say-Hóa</t>
-  </si>
-  <si>
-    <t>Vương Thị Thanh-Sinh</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Phúc-TD</t>
-  </si>
-  <si>
-    <t>Tạ Thanh Hải-Anh</t>
-  </si>
-  <si>
-    <t>Phùng Công Thành-Hóa</t>
-  </si>
-  <si>
-    <t>Phạm Văn Thanh-Lý</t>
-  </si>
-  <si>
-    <t>Vương T.Ngọc Trang-CD Lý</t>
-  </si>
-  <si>
-    <t>Thò Mí Say-CD Hóa</t>
-  </si>
-  <si>
-    <t>Nguyễn Thế Duy-CD Lý</t>
-  </si>
-  <si>
-    <t>Dương Thành Tuyên-CD Toán</t>
-  </si>
-  <si>
-    <t>Hồ Duy Kiên-CD Sinh</t>
-  </si>
-  <si>
-    <t>Nông Thị Đảm-CD Địa</t>
-  </si>
-  <si>
-    <t>Phùng Công Thành-CD Hóa</t>
-  </si>
-  <si>
-    <t>Đặng Công Đức-CD Toán</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Hường-CD Địa</t>
-  </si>
-  <si>
-    <t>Đặng Công Đức-Toán</t>
-  </si>
-  <si>
-    <t>Hồ Duy Kiên-CN</t>
-  </si>
-  <si>
-    <t>Phạm Văn Thanh-CD Lý</t>
-  </si>
-  <si>
-    <t>Bùi Văn Hiệu-CD Toán</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Ngà-GDCD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -831,6 +832,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -842,15 +852,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1135,25 +1136,25 @@
   <dimension ref="A5:U153"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" customWidth="1"/>
-    <col min="2" max="2" width="63.08984375" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.36328125" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="21.54296875" customWidth="1"/>
-    <col min="8" max="8" width="20.36328125" customWidth="1"/>
-    <col min="9" max="9" width="26.453125" customWidth="1"/>
-    <col min="10" max="10" width="22.81640625" customWidth="1"/>
-    <col min="11" max="11" width="23.36328125" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
-    <col min="13" max="13" width="19.1796875" customWidth="1"/>
-    <col min="14" max="14" width="16.08984375" customWidth="1"/>
-    <col min="15" max="15" width="16.1796875" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" customWidth="1"/>
-    <col min="20" max="20" width="17.08984375" customWidth="1"/>
-    <col min="21" max="21" width="9.90625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="28.08984375"/>
+    <col min="2" max="2" customWidth="true" width="63.08984375"/>
+    <col min="3" max="3" customWidth="true" width="20.1796875"/>
+    <col min="4" max="4" customWidth="true" width="16.36328125"/>
+    <col min="5" max="5" customWidth="true" width="15.26953125"/>
+    <col min="6" max="6" customWidth="true" width="22.7265625"/>
+    <col min="7" max="7" customWidth="true" width="21.54296875"/>
+    <col min="8" max="8" customWidth="true" width="20.36328125"/>
+    <col min="9" max="9" customWidth="true" width="26.453125"/>
+    <col min="10" max="10" customWidth="true" width="22.81640625"/>
+    <col min="11" max="11" customWidth="true" width="23.36328125"/>
+    <col min="12" max="12" customWidth="true" width="12.7265625"/>
+    <col min="13" max="13" customWidth="true" width="19.1796875"/>
+    <col min="14" max="14" customWidth="true" width="16.08984375"/>
+    <col min="15" max="15" customWidth="true" width="16.1796875"/>
+    <col min="16" max="16" customWidth="true" width="10.90625"/>
+    <col min="17" max="17" customWidth="true" width="13.54296875"/>
+    <col min="20" max="20" customWidth="true" width="17.08984375"/>
+    <col min="21" max="21" customWidth="true" width="9.90625"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -1178,22 +1179,22 @@
         <v>32</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="L6" s="14" t="s">
         <v>62</v>
@@ -1225,12 +1226,11 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="13" t="str">
-        <f t="shared" ref="L7:L31" si="0">A$146</f>
-        <v>Thứ Năm</v>
+      <c r="L7" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="M7" s="13" t="str">
-        <f t="shared" ref="M7:M31" si="1">F$116</f>
+        <f t="shared" ref="M7:M31" si="0">F$116</f>
         <v>Xã Hội</v>
       </c>
     </row>
@@ -1257,21 +1257,20 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="13" t="str">
+      <c r="L8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M8" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="13" t="str">
         <f>A$116</f>
@@ -1284,33 +1283,32 @@
         <v>105</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L9" s="13" t="str">
+        <v>85</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M9" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>6</v>
@@ -1330,21 +1328,20 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="13" t="str">
+      <c r="L10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M10" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="13" t="str">
         <f>A$116</f>
@@ -1362,21 +1359,20 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="13" t="str">
+      <c r="L11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M11" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>75</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>54</v>
@@ -1393,21 +1389,20 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="13" t="str">
+      <c r="L12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M12" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="C13" s="13" t="str">
         <f>A$116</f>
@@ -1425,21 +1420,20 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="13" t="str">
+      <c r="L13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M13" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>54</v>
@@ -1456,21 +1450,20 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="13" t="str">
+      <c r="L14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M14" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C15" s="13" t="str">
         <f>A$118</f>
@@ -1488,21 +1481,20 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="13" t="str">
+      <c r="L15" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M15" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C16" s="13" t="str">
         <f>A$118</f>
@@ -1520,21 +1512,20 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="13" t="str">
+      <c r="L16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M16" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>83</v>
       </c>
       <c r="C17" s="13" t="str">
         <f>A$127</f>
@@ -1552,21 +1543,20 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="13" t="str">
+      <c r="L17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M17" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C18" s="13" t="str">
         <f>A$118</f>
@@ -1584,21 +1574,20 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="13" t="str">
+      <c r="L18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M18" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C19" s="13" t="str">
         <f>A$118</f>
@@ -1616,21 +1605,20 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="13" t="str">
+      <c r="L19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M19" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C20" s="13" t="str">
         <f>A$127</f>
@@ -1648,21 +1636,20 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="13" t="str">
+      <c r="L20" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M20" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>49</v>
@@ -1679,21 +1666,20 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="13" t="str">
+      <c r="L21" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M21" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>55</v>
@@ -1710,21 +1696,20 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="13" t="str">
+      <c r="L22" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M22" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>49</v>
@@ -1741,12 +1726,11 @@
       <c r="I23" s="1"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="13" t="str">
+      <c r="L23" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M23" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
       <c r="N23" s="6"/>
@@ -1760,10 +1744,10 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>55</v>
@@ -1780,21 +1764,20 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="13" t="str">
+      <c r="L24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M24" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>47</v>
@@ -1811,21 +1794,20 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="13" t="str">
+      <c r="L25" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M25" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>47</v>
@@ -1842,21 +1824,20 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="13" t="str">
+      <c r="L26" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M26" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>47</v>
@@ -1873,21 +1854,20 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="13" t="str">
+      <c r="L27" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M27" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>47</v>
@@ -1904,24 +1884,23 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="13" t="str">
+      <c r="L28" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M28" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -1935,24 +1914,23 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="13" t="str">
+      <c r="L29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M29" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -1966,24 +1944,23 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="13" t="str">
+      <c r="L30" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M30" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -1997,21 +1974,20 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="13" t="str">
+      <c r="L31" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thứ Năm</v>
-      </c>
-      <c r="M31" s="13" t="str">
-        <f t="shared" si="1"/>
         <v>Xã Hội</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>43</v>
@@ -2037,10 +2013,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>43</v>
@@ -2066,7 +2042,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -2095,10 +2071,10 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>43</v>
@@ -2124,7 +2100,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -2153,10 +2129,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>43</v>
@@ -2182,10 +2158,10 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>53</v>
@@ -2211,10 +2187,10 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>43</v>
@@ -2240,10 +2216,10 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>53</v>
@@ -2269,10 +2245,10 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>50</v>
@@ -2298,10 +2274,10 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>50</v>
@@ -2327,7 +2303,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
@@ -2356,7 +2332,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>8</v>
@@ -2385,10 +2361,10 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>50</v>
@@ -2414,10 +2390,10 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>50</v>
@@ -2443,10 +2419,10 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>57</v>
@@ -2472,10 +2448,10 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>51</v>
@@ -2501,10 +2477,10 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>58</v>
@@ -2530,10 +2506,10 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>51</v>
@@ -2559,10 +2535,10 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>58</v>
@@ -2588,10 +2564,10 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>59</v>
@@ -2617,10 +2593,10 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>59</v>
@@ -2646,13 +2622,13 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
@@ -2675,10 +2651,10 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>60</v>
@@ -2704,10 +2680,10 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>59</v>
@@ -2733,10 +2709,10 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>59</v>
@@ -2762,10 +2738,10 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>60</v>
@@ -2791,10 +2767,10 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>60</v>
@@ -2820,10 +2796,10 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>52</v>
@@ -2849,10 +2825,10 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="18" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C61" s="18" t="s">
         <v>52</v>
@@ -2878,10 +2854,10 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>61</v>
@@ -2907,10 +2883,10 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>61</v>
@@ -2936,10 +2912,10 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>61</v>
@@ -2965,10 +2941,10 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>61</v>
@@ -3473,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="C115" s="2" t="str">
-        <f t="shared" ref="C115:C131" si="2">A$152</f>
+        <f t="shared" ref="C115:C131" si="1">A$152</f>
         <v>Sáng</v>
       </c>
       <c r="D115" s="2">
@@ -3496,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="C116" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D116" s="2">
@@ -3519,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="C117" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D117" s="2">
@@ -3542,14 +3518,14 @@
         <v>1</v>
       </c>
       <c r="C118" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D118" s="2">
         <v>1</v>
       </c>
       <c r="E118" s="2" t="b">
-        <f t="shared" ref="E118:E131" si="3">B$153</f>
+        <f t="shared" ref="E118:E131" si="2">B$153</f>
         <v>0</v>
       </c>
       <c r="F118" s="2" t="str">
@@ -3566,14 +3542,14 @@
         <v>1</v>
       </c>
       <c r="C119" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D119" s="2">
         <v>1</v>
       </c>
       <c r="E119" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F119" s="2" t="str">
@@ -3589,14 +3565,14 @@
         <v>1</v>
       </c>
       <c r="C120" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D120" s="2">
         <v>1</v>
       </c>
       <c r="E120" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F120" s="2" t="str">
@@ -3612,14 +3588,14 @@
         <v>1</v>
       </c>
       <c r="C121" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D121" s="2">
         <v>1</v>
       </c>
       <c r="E121" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F121" s="2" t="str">
@@ -3635,14 +3611,14 @@
         <v>1</v>
       </c>
       <c r="C122" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D122" s="2">
         <v>1</v>
       </c>
       <c r="E122" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F122" s="2" t="str">
@@ -3657,15 +3633,14 @@
       <c r="B123" s="2">
         <v>2</v>
       </c>
-      <c r="C123" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Sáng</v>
+      <c r="C123" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D123" s="2">
         <v>2</v>
       </c>
       <c r="E123" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F123" s="2" t="str">
@@ -3680,15 +3655,14 @@
       <c r="B124" s="2">
         <v>2</v>
       </c>
-      <c r="C124" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Sáng</v>
+      <c r="C124" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D124" s="2">
         <v>2</v>
       </c>
       <c r="E124" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F124" s="2" t="str">
@@ -3704,14 +3678,14 @@
         <v>1</v>
       </c>
       <c r="C125" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D125" s="2">
         <v>1</v>
       </c>
       <c r="E125" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F125" s="2" t="s">
@@ -3725,15 +3699,14 @@
       <c r="B126" s="2">
         <v>2</v>
       </c>
-      <c r="C126" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Sáng</v>
+      <c r="C126" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D126" s="2">
         <v>2</v>
       </c>
       <c r="E126" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F126" s="2" t="str">
@@ -3748,15 +3721,14 @@
       <c r="B127" s="2">
         <v>2</v>
       </c>
-      <c r="C127" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Sáng</v>
+      <c r="C127" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D127" s="2">
         <v>2</v>
       </c>
       <c r="E127" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F127" s="2" t="str">
@@ -3771,15 +3743,14 @@
       <c r="B128" s="2">
         <v>2</v>
       </c>
-      <c r="C128" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Sáng</v>
+      <c r="C128" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D128" s="2">
         <v>2</v>
       </c>
       <c r="E128" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F128" s="2" t="str">
@@ -3794,15 +3765,14 @@
       <c r="B129" s="2">
         <v>2</v>
       </c>
-      <c r="C129" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Sáng</v>
+      <c r="C129" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D129" s="2">
         <v>2</v>
       </c>
       <c r="E129" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F129" s="2" t="str">
@@ -3818,14 +3788,14 @@
         <v>1</v>
       </c>
       <c r="C130" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D130" s="2">
         <v>1</v>
       </c>
       <c r="E130" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F130" s="2" t="str">
@@ -3841,14 +3811,14 @@
         <v>1</v>
       </c>
       <c r="C131" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Sáng</v>
       </c>
       <c r="D131" s="2">
         <v>1</v>
       </c>
       <c r="E131" s="2" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F131" s="2" t="str">
@@ -3858,13 +3828,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B132" s="2">
         <v>2</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D132" s="2">
         <v>2</v>
@@ -3878,7 +3848,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B133" s="2">
         <v>1</v>
@@ -4020,38 +3990,38 @@
   <dimension ref="A4:V73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" width="24.90625" customWidth="1"/>
-    <col min="11" max="11" width="17.90625" customWidth="1"/>
-    <col min="14" max="14" width="16.26953125" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" customWidth="1"/>
-    <col min="17" max="17" width="19.6328125" customWidth="1"/>
-    <col min="18" max="18" width="24.36328125" customWidth="1"/>
-    <col min="19" max="19" width="23" customWidth="1"/>
+    <col min="10" max="10" customWidth="true" width="24.90625"/>
+    <col min="11" max="11" customWidth="true" width="17.90625"/>
+    <col min="14" max="14" customWidth="true" width="16.26953125"/>
+    <col min="15" max="15" customWidth="true" width="17.453125"/>
+    <col min="17" max="17" customWidth="true" width="19.6328125"/>
+    <col min="18" max="18" customWidth="true" width="24.36328125"/>
+    <col min="19" max="19" customWidth="true" width="23.0"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="25"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="21"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -4117,352 +4087,352 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="P6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="T6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="U6" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="V6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>177</v>
-      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="19"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="P7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="R7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="U7" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="V7" s="1" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="19"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="L8" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="P8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="U8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V8" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="19"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T9" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="U9" s="1" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="19"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="U10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="23" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>72</v>
@@ -4471,28 +4441,28 @@
         <v>72</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>72</v>
@@ -4517,12 +4487,12 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="21"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>72</v>
@@ -4531,23 +4501,23 @@
         <v>188</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="L12" s="1" t="s">
         <v>72</v>
       </c>
@@ -4555,7 +4525,7 @@
         <v>72</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>72</v>
@@ -4583,7 +4553,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="22"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -4600,7 +4570,7 @@
         <v>72</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>72</v>
@@ -4621,7 +4591,7 @@
         <v>72</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>72</v>
@@ -4649,28 +4619,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="25"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="21"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -4736,63 +4706,63 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="P18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="T18" s="1" t="s">
         <v>72</v>
       </c>
@@ -4804,139 +4774,139 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="19"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="1" t="s">
+      <c r="L19" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M19" s="1" t="s">
+      <c r="P19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q19" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="R19" s="1" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="19"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="N20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="R20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="T20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="19"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -4947,7 +4917,7 @@
         <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>72</v>
@@ -4959,7 +4929,7 @@
         <v>72</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>72</v>
@@ -4986,7 +4956,7 @@
         <v>72</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>72</v>
@@ -4998,11 +4968,11 @@
         <v>72</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="19"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -5055,7 +5025,7 @@
         <v>72</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>72</v>
@@ -5068,7 +5038,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="23" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -5093,7 +5063,7 @@
         <v>72</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>72</v>
@@ -5105,13 +5075,13 @@
         <v>72</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>72</v>
@@ -5136,7 +5106,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="21"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -5202,7 +5172,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="22"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -5268,28 +5238,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="25"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="21"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -5355,329 +5325,329 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q30" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="1" t="s">
+      <c r="R30" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U30" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="N30" s="1" t="s">
+      <c r="V30" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="19"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q31" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q31" s="1" t="s">
+      <c r="R31" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U31" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="R31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="V31" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="19"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="R32" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="S32" s="1" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="19"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S33" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="T33" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="U33" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="V33" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="19"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="U34" s="1" t="s">
         <v>72</v>
@@ -5687,7 +5657,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="23" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -5697,19 +5667,19 @@
         <v>72</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>72</v>
@@ -5724,7 +5694,7 @@
         <v>72</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>72</v>
@@ -5755,7 +5725,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="21"/>
+      <c r="A36" s="24"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -5763,7 +5733,7 @@
         <v>72</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>72</v>
@@ -5775,7 +5745,7 @@
         <v>72</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>72</v>
@@ -5821,7 +5791,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="22"/>
+      <c r="A37" s="25"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -5829,7 +5799,7 @@
         <v>72</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>72</v>
@@ -5887,28 +5857,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="24"/>
-      <c r="T40" s="24"/>
-      <c r="U40" s="24"/>
-      <c r="V40" s="25"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="21"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -5974,141 +5944,141 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="T42" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q42" s="1" t="s">
+      <c r="U42" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="V42" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="R42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="V42" s="1" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="19"/>
+      <c r="A43" s="22"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F43" s="1" t="s">
+      <c r="J43" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="P43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="V43" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="M43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="19"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -6119,7 +6089,7 @@
         <v>72</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>72</v>
@@ -6128,7 +6098,7 @@
         <v>72</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>72</v>
@@ -6140,10 +6110,10 @@
         <v>72</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>72</v>
@@ -6158,23 +6128,23 @@
         <v>72</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="19"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -6209,10 +6179,10 @@
         <v>72</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>72</v>
@@ -6236,11 +6206,11 @@
         <v>72</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="19"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -6278,7 +6248,7 @@
         <v>72</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>72</v>
@@ -6306,7 +6276,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="23" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -6319,7 +6289,7 @@
         <v>72</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>72</v>
@@ -6340,7 +6310,7 @@
         <v>72</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>72</v>
@@ -6374,7 +6344,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="21"/>
+      <c r="A48" s="24"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -6440,7 +6410,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="22"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -6506,28 +6476,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="24"/>
-      <c r="K52" s="24"/>
-      <c r="L52" s="24"/>
-      <c r="M52" s="24"/>
-      <c r="N52" s="24"/>
-      <c r="O52" s="24"/>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="24"/>
-      <c r="R52" s="24"/>
-      <c r="S52" s="24"/>
-      <c r="T52" s="24"/>
-      <c r="U52" s="24"/>
-      <c r="V52" s="25"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
+      <c r="U52" s="20"/>
+      <c r="V52" s="21"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -6593,141 +6563,141 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R54" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="N54" s="1" t="s">
+      <c r="S54" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="O54" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="T54" s="1" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="U54" s="1" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="V54" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="19"/>
+      <c r="A55" s="22"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>169</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="O55" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="U55" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="V55" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="19"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -6735,131 +6705,131 @@
         <v>72</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="F56" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S56" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="N56" s="1" t="s">
+      <c r="T56" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="V56" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="O56" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="V56" s="1" t="s">
-        <v>182</v>
-      </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="19"/>
+      <c r="A57" s="22"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="O57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="V57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="V57" s="1" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="19"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -6873,66 +6843,66 @@
         <v>72</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>193</v>
+        <v>72</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="U58" s="1" t="s">
         <v>166</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="23" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
         <v>6</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>72</v>
@@ -6941,34 +6911,34 @@
         <v>72</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>72</v>
@@ -6993,7 +6963,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="21"/>
+      <c r="A60" s="24"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -7007,10 +6977,10 @@
         <v>72</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>72</v>
@@ -7028,7 +6998,7 @@
         <v>72</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>72</v>
@@ -7059,7 +7029,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="22"/>
+      <c r="A61" s="25"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -7073,10 +7043,10 @@
         <v>72</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>72</v>
@@ -7094,7 +7064,7 @@
         <v>72</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>72</v>
@@ -7125,28 +7095,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="24"/>
-      <c r="J64" s="24"/>
-      <c r="K64" s="24"/>
-      <c r="L64" s="24"/>
-      <c r="M64" s="24"/>
-      <c r="N64" s="24"/>
-      <c r="O64" s="24"/>
-      <c r="P64" s="24"/>
-      <c r="Q64" s="24"/>
-      <c r="R64" s="24"/>
-      <c r="S64" s="24"/>
-      <c r="T64" s="24"/>
-      <c r="U64" s="24"/>
-      <c r="V64" s="25"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
+      <c r="R64" s="20"/>
+      <c r="S64" s="20"/>
+      <c r="T64" s="20"/>
+      <c r="U64" s="20"/>
+      <c r="V64" s="21"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -7212,141 +7182,141 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="19" t="s">
+      <c r="A66" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="K66" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="M66" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="O66" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="N66" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O66" s="1" t="s">
+      <c r="P66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="U66" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="V66" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="19"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="G67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I67" s="1" t="s">
+      <c r="K67" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="T67" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="P67" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="T67" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="U67" s="1" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="19"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -7354,79 +7324,79 @@
         <v>72</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="S68" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O68" s="1" t="s">
+      <c r="T68" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="V68" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T68" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="U68" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="V68" s="1" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="19"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>72</v>
@@ -7435,50 +7405,50 @@
         <v>72</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="T69" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R69" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="U69" s="1" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="19"/>
+      <c r="A70" s="22"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -7489,10 +7459,10 @@
         <v>72</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>72</v>
@@ -7501,50 +7471,50 @@
         <v>72</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="T70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="U70" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M70" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T70" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="U70" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="V70" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="23" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -7566,28 +7536,28 @@
         <v>72</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>72</v>
@@ -7612,7 +7582,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="21"/>
+      <c r="A72" s="24"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -7632,10 +7602,10 @@
         <v>72</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>72</v>
@@ -7644,16 +7614,16 @@
         <v>72</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>72</v>
@@ -7678,7 +7648,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="22"/>
+      <c r="A73" s="25"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -7701,7 +7671,7 @@
         <v>72</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>72</v>
@@ -7716,7 +7686,7 @@
         <v>72</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>72</v>
@@ -7745,16 +7715,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -7763,6 +7723,16 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18903091-5D99-4E82-B557-702971302EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2D3F16-CEA1-4EA5-AB6A-2727D7073BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1227,7 +1227,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M7" s="13" t="str">
         <f t="shared" ref="M7:M31" si="0">F$116</f>
@@ -1258,7 +1258,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M8" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1299,7 +1299,7 @@
         <v>85</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1329,7 +1329,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M10" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1360,7 +1360,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M11" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1390,7 +1390,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M12" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1421,7 +1421,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M13" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1451,7 +1451,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M14" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1482,7 +1482,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M15" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1513,7 +1513,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M16" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1544,7 +1544,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M17" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1575,7 +1575,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M18" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1606,7 +1606,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M19" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1637,7 +1637,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M20" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1667,7 +1667,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M21" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1697,7 +1697,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M22" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1727,7 +1727,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M23" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1765,7 +1765,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M24" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1795,7 +1795,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M25" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1825,7 +1825,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M26" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1855,7 +1855,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M27" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1885,7 +1885,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M28" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1915,7 +1915,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M29" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1945,7 +1945,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M30" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1975,7 +1975,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M31" s="13" t="str">
         <f t="shared" si="0"/>
@@ -2004,8 +2004,8 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="L32" s="1" t="s">
-        <v>22</v>
+      <c r="L32" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>36</v>
@@ -2033,8 +2033,8 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1" t="s">
-        <v>22</v>
+      <c r="L33" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>36</v>
@@ -2062,8 +2062,8 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="1" t="s">
-        <v>22</v>
+      <c r="L34" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>36</v>
@@ -2091,8 +2091,8 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="1" t="s">
-        <v>22</v>
+      <c r="L35" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>36</v>
@@ -2120,8 +2120,8 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="1" t="s">
-        <v>22</v>
+      <c r="L36" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>36</v>
@@ -2149,8 +2149,8 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1" t="s">
-        <v>22</v>
+      <c r="L37" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>36</v>
@@ -2178,8 +2178,8 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>22</v>
+      <c r="L38" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>36</v>
@@ -2207,8 +2207,8 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="1" t="s">
-        <v>22</v>
+      <c r="L39" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>36</v>
@@ -2236,8 +2236,8 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="1" t="s">
-        <v>22</v>
+      <c r="L40" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>36</v>
@@ -2265,8 +2265,8 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="1" t="s">
-        <v>22</v>
+      <c r="L41" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>36</v>
@@ -2294,8 +2294,8 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="1" t="s">
-        <v>22</v>
+      <c r="L42" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>36</v>
@@ -2323,8 +2323,8 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="1" t="s">
-        <v>22</v>
+      <c r="L43" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>36</v>
@@ -2352,8 +2352,8 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="1" t="s">
-        <v>22</v>
+      <c r="L44" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>36</v>
@@ -2381,8 +2381,8 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="1" t="s">
-        <v>22</v>
+      <c r="L45" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>36</v>
@@ -2410,8 +2410,8 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="1" t="s">
-        <v>22</v>
+      <c r="L46" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>36</v>
@@ -2439,8 +2439,8 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="L47" s="1" t="s">
-        <v>22</v>
+      <c r="L47" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>36</v>
@@ -2468,8 +2468,8 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="1" t="s">
-        <v>22</v>
+      <c r="L48" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>36</v>
@@ -2497,8 +2497,8 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="1" t="s">
-        <v>22</v>
+      <c r="L49" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>36</v>
@@ -2526,8 +2526,8 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="L50" s="1" t="s">
-        <v>22</v>
+      <c r="L50" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>36</v>
@@ -2555,8 +2555,8 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="L51" s="1" t="s">
-        <v>22</v>
+      <c r="L51" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>36</v>
@@ -2584,8 +2584,8 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="L52" s="1" t="s">
-        <v>22</v>
+      <c r="L52" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>36</v>
@@ -2613,8 +2613,8 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="L53" s="1" t="s">
-        <v>22</v>
+      <c r="L53" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>36</v>
@@ -2642,8 +2642,8 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="L54" s="1" t="s">
-        <v>22</v>
+      <c r="L54" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>36</v>
@@ -2671,8 +2671,8 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="L55" s="1" t="s">
-        <v>22</v>
+      <c r="L55" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>36</v>
@@ -2700,8 +2700,8 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-      <c r="L56" s="1" t="s">
-        <v>22</v>
+      <c r="L56" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>36</v>
@@ -2729,8 +2729,8 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
-      <c r="L57" s="1" t="s">
-        <v>22</v>
+      <c r="L57" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>36</v>
@@ -2758,8 +2758,8 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
-      <c r="L58" s="1" t="s">
-        <v>22</v>
+      <c r="L58" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>36</v>
@@ -2787,8 +2787,8 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
-      <c r="L59" s="1" t="s">
-        <v>22</v>
+      <c r="L59" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>36</v>
@@ -2816,8 +2816,8 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
-      <c r="L60" s="1" t="s">
-        <v>22</v>
+      <c r="L60" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>36</v>
@@ -2845,8 +2845,8 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
-      <c r="L61" s="1" t="s">
-        <v>22</v>
+      <c r="L61" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M61" s="1" t="s">
         <v>36</v>
@@ -2874,8 +2874,8 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
-      <c r="L62" s="1" t="s">
-        <v>24</v>
+      <c r="L62" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>35</v>
@@ -2892,7 +2892,7 @@
         <v>61</v>
       </c>
       <c r="D63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="1">
         <v>70</v>
@@ -2903,8 +2903,8 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
-      <c r="L63" s="1" t="s">
-        <v>24</v>
+      <c r="L63" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>35</v>
@@ -2921,7 +2921,7 @@
         <v>61</v>
       </c>
       <c r="D64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="1">
         <v>70</v>
@@ -2932,8 +2932,8 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
-      <c r="L64" s="1" t="s">
-        <v>24</v>
+      <c r="L64" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>35</v>
@@ -2950,7 +2950,7 @@
         <v>61</v>
       </c>
       <c r="D65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="1">
         <v>50</v>
@@ -2961,8 +2961,8 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
-      <c r="L65" s="1" t="s">
-        <v>24</v>
+      <c r="L65" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>35</v>
@@ -3637,7 +3637,7 @@
         <v>21</v>
       </c>
       <c r="D123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="2" t="b">
         <f t="shared" si="2"/>
@@ -3659,7 +3659,7 @@
         <v>21</v>
       </c>
       <c r="D124" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="2" t="b">
         <f t="shared" si="2"/>
@@ -3703,7 +3703,7 @@
         <v>21</v>
       </c>
       <c r="D126" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="2" t="b">
         <f t="shared" si="2"/>
@@ -3725,7 +3725,7 @@
         <v>21</v>
       </c>
       <c r="D127" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" s="2" t="b">
         <f t="shared" si="2"/>
@@ -3747,7 +3747,7 @@
         <v>21</v>
       </c>
       <c r="D128" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" s="2" t="b">
         <f t="shared" si="2"/>
@@ -3769,7 +3769,7 @@
         <v>21</v>
       </c>
       <c r="D129" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="2" t="b">
         <f t="shared" si="2"/>
@@ -3837,7 +3837,7 @@
         <v>21</v>
       </c>
       <c r="D132" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" s="2" t="b">
         <v>0</v>
@@ -4145,10 +4145,10 @@
         <v>166</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="V6" s="1" t="s">
         <v>169</v>
@@ -4160,7 +4160,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>152</v>
@@ -4172,10 +4172,10 @@
         <v>154</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>157</v>
@@ -4187,37 +4187,37 @@
         <v>160</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="R7" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>166</v>
       </c>
       <c r="T7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="V7" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
@@ -4226,64 +4226,64 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>172</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="S8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="U8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="V8" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
@@ -4292,43 +4292,43 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>178</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>72</v>
@@ -4337,19 +4337,19 @@
         <v>155</v>
       </c>
       <c r="R9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="S9" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="T9" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
@@ -4358,10 +4358,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>72</v>
@@ -4370,49 +4370,49 @@
         <v>72</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="U10" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="V10" s="1" t="s">
         <v>72</v>
@@ -4426,43 +4426,43 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>185</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>72</v>
@@ -4492,19 +4492,19 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>72</v>
@@ -4513,13 +4513,13 @@
         <v>72</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>191</v>
+        <v>72</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>192</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>72</v>
@@ -4567,7 +4567,7 @@
         <v>72</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>72</v>
@@ -4713,7 +4713,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>152</v>
@@ -4722,55 +4722,55 @@
         <v>153</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>157</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="M18" s="1" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="O18" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="P18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="R18" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>166</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
@@ -4779,64 +4779,64 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>159</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
@@ -4845,61 +4845,61 @@
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>175</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="L20" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>72</v>
@@ -4920,22 +4920,22 @@
         <v>72</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>72</v>
@@ -4944,7 +4944,7 @@
         <v>72</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>72</v>
@@ -4953,19 +4953,19 @@
         <v>72</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="T21" s="1" t="s">
         <v>72</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>72</v>
@@ -4995,13 +4995,13 @@
         <v>72</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>72</v>
@@ -5022,7 +5022,7 @@
         <v>72</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>72</v>
@@ -5045,34 +5045,34 @@
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>186</v>
@@ -5117,7 +5117,7 @@
         <v>72</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>72</v>
@@ -5141,7 +5141,7 @@
         <v>72</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>72</v>
@@ -5335,7 +5335,7 @@
         <v>170</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>152</v>
@@ -5347,49 +5347,49 @@
         <v>175</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="J30" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>154</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>159</v>
       </c>
       <c r="N30" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="P30" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>157</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
@@ -5401,7 +5401,7 @@
         <v>174</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>152</v>
@@ -5410,52 +5410,52 @@
         <v>153</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="I31" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>154</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q31" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R31" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="R31" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="S31" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>157</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
@@ -5464,64 +5464,64 @@
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>161</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="T32" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="T32" s="1" t="s">
+      <c r="U32" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="U32" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="V32" s="1" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
@@ -5530,61 +5530,61 @@
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="N33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U33" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="V33" s="1" t="s">
         <v>72</v>
@@ -5596,13 +5596,13 @@
         <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>72</v>
@@ -5611,19 +5611,19 @@
         <v>72</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="K34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>72</v>
@@ -5638,19 +5638,19 @@
         <v>72</v>
       </c>
       <c r="Q34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U34" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>72</v>
@@ -5667,29 +5667,29 @@
         <v>72</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>193</v>
+        <v>72</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="L35" s="1" t="s">
         <v>72</v>
       </c>
@@ -5697,10 +5697,10 @@
         <v>72</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>72</v>
@@ -5733,7 +5733,7 @@
         <v>72</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>72</v>
@@ -5763,7 +5763,7 @@
         <v>72</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>72</v>
@@ -5799,7 +5799,7 @@
         <v>72</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>72</v>
@@ -5951,19 +5951,19 @@
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>170</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>171</v>
@@ -5972,19 +5972,19 @@
         <v>156</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>162</v>
@@ -5996,19 +5996,19 @@
         <v>158</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>165</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
@@ -6017,43 +6017,43 @@
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>174</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="K43" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M43" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="N43" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>72</v>
@@ -6062,19 +6062,19 @@
         <v>158</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="U43" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="V43" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
@@ -6083,19 +6083,19 @@
         <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>72</v>
@@ -6104,16 +6104,16 @@
         <v>72</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>72</v>
@@ -6125,22 +6125,22 @@
         <v>72</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
@@ -6155,13 +6155,13 @@
         <v>72</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>72</v>
@@ -6170,7 +6170,7 @@
         <v>72</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>72</v>
@@ -6179,7 +6179,7 @@
         <v>72</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>72</v>
@@ -6191,16 +6191,16 @@
         <v>72</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="U45" s="1" t="s">
         <v>72</v>
@@ -6236,7 +6236,7 @@
         <v>72</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>72</v>
@@ -6260,13 +6260,13 @@
         <v>72</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="U46" s="1" t="s">
         <v>72</v>
@@ -6289,7 +6289,7 @@
         <v>72</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>193</v>
+        <v>72</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>72</v>
@@ -6316,10 +6316,10 @@
         <v>72</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>72</v>
@@ -6385,7 +6385,7 @@
         <v>72</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>72</v>
@@ -6570,64 +6570,64 @@
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N54" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="N54" s="1" t="s">
+      <c r="O54" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="O54" s="1" t="s">
+      <c r="P54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q54" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q54" s="1" t="s">
+      <c r="R54" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="R54" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="S54" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="T54" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T54" s="1" t="s">
+      <c r="U54" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="U54" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="V54" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
@@ -6636,64 +6636,64 @@
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>166</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>154</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>179</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>161</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="U55" s="1" t="s">
         <v>165</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
@@ -6702,40 +6702,40 @@
         <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>173</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>72</v>
@@ -6744,19 +6744,19 @@
         <v>72</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R56" s="1" t="s">
         <v>161</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>177</v>
@@ -6768,64 +6768,64 @@
         <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="H57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T57" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="U57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V57" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="V57" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
@@ -6846,13 +6846,13 @@
         <v>72</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>152</v>
+        <v>72</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>72</v>
@@ -6867,7 +6867,7 @@
         <v>72</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>72</v>
@@ -6879,19 +6879,19 @@
         <v>72</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
@@ -6902,7 +6902,7 @@
         <v>6</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>72</v>
@@ -6911,34 +6911,34 @@
         <v>72</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>189</v>
+        <v>72</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>187</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>72</v>
@@ -6977,10 +6977,10 @@
         <v>72</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>189</v>
+        <v>72</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>72</v>
@@ -6998,7 +6998,7 @@
         <v>72</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>72</v>
@@ -7043,7 +7043,7 @@
         <v>72</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>72</v>
@@ -7064,7 +7064,7 @@
         <v>72</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>72</v>
@@ -7189,13 +7189,13 @@
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>152</v>
@@ -7204,25 +7204,25 @@
         <v>153</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="J66" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>154</v>
       </c>
       <c r="M66" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N66" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>169</v>
@@ -7231,7 +7231,7 @@
         <v>72</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="R66" s="1" t="s">
         <v>158</v>
@@ -7240,13 +7240,13 @@
         <v>162</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
@@ -7258,10 +7258,10 @@
         <v>173</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>152</v>
@@ -7270,49 +7270,49 @@
         <v>153</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="J67" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>154</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>171</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="R67" s="1" t="s">
         <v>158</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="T67" s="1" t="s">
         <v>166</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
@@ -7321,16 +7321,16 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>195</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>196</v>
@@ -7339,46 +7339,46 @@
         <v>72</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="R68" s="1" t="s">
         <v>155</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="T68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="V68" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="U68" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="V68" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
@@ -7390,22 +7390,22 @@
         <v>72</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>72</v>
@@ -7417,31 +7417,31 @@
         <v>72</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S69" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="R69" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="T69" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="V69" s="1" t="s">
         <v>167</v>
@@ -7459,10 +7459,10 @@
         <v>72</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>72</v>
@@ -7471,7 +7471,7 @@
         <v>72</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>72</v>
@@ -7483,34 +7483,34 @@
         <v>72</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="N70" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="R70" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="V70" s="1" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
@@ -7536,7 +7536,7 @@
         <v>72</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>72</v>
@@ -7545,10 +7545,10 @@
         <v>72</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>191</v>
+        <v>72</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>72</v>
@@ -7557,7 +7557,7 @@
         <v>187</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>72</v>
@@ -7602,7 +7602,7 @@
         <v>72</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>189</v>
+        <v>72</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>72</v>
@@ -7614,16 +7614,16 @@
         <v>72</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>72</v>
@@ -7686,7 +7686,7 @@
         <v>72</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>72</v>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2D3F16-CEA1-4EA5-AB6A-2727D7073BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA466B43-30DE-46CC-AB2B-2C7627C03C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input" sheetId="1" r:id="rId1"/>
@@ -832,15 +832,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -852,6 +843,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4000,28 +4000,28 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="21"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="25"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -4087,7 +4087,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3">
@@ -4155,7 +4155,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="22"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
@@ -4221,7 +4221,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="3">
         <v>3</v>
       </c>
@@ -4274,10 +4274,10 @@
         <v>174</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="U8" s="1" t="s">
         <v>157</v>
@@ -4287,7 +4287,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="3">
         <v>4</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>72</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>72</v>
@@ -4346,14 +4346,14 @@
         <v>168</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>72</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>72</v>
@@ -4406,20 +4406,20 @@
         <v>177</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>180</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="V10" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="3">
@@ -4487,7 +4487,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="24"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
@@ -4553,7 +4553,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="25"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="4">
         <v>8</v>
       </c>
@@ -4619,28 +4619,28 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="21"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="25"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -4706,7 +4706,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3">
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="22"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="3">
         <v>2</v>
       </c>
@@ -4840,7 +4840,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="22"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>154</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>164</v>
@@ -4890,7 +4890,7 @@
         <v>161</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>178</v>
@@ -4902,11 +4902,11 @@
         <v>157</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="22"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="3">
         <v>4</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>72</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>152</v>
@@ -4944,7 +4944,7 @@
         <v>72</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>72</v>
@@ -4953,13 +4953,13 @@
         <v>72</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>177</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="T21" s="1" t="s">
         <v>72</v>
@@ -4972,7 +4972,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A22" s="22"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="3">
         <v>5</v>
       </c>
@@ -4995,13 +4995,13 @@
         <v>72</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>72</v>
@@ -5038,7 +5038,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
@@ -5106,7 +5106,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A24" s="24"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="4">
         <v>7</v>
       </c>
@@ -5172,7 +5172,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A25" s="25"/>
+      <c r="A25" s="22"/>
       <c r="B25" s="4">
         <v>8</v>
       </c>
@@ -5238,28 +5238,28 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="20"/>
-      <c r="V28" s="21"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="24"/>
+      <c r="U28" s="24"/>
+      <c r="V28" s="25"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -5325,7 +5325,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="3">
@@ -5393,7 +5393,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A31" s="22"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="3">
         <v>2</v>
       </c>
@@ -5459,7 +5459,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A32" s="22"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="3">
         <v>3</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>72</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>161</v>
@@ -5521,11 +5521,11 @@
         <v>162</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="22"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="3">
         <v>4</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>72</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>178</v>
@@ -5566,7 +5566,7 @@
         <v>72</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>72</v>
@@ -5587,11 +5587,11 @@
         <v>155</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="22"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>72</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>171</v>
@@ -5641,7 +5641,7 @@
         <v>72</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>72</v>
@@ -5650,14 +5650,14 @@
         <v>72</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3">
@@ -5725,7 +5725,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="24"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="4">
         <v>7</v>
       </c>
@@ -5791,7 +5791,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="25"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="4">
         <v>8</v>
       </c>
@@ -5857,28 +5857,28 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="20"/>
-      <c r="U40" s="20"/>
-      <c r="V40" s="21"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="24"/>
+      <c r="S40" s="24"/>
+      <c r="T40" s="24"/>
+      <c r="U40" s="24"/>
+      <c r="V40" s="25"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
@@ -5944,7 +5944,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="3">
@@ -6012,7 +6012,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="22"/>
+      <c r="A43" s="19"/>
       <c r="B43" s="3">
         <v>2</v>
       </c>
@@ -6078,7 +6078,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="22"/>
+      <c r="A44" s="19"/>
       <c r="B44" s="3">
         <v>3</v>
       </c>
@@ -6144,7 +6144,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="22"/>
+      <c r="A45" s="19"/>
       <c r="B45" s="3">
         <v>4</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>181</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>168</v>
@@ -6173,7 +6173,7 @@
         <v>176</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>72</v>
@@ -6191,26 +6191,26 @@
         <v>72</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>164</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="22"/>
+      <c r="A46" s="19"/>
       <c r="B46" s="3">
         <v>5</v>
       </c>
@@ -6260,23 +6260,23 @@
         <v>72</v>
       </c>
       <c r="R46" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U46" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="S46" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="V46" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B47" s="3">
@@ -6344,7 +6344,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="24"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="4">
         <v>7</v>
       </c>
@@ -6410,7 +6410,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="25"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="4">
         <v>8</v>
       </c>
@@ -6476,28 +6476,28 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C52" s="19" t="s">
+      <c r="C52" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="20"/>
-      <c r="O52" s="20"/>
-      <c r="P52" s="20"/>
-      <c r="Q52" s="20"/>
-      <c r="R52" s="20"/>
-      <c r="S52" s="20"/>
-      <c r="T52" s="20"/>
-      <c r="U52" s="20"/>
-      <c r="V52" s="21"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
+      <c r="N52" s="24"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="24"/>
+      <c r="Q52" s="24"/>
+      <c r="R52" s="24"/>
+      <c r="S52" s="24"/>
+      <c r="T52" s="24"/>
+      <c r="U52" s="24"/>
+      <c r="V52" s="25"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
@@ -6563,7 +6563,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="3">
@@ -6631,7 +6631,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="22"/>
+      <c r="A55" s="19"/>
       <c r="B55" s="3">
         <v>2</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>153</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>166</v>
@@ -6669,7 +6669,7 @@
         <v>160</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>72</v>
@@ -6684,10 +6684,10 @@
         <v>158</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="U55" s="1" t="s">
         <v>165</v>
@@ -6697,7 +6697,7 @@
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="22"/>
+      <c r="A56" s="19"/>
       <c r="B56" s="3">
         <v>3</v>
       </c>
@@ -6763,7 +6763,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57" s="22"/>
+      <c r="A57" s="19"/>
       <c r="B57" s="3">
         <v>4</v>
       </c>
@@ -6771,13 +6771,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>72</v>
@@ -6792,7 +6792,7 @@
         <v>178</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>72</v>
@@ -6819,7 +6819,7 @@
         <v>72</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="U57" s="1" t="s">
         <v>72</v>
@@ -6829,7 +6829,7 @@
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58" s="22"/>
+      <c r="A58" s="19"/>
       <c r="B58" s="3">
         <v>5</v>
       </c>
@@ -6895,7 +6895,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="3">
@@ -6963,7 +6963,7 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60" s="24"/>
+      <c r="A60" s="21"/>
       <c r="B60" s="4">
         <v>7</v>
       </c>
@@ -7029,7 +7029,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61" s="25"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="4">
         <v>8</v>
       </c>
@@ -7095,28 +7095,28 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20"/>
-      <c r="N64" s="20"/>
-      <c r="O64" s="20"/>
-      <c r="P64" s="20"/>
-      <c r="Q64" s="20"/>
-      <c r="R64" s="20"/>
-      <c r="S64" s="20"/>
-      <c r="T64" s="20"/>
-      <c r="U64" s="20"/>
-      <c r="V64" s="21"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="24"/>
+      <c r="J64" s="24"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="24"/>
+      <c r="N64" s="24"/>
+      <c r="O64" s="24"/>
+      <c r="P64" s="24"/>
+      <c r="Q64" s="24"/>
+      <c r="R64" s="24"/>
+      <c r="S64" s="24"/>
+      <c r="T64" s="24"/>
+      <c r="U64" s="24"/>
+      <c r="V64" s="25"/>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
@@ -7182,7 +7182,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3">
@@ -7250,7 +7250,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A67" s="22"/>
+      <c r="A67" s="19"/>
       <c r="B67" s="3">
         <v>2</v>
       </c>
@@ -7270,10 +7270,10 @@
         <v>153</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>169</v>
@@ -7303,7 +7303,7 @@
         <v>158</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="T67" s="1" t="s">
         <v>166</v>
@@ -7316,7 +7316,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A68" s="22"/>
+      <c r="A68" s="19"/>
       <c r="B68" s="3">
         <v>3</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>72</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>164</v>
@@ -7382,7 +7382,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A69" s="22"/>
+      <c r="A69" s="19"/>
       <c r="B69" s="3">
         <v>4</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>72</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>72</v>
@@ -7420,7 +7420,7 @@
         <v>72</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>72</v>
@@ -7435,20 +7435,20 @@
         <v>161</v>
       </c>
       <c r="S69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U69" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="V69" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A70" s="22"/>
+      <c r="A70" s="19"/>
       <c r="B70" s="3">
         <v>5</v>
       </c>
@@ -7514,7 +7514,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A71" s="23" t="s">
+      <c r="A71" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B71" s="3">
@@ -7582,7 +7582,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A72" s="24"/>
+      <c r="A72" s="21"/>
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -7648,7 +7648,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A73" s="25"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -7715,6 +7715,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C28:V28"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C64:V64"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="C40:V40"/>
@@ -7723,16 +7733,6 @@
     <mergeCell ref="C52:V52"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C28:V28"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C64:V64"/>
-    <mergeCell ref="C4:V4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java memory\java learning\java project\TeacherWorkingDistributionSchedule\src\excel_resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA466B43-30DE-46CC-AB2B-2C7627C03C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FA4CB6-FAF4-4EE1-A3C6-1261EAAC1D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3371" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8151" uniqueCount="190">
   <si>
     <t>10A1</t>
   </si>
@@ -457,33 +457,6 @@
     <t>10A4,10A5,10A6,10A7,11B1,11B2,11B4,11B5</t>
   </si>
   <si>
-    <t>Hoàng Thanh Đô</t>
-  </si>
-  <si>
-    <t>10A1,10A2,10A3,10A4,10A5,10A6,10A7,11B1,11B2,11B3,11B4,11B5,11B6, 12C1,12C2,12C3,12C4,12C5,12C6</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Phúc</t>
-  </si>
-  <si>
-    <t>11B1,11B2,12C1,12C2,12C3,12C4,12C5,12C6</t>
-  </si>
-  <si>
-    <t>Hoàng Thanh Quang</t>
-  </si>
-  <si>
-    <t>10A1,10A2,10A3,10A4,10A5,11B3,11B4,11B5,11B6</t>
-  </si>
-  <si>
-    <t>Ngô Thị Hà Chang</t>
-  </si>
-  <si>
-    <t>10A6,10A7</t>
-  </si>
-  <si>
-    <t>Hoàng Thanh Quang-TD</t>
-  </si>
-  <si>
     <t>Củng Thị Trường-Anh</t>
   </si>
   <si>
@@ -544,9 +517,6 @@
     <t>Phạm Văn Đoàn-Tin</t>
   </si>
   <si>
-    <t>Ngô Thị Hà Chang-TD</t>
-  </si>
-  <si>
     <t>Vi Văn Tình-Văn</t>
   </si>
   <si>
@@ -554,9 +524,6 @@
   </si>
   <si>
     <t>Nguyễn Thị Hằng-Sử</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Phúc-TD</t>
   </si>
   <si>
     <t>Tạ Thanh Hải-Anh</t>
@@ -2853,120 +2820,64 @@
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D62" s="1">
-        <v>1</v>
-      </c>
-      <c r="E62" s="1">
-        <v>35</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
-      <c r="L62" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="L62" s="13"/>
+      <c r="M62" s="1"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D63" s="1">
-        <v>1</v>
-      </c>
-      <c r="E63" s="1">
-        <v>70</v>
-      </c>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
-      <c r="L63" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="L63" s="13"/>
+      <c r="M63" s="1"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D64" s="1">
-        <v>1</v>
-      </c>
-      <c r="E64" s="1">
-        <v>70</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
-      <c r="L64" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M64" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="L64" s="13"/>
+      <c r="M64" s="1"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D65" s="1">
-        <v>1</v>
-      </c>
-      <c r="E65" s="1">
-        <v>50</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
-      <c r="L65" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="L65" s="13"/>
+      <c r="M65" s="1"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
@@ -4094,64 +4005,64 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="L6" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="P6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="T6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="V6" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
@@ -4160,64 +4071,64 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="T7" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="U7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="V7" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
@@ -4229,61 +4140,61 @@
         <v>72</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="R8" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="V8" s="1" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
@@ -4301,31 +4212,31 @@
         <v>72</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>72</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>72</v>
@@ -4334,22 +4245,22 @@
         <v>72</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="U9" s="1" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
@@ -4382,13 +4293,13 @@
         <v>72</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>72</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>72</v>
@@ -4403,13 +4314,13 @@
         <v>72</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="U10" s="1" t="s">
         <v>72</v>
@@ -4426,40 +4337,40 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="N11" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>187</v>
@@ -4492,19 +4403,19 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>72</v>
@@ -4516,13 +4427,13 @@
         <v>72</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>72</v>
@@ -4564,10 +4475,10 @@
         <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>72</v>
@@ -4713,64 +4624,64 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="P18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R18" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="T18" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="V18" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
@@ -4779,64 +4690,64 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q19" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="R19" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="U19" s="1" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
@@ -4845,64 +4756,64 @@
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="P20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="S20" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
@@ -4923,19 +4834,19 @@
         <v>72</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>152</v>
+        <v>72</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>72</v>
@@ -4944,7 +4855,7 @@
         <v>72</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>72</v>
@@ -4953,19 +4864,19 @@
         <v>72</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>72</v>
@@ -5022,7 +4933,7 @@
         <v>72</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>72</v>
@@ -5045,40 +4956,40 @@
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="K23" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="M23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>72</v>
@@ -5117,7 +5028,7 @@
         <v>72</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>72</v>
@@ -5126,13 +5037,13 @@
         <v>72</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>72</v>
@@ -5141,7 +5052,7 @@
         <v>72</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>72</v>
@@ -5332,64 +5243,64 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F30" s="1" t="s">
+      <c r="K30" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I30" s="1" t="s">
+      <c r="P30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="S30" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="T30" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="U30" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="U30" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="V30" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
@@ -5398,64 +5309,64 @@
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R31" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="S31" s="1" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="T31" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="U31" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="V31" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
@@ -5464,64 +5375,64 @@
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="K32" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
@@ -5530,16 +5441,16 @@
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>72</v>
@@ -5551,7 +5462,7 @@
         <v>72</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>72</v>
@@ -5560,22 +5471,22 @@
         <v>72</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>72</v>
@@ -5584,10 +5495,10 @@
         <v>72</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
@@ -5617,7 +5528,7 @@
         <v>72</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>72</v>
@@ -5641,7 +5552,7 @@
         <v>72</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>72</v>
@@ -5650,7 +5561,7 @@
         <v>72</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>72</v>
@@ -5676,31 +5587,31 @@
         <v>72</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N35" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>72</v>
@@ -5763,7 +5674,7 @@
         <v>72</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>72</v>
@@ -5951,64 +5862,64 @@
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F42" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="P42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I42" s="1" t="s">
+      <c r="S42" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="T42" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="U42" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="U42" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="V42" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
@@ -6017,64 +5928,64 @@
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J43" s="1" t="s">
+      <c r="K43" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="L43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N43" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="M43" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="O43" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
@@ -6083,64 +5994,64 @@
         <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="K44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="T44" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="U44" s="1" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
@@ -6152,58 +6063,58 @@
         <v>72</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S45" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="S45" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="T45" s="1" t="s">
         <v>72</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>72</v>
@@ -6236,7 +6147,7 @@
         <v>72</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>72</v>
@@ -6269,7 +6180,7 @@
         <v>72</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="V46" s="1" t="s">
         <v>72</v>
@@ -6298,7 +6209,7 @@
         <v>72</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>72</v>
@@ -6310,16 +6221,16 @@
         <v>72</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>72</v>
@@ -6385,7 +6296,7 @@
         <v>72</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>72</v>
@@ -6570,64 +6481,64 @@
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M54" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="N54" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="S54" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="T54" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="U54" s="1" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="V54" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
@@ -6636,64 +6547,64 @@
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q55" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="R55" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="V55" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="V55" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
@@ -6702,64 +6613,64 @@
         <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="S56" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="K56" s="1" t="s">
+      <c r="T56" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V56" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="V56" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
@@ -6768,7 +6679,7 @@
         <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>72</v>
@@ -6777,25 +6688,25 @@
         <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>72</v>
@@ -6810,22 +6721,22 @@
         <v>72</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="S57" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="U57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
@@ -6876,13 +6787,13 @@
         <v>72</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="T58" s="1" t="s">
         <v>72</v>
@@ -6932,10 +6843,10 @@
         <v>72</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="O59" s="1" t="s">
         <v>72</v>
@@ -7189,64 +7100,64 @@
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q66" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="R66" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="S66" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I66" s="1" t="s">
+      <c r="T66" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V66" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M66" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="P66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
@@ -7255,64 +7166,64 @@
         <v>2</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="F67" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L67" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>160</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="T67" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U67" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="V67" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="U67" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="V67" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
@@ -7321,64 +7232,64 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="K68" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="S68" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U68" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="L68" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="T68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U68" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="V68" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
@@ -7390,16 +7301,16 @@
         <v>72</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>72</v>
@@ -7408,7 +7319,7 @@
         <v>72</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>72</v>
@@ -7420,7 +7331,7 @@
         <v>72</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>72</v>
@@ -7429,22 +7340,22 @@
         <v>72</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
@@ -7474,7 +7385,7 @@
         <v>72</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>72</v>
@@ -7554,10 +7465,10 @@
         <v>72</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>72</v>

--- a/src/excel_resources/excel_data.xlsx
+++ b/src/excel_resources/excel_data.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8151" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11031" uniqueCount="190">
   <si>
     <t>10A1</t>
   </si>
@@ -4005,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>143</v>
@@ -4017,7 +4017,7 @@
         <v>145</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>147</v>
@@ -4032,25 +4032,25 @@
         <v>151</v>
       </c>
       <c r="L6" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>153</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>157</v>
@@ -4083,10 +4083,10 @@
         <v>145</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>148</v>
@@ -4098,37 +4098,37 @@
         <v>151</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>150</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>157</v>
       </c>
       <c r="T7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="U7" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="V7" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
@@ -4137,64 +4137,64 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>146</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>167</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>145</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="V8" s="1" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
@@ -4206,61 +4206,61 @@
         <v>72</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U9" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="S9" s="1" t="s">
+      <c r="V9" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
@@ -4299,7 +4299,7 @@
         <v>72</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>72</v>
@@ -4314,7 +4314,7 @@
         <v>72</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>72</v>
@@ -4326,7 +4326,7 @@
         <v>72</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
@@ -4346,7 +4346,7 @@
         <v>172</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>178</v>
@@ -4370,10 +4370,10 @@
         <v>186</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>72</v>
@@ -4430,7 +4430,7 @@
         <v>181</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>183</v>
@@ -4469,13 +4469,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>179</v>
@@ -4624,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>143</v>
@@ -4636,7 +4636,7 @@
         <v>145</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>147</v>
@@ -4651,25 +4651,25 @@
         <v>151</v>
       </c>
       <c r="L18" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>153</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>157</v>
@@ -4690,64 +4690,64 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>144</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>145</v>
       </c>
       <c r="N19" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="P19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="P19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q19" s="1" t="s">
+      <c r="R19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="S19" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="T19" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="U19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="V19" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
@@ -4756,25 +4756,25 @@
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="I20" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>72</v>
@@ -4786,34 +4786,34 @@
         <v>72</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>151</v>
       </c>
       <c r="O20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="R20" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="U20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="V20" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.35">
@@ -4867,19 +4867,19 @@
         <v>72</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="U21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V21" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
@@ -4945,7 +4945,7 @@
         <v>72</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
@@ -4956,40 +4956,40 @@
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>177</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>178</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>175</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>72</v>
@@ -5040,19 +5040,19 @@
         <v>179</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>72</v>
@@ -5243,10 +5243,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>143</v>
@@ -5255,13 +5255,13 @@
         <v>144</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>151</v>
@@ -5270,10 +5270,10 @@
         <v>145</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>160</v>
@@ -5297,10 +5297,10 @@
         <v>148</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
@@ -5309,10 +5309,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>143</v>
@@ -5321,13 +5321,13 @@
         <v>144</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>151</v>
@@ -5342,10 +5342,10 @@
         <v>168</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>72</v>
@@ -5363,10 +5363,10 @@
         <v>148</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
@@ -5375,52 +5375,52 @@
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>152</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>155</v>
@@ -5429,10 +5429,10 @@
         <v>150</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
@@ -5441,25 +5441,25 @@
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>162</v>
@@ -5483,19 +5483,19 @@
         <v>72</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>169</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="V33" s="1" t="s">
         <v>72</v>
@@ -5552,16 +5552,16 @@
         <v>72</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>72</v>
@@ -5587,13 +5587,13 @@
         <v>72</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>72</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>72</v>
@@ -5602,7 +5602,7 @@
         <v>72</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>72</v>
@@ -5674,10 +5674,10 @@
         <v>72</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>72</v>
@@ -5862,10 +5862,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>143</v>
@@ -5874,13 +5874,13 @@
         <v>144</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>151</v>
@@ -5889,10 +5889,10 @@
         <v>145</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>160</v>
@@ -5916,10 +5916,10 @@
         <v>148</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
@@ -5928,25 +5928,25 @@
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="F43" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>143</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>152</v>
@@ -5964,28 +5964,28 @@
         <v>163</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q43" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="R43" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>149</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
@@ -5994,28 +5994,28 @@
         <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>72</v>
@@ -6024,19 +6024,19 @@
         <v>151</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>163</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>72</v>
@@ -6045,13 +6045,13 @@
         <v>149</v>
       </c>
       <c r="T44" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V44" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="V44" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
@@ -6063,7 +6063,7 @@
         <v>72</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>72</v>
@@ -6072,7 +6072,7 @@
         <v>72</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>72</v>
@@ -6090,13 +6090,13 @@
         <v>72</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>72</v>
@@ -6108,13 +6108,13 @@
         <v>72</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>72</v>
@@ -6203,7 +6203,7 @@
         <v>72</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>72</v>
@@ -6212,7 +6212,7 @@
         <v>173</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>72</v>
@@ -6224,7 +6224,7 @@
         <v>72</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>72</v>
@@ -6296,7 +6296,7 @@
         <v>72</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>72</v>
@@ -6481,10 +6481,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>147</v>
@@ -6496,16 +6496,16 @@
         <v>144</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J54" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>145</v>
@@ -6514,31 +6514,31 @@
         <v>151</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="R54" s="1" t="s">
         <v>149</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="U54" s="1" t="s">
         <v>148</v>
       </c>
       <c r="V54" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
@@ -6547,13 +6547,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>143</v>
@@ -6565,13 +6565,13 @@
         <v>185</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J55" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>145</v>
@@ -6580,7 +6580,7 @@
         <v>151</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>72</v>
@@ -6589,22 +6589,22 @@
         <v>72</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="R55" s="1" t="s">
         <v>149</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="U55" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
@@ -6613,40 +6613,40 @@
         <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="F56" s="1" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>143</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="J56" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>152</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>72</v>
@@ -6655,19 +6655,19 @@
         <v>72</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="R56" s="1" t="s">
         <v>164</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>159</v>
@@ -6679,16 +6679,16 @@
         <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>162</v>
@@ -6697,10 +6697,10 @@
         <v>143</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>185</v>
+        <v>72</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>72</v>
@@ -6721,19 +6721,19 @@
         <v>72</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>146</v>
       </c>
       <c r="S57" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="V57" s="1" t="s">
         <v>72</v>
@@ -6766,7 +6766,7 @@
         <v>72</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>72</v>
@@ -6787,16 +6787,16 @@
         <v>72</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="U58" s="1" t="s">
         <v>72</v>
@@ -6837,7 +6837,7 @@
         <v>72</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>72</v>
@@ -6846,7 +6846,7 @@
         <v>72</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="O59" s="1" t="s">
         <v>72</v>
@@ -7100,10 +7100,10 @@
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>147</v>
@@ -7115,16 +7115,16 @@
         <v>144</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>145</v>
@@ -7133,31 +7133,31 @@
         <v>151</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="R66" s="1" t="s">
         <v>149</v>
       </c>
       <c r="S66" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="V66" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
@@ -7166,31 +7166,31 @@
         <v>2</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>164</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>144</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="J67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>152</v>
@@ -7211,19 +7211,19 @@
         <v>169</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>149</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
@@ -7232,31 +7232,31 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>144</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="J68" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>72</v>
@@ -7274,22 +7274,22 @@
         <v>72</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>169</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
@@ -7319,10 +7319,10 @@
         <v>72</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>72</v>
@@ -7331,25 +7331,25 @@
         <v>72</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>72</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="U69" s="1" t="s">
         <v>72</v>
@@ -7385,7 +7385,7 @@
         <v>72</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>72</v>
@@ -7459,16 +7459,16 @@
         <v>72</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>72</v>
